--- a/docs/plan-scaling-diversifie.xlsx
+++ b/docs/plan-scaling-diversifie.xlsx
@@ -90,12 +90,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -125,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -149,7 +149,8 @@
     <xf numFmtId="165" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1155,7 +1156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K190"/>
+  <dimension ref="A1:M190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1169,6 +1170,8 @@
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="17" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1227,6 +1230,16 @@
           <t>Prix cumulé ($)</t>
         </is>
       </c>
+      <c r="L1" s="9" t="inlineStr">
+        <is>
+          <t>Plateforme</t>
+        </is>
+      </c>
+      <c r="M1" s="9" t="inlineStr">
+        <is>
+          <t>MetaTrader 5 ?</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="10" t="n">
@@ -1239,7 +1252,7 @@
       </c>
       <c r="C2" s="10" t="inlineStr">
         <is>
-          <t>FundedHive</t>
+          <t>Real Trader Fund</t>
         </is>
       </c>
       <c r="D2" s="10" t="inlineStr">
@@ -1248,13 +1261,13 @@
         </is>
       </c>
       <c r="E2" s="12" t="n">
-        <v>1000000</v>
+        <v>100000</v>
       </c>
       <c r="F2" s="12" t="n">
-        <v>349</v>
+        <v>360</v>
       </c>
       <c r="G2" s="13" t="n">
-        <v>0.99</v>
+        <v>0.9</v>
       </c>
       <c r="H2" s="12">
         <f>E2*G2</f>
@@ -1271,6 +1284,16 @@
       <c r="K2" s="12">
         <f>F2</f>
         <v/>
+      </c>
+      <c r="L2" s="10" t="inlineStr">
+        <is>
+          <t>MT5</t>
+        </is>
+      </c>
+      <c r="M2" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -1284,7 +1307,7 @@
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>Real Trader Fund</t>
+          <t>Hydra Futures</t>
         </is>
       </c>
       <c r="D3" s="10" t="inlineStr">
@@ -1293,10 +1316,10 @@
         </is>
       </c>
       <c r="E3" s="12" t="n">
-        <v>100000</v>
+        <v>500000</v>
       </c>
       <c r="F3" s="12" t="n">
-        <v>360</v>
+        <v>1980</v>
       </c>
       <c r="G3" s="13" t="n">
         <v>0.9</v>
@@ -1316,6 +1339,16 @@
       <c r="K3" s="12">
         <f>K2+F3</f>
         <v/>
+      </c>
+      <c r="L3" s="10" t="inlineStr">
+        <is>
+          <t>cTrader, DXtrade, Volumetrica</t>
+        </is>
+      </c>
+      <c r="M3" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -1329,7 +1362,7 @@
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>Hydra Futures</t>
+          <t>XPIPS</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
@@ -1338,13 +1371,13 @@
         </is>
       </c>
       <c r="E4" s="12" t="n">
-        <v>500000</v>
+        <v>400000</v>
       </c>
       <c r="F4" s="12" t="n">
-        <v>1980</v>
+        <v>1596</v>
       </c>
       <c r="G4" s="13" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H4" s="12">
         <f>E4*G4</f>
@@ -1361,6 +1394,16 @@
       <c r="K4" s="12">
         <f>K3+F4</f>
         <v/>
+      </c>
+      <c r="L4" s="10" t="inlineStr">
+        <is>
+          <t>MetaTrader 5</t>
+        </is>
+      </c>
+      <c r="M4" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -1374,7 +1417,7 @@
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>XPIPS</t>
+          <t>Elysium Forex</t>
         </is>
       </c>
       <c r="D5" s="10" t="inlineStr">
@@ -1383,13 +1426,13 @@
         </is>
       </c>
       <c r="E5" s="12" t="n">
-        <v>400000</v>
+        <v>1000000</v>
       </c>
       <c r="F5" s="12" t="n">
-        <v>1596</v>
+        <v>4000</v>
       </c>
       <c r="G5" s="13" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H5" s="12">
         <f>E5*G5</f>
@@ -1406,6 +1449,16 @@
       <c r="K5" s="12">
         <f>K4+F5</f>
         <v/>
+      </c>
+      <c r="L5" s="10" t="inlineStr">
+        <is>
+          <t>MT5</t>
+        </is>
+      </c>
+      <c r="M5" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -1419,7 +1472,7 @@
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>Elysium Forex</t>
+          <t>Alpine Funded</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr">
@@ -1428,13 +1481,13 @@
         </is>
       </c>
       <c r="E6" s="12" t="n">
-        <v>1000000</v>
+        <v>200000</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>4000</v>
+        <v>839</v>
       </c>
       <c r="G6" s="13" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H6" s="12">
         <f>E6*G6</f>
@@ -1451,6 +1504,16 @@
       <c r="K6" s="12">
         <f>K5+F6</f>
         <v/>
+      </c>
+      <c r="L6" s="10" t="inlineStr">
+        <is>
+          <t>MetaTrader 5, cTrader</t>
+        </is>
+      </c>
+      <c r="M6" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -1464,7 +1527,7 @@
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>Alpine Funded</t>
+          <t>Funding Pips</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
@@ -1473,10 +1536,10 @@
         </is>
       </c>
       <c r="E7" s="12" t="n">
-        <v>200000</v>
+        <v>300000</v>
       </c>
       <c r="F7" s="12" t="n">
-        <v>839</v>
+        <v>1332</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>1</v>
@@ -1496,6 +1559,16 @@
       <c r="K7" s="12">
         <f>K6+F7</f>
         <v/>
+      </c>
+      <c r="L7" s="10" t="inlineStr">
+        <is>
+          <t>cTrader, Match-Trader</t>
+        </is>
+      </c>
+      <c r="M7" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -1509,7 +1582,7 @@
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>Funding Pips</t>
+          <t>Hex Funded</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
@@ -1518,13 +1591,13 @@
         </is>
       </c>
       <c r="E8" s="12" t="n">
-        <v>300000</v>
+        <v>400000</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>1332</v>
+        <v>1908</v>
       </c>
       <c r="G8" s="13" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H8" s="12">
         <f>E8*G8</f>
@@ -1541,6 +1614,16 @@
       <c r="K8" s="12">
         <f>K7+F8</f>
         <v/>
+      </c>
+      <c r="L8" s="10" t="inlineStr">
+        <is>
+          <t>MT5</t>
+        </is>
+      </c>
+      <c r="M8" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -1554,7 +1637,7 @@
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>Hex Funded</t>
+          <t>FX2 Funding</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr">
@@ -1563,13 +1646,13 @@
         </is>
       </c>
       <c r="E9" s="12" t="n">
-        <v>400000</v>
+        <v>190000</v>
       </c>
       <c r="F9" s="12" t="n">
-        <v>1908</v>
+        <v>1055</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="H9" s="12">
         <f>E9*G9</f>
@@ -1586,6 +1669,16 @@
       <c r="K9" s="12">
         <f>K8+F9</f>
         <v/>
+      </c>
+      <c r="L9" s="10" t="inlineStr">
+        <is>
+          <t>cTrader, DXtrade</t>
+        </is>
+      </c>
+      <c r="M9" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -1599,7 +1692,7 @@
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>FX2 Funding</t>
+          <t>We Copy Trade</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr">
@@ -1608,13 +1701,13 @@
         </is>
       </c>
       <c r="E10" s="12" t="n">
-        <v>190000</v>
+        <v>200000</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>1055</v>
+        <v>2000</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="H10" s="12">
         <f>E10*G10</f>
@@ -1631,6 +1724,16 @@
       <c r="K10" s="12">
         <f>K9+F10</f>
         <v/>
+      </c>
+      <c r="L10" s="10" t="inlineStr">
+        <is>
+          <t>Match-Trader</t>
+        </is>
+      </c>
+      <c r="M10" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -1644,7 +1747,7 @@
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>Audacity Capital (FTP Instant Funding)</t>
+          <t>Ifunds</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
@@ -1653,13 +1756,13 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>240000</v>
+        <v>10000</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>1365</v>
+        <v>700</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="H11" s="12">
         <f>E11*G11</f>
@@ -1676,6 +1779,16 @@
       <c r="K11" s="12">
         <f>K10+F11</f>
         <v/>
+      </c>
+      <c r="L11" s="10" t="inlineStr">
+        <is>
+          <t>MetaTrader 5</t>
+        </is>
+      </c>
+      <c r="M11" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -1689,7 +1802,7 @@
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>FundedForge</t>
+          <t>ADN Broker</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr">
@@ -1698,13 +1811,13 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>100000</v>
+        <v>500000</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>650</v>
+        <v>50000</v>
       </c>
       <c r="G12" s="13" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H12" s="12">
         <f>E12*G12</f>
@@ -1721,6 +1834,16 @@
       <c r="K12" s="12">
         <f>K11+F12</f>
         <v/>
+      </c>
+      <c r="L12" s="10" t="inlineStr">
+        <is>
+          <t>MT5</t>
+        </is>
+      </c>
+      <c r="M12" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -1734,19 +1857,19 @@
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>We Copy Trade</t>
+          <t>Lux Trading Firm</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>Instant</t>
+          <t>1 étape</t>
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>200000</v>
+        <v>5000000</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>2000</v>
+        <v>4995</v>
       </c>
       <c r="G13" s="13" t="n">
         <v>0.9</v>
@@ -1766,6 +1889,16 @@
       <c r="K13" s="12">
         <f>K12+F13</f>
         <v/>
+      </c>
+      <c r="L13" s="10" t="inlineStr">
+        <is>
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="M13" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -1779,22 +1912,22 @@
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>BuoyTrade</t>
+          <t>PaidPex</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>Instant</t>
+          <t>1 étape</t>
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>40000</v>
+        <v>6000000</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>1980</v>
+        <v>11960</v>
       </c>
       <c r="G14" s="13" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H14" s="12">
         <f>E14*G14</f>
@@ -1811,6 +1944,16 @@
       <c r="K14" s="12">
         <f>K13+F14</f>
         <v/>
+      </c>
+      <c r="L14" s="10" t="inlineStr">
+        <is>
+          <t>cTrader</t>
+        </is>
+      </c>
+      <c r="M14" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1824,22 +1967,22 @@
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>Ifunds</t>
+          <t>Hola Prime</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>Instant</t>
+          <t>1 étape</t>
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>10000</v>
+        <v>500000</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>700</v>
+        <v>1236</v>
       </c>
       <c r="G15" s="13" t="n">
-        <v>0.5</v>
+        <v>0.95</v>
       </c>
       <c r="H15" s="12">
         <f>E15*G15</f>
@@ -1856,6 +1999,16 @@
       <c r="K15" s="12">
         <f>K14+F15</f>
         <v/>
+      </c>
+      <c r="L15" s="10" t="inlineStr">
+        <is>
+          <t>cTrader, Match-Trader, TradeLocker</t>
+        </is>
+      </c>
+      <c r="M15" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -1869,19 +2022,19 @@
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>ADN Broker</t>
+          <t>FundYourFX</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>Instant</t>
+          <t>1 étape</t>
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>500000</v>
+        <v>200000</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>50000</v>
+        <v>514</v>
       </c>
       <c r="G16" s="13" t="n">
         <v>1</v>
@@ -1901,6 +2054,16 @@
       <c r="K16" s="12">
         <f>K15+F16</f>
         <v/>
+      </c>
+      <c r="L16" s="10" t="inlineStr">
+        <is>
+          <t>MT5</t>
+        </is>
+      </c>
+      <c r="M16" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -1914,7 +2077,7 @@
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>Lux Trading Firm</t>
+          <t>E8 Perpetuals</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr">
@@ -1923,13 +2086,13 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>5000000</v>
+        <v>500000</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>4995</v>
+        <v>1300</v>
       </c>
       <c r="G17" s="13" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H17" s="12">
         <f>E17*G17</f>
@@ -1946,6 +2109,16 @@
       <c r="K17" s="12">
         <f>K16+F17</f>
         <v/>
+      </c>
+      <c r="L17" s="10" t="inlineStr">
+        <is>
+          <t>MetaTrader 5, cTrader, TradeLocker</t>
+        </is>
+      </c>
+      <c r="M17" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -1959,7 +2132,7 @@
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>PaidPex</t>
+          <t>E8 Markets</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr">
@@ -1968,13 +2141,13 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>6000000</v>
+        <v>500000</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>11960</v>
+        <v>1300</v>
       </c>
       <c r="G18" s="13" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H18" s="12">
         <f>E18*G18</f>
@@ -1991,6 +2164,16 @@
       <c r="K18" s="12">
         <f>K17+F18</f>
         <v/>
+      </c>
+      <c r="L18" s="10" t="inlineStr">
+        <is>
+          <t>MetaTrader 5, cTrader, Match-Trader, Tra</t>
+        </is>
+      </c>
+      <c r="M18" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -2004,7 +2187,7 @@
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>Hola Prime</t>
+          <t>XLTrade</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr">
@@ -2013,13 +2196,13 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>500000</v>
+        <v>1000000</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>1236</v>
+        <v>3168</v>
       </c>
       <c r="G19" s="13" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="H19" s="12">
         <f>E19*G19</f>
@@ -2036,6 +2219,16 @@
       <c r="K19" s="12">
         <f>K18+F19</f>
         <v/>
+      </c>
+      <c r="L19" s="10" t="inlineStr">
+        <is>
+          <t>MetaTrader 5</t>
+        </is>
+      </c>
+      <c r="M19" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -2049,7 +2242,7 @@
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>FundYourFX</t>
+          <t>Funded Traders Pro</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
@@ -2058,10 +2251,10 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>200000</v>
+        <v>1000000</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>514</v>
+        <v>3500</v>
       </c>
       <c r="G20" s="13" t="n">
         <v>1</v>
@@ -2081,6 +2274,16 @@
       <c r="K20" s="12">
         <f>K19+F20</f>
         <v/>
+      </c>
+      <c r="L20" s="10" t="inlineStr">
+        <is>
+          <t>MetaTrader 5</t>
+        </is>
+      </c>
+      <c r="M20" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -2094,7 +2297,7 @@
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>E8 Perpetuals</t>
+          <t>Funded Index</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr">
@@ -2103,13 +2306,13 @@
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>500000</v>
+        <v>100000</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>1300</v>
+        <v>352</v>
       </c>
       <c r="G21" s="13" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="H21" s="12">
         <f>E21*G21</f>
@@ -2126,6 +2329,16 @@
       <c r="K21" s="12">
         <f>K20+F21</f>
         <v/>
+      </c>
+      <c r="L21" s="10" t="inlineStr">
+        <is>
+          <t>cTrader, DXtrade</t>
+        </is>
+      </c>
+      <c r="M21" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -2139,7 +2352,7 @@
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>E8 Markets</t>
+          <t>Propanium</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
@@ -2148,10 +2361,10 @@
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>500000</v>
+        <v>100000</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>1300</v>
+        <v>360</v>
       </c>
       <c r="G22" s="13" t="n">
         <v>1</v>
@@ -2171,6 +2384,16 @@
       <c r="K22" s="12">
         <f>K21+F22</f>
         <v/>
+      </c>
+      <c r="L22" s="10" t="inlineStr">
+        <is>
+          <t>cTrader, TradeLocker</t>
+        </is>
+      </c>
+      <c r="M22" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -2184,7 +2407,7 @@
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>XLTrade</t>
+          <t>Blue Guardian</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">
@@ -2193,13 +2416,13 @@
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>1000000</v>
+        <v>400000</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>3168</v>
+        <v>1472</v>
       </c>
       <c r="G23" s="13" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H23" s="12">
         <f>E23*G23</f>
@@ -2216,6 +2439,16 @@
       <c r="K23" s="12">
         <f>K22+F23</f>
         <v/>
+      </c>
+      <c r="L23" s="10" t="inlineStr">
+        <is>
+          <t>MetaTrader 5, Match-Trader, TradeLocker,</t>
+        </is>
+      </c>
+      <c r="M23" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -2229,7 +2462,7 @@
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>Funded Traders Pro</t>
+          <t>Foxx Funded</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr">
@@ -2238,13 +2471,13 @@
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>1000000</v>
+        <v>500000</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>3500</v>
+        <v>1990</v>
       </c>
       <c r="G24" s="13" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H24" s="12">
         <f>E24*G24</f>
@@ -2261,6 +2494,16 @@
       <c r="K24" s="12">
         <f>K23+F24</f>
         <v/>
+      </c>
+      <c r="L24" s="10" t="inlineStr">
+        <is>
+          <t>MetaTrader 5, cTrader</t>
+        </is>
+      </c>
+      <c r="M24" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -2274,7 +2517,7 @@
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>Funded Index</t>
+          <t>Quantum Funding</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr">
@@ -2283,10 +2526,10 @@
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>100000</v>
+        <v>500000</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>352</v>
+        <v>2145</v>
       </c>
       <c r="G25" s="13" t="n">
         <v>0.8</v>
@@ -2306,6 +2549,16 @@
       <c r="K25" s="12">
         <f>K24+F25</f>
         <v/>
+      </c>
+      <c r="L25" s="10" t="inlineStr">
+        <is>
+          <t>cTrader</t>
+        </is>
+      </c>
+      <c r="M25" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -2319,7 +2572,7 @@
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>Propanium</t>
+          <t>EverFunded</t>
         </is>
       </c>
       <c r="D26" s="10" t="inlineStr">
@@ -2328,10 +2581,10 @@
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>360</v>
+        <v>878</v>
       </c>
       <c r="G26" s="13" t="n">
         <v>1</v>
@@ -2351,6 +2604,16 @@
       <c r="K26" s="12">
         <f>K25+F26</f>
         <v/>
+      </c>
+      <c r="L26" s="10" t="inlineStr">
+        <is>
+          <t>MetaTrader 5, Match-Trader</t>
+        </is>
+      </c>
+      <c r="M26" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -2364,7 +2627,7 @@
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>Blue Guardian</t>
+          <t>Pipcy</t>
         </is>
       </c>
       <c r="D27" s="10" t="inlineStr">
@@ -2373,13 +2636,13 @@
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>400000</v>
+        <v>100000</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>1472</v>
+        <v>459</v>
       </c>
       <c r="G27" s="13" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H27" s="12">
         <f>E27*G27</f>
@@ -2396,6 +2659,16 @@
       <c r="K27" s="12">
         <f>K26+F27</f>
         <v/>
+      </c>
+      <c r="L27" s="10" t="inlineStr">
+        <is>
+          <t>MetaTrader 5</t>
+        </is>
+      </c>
+      <c r="M27" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -2409,7 +2682,7 @@
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>PipFarm</t>
+          <t>IQ Capital</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr">
@@ -2418,13 +2691,13 @@
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>600000</v>
+        <v>1000000</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>2360</v>
+        <v>4750</v>
       </c>
       <c r="G28" s="13" t="n">
-        <v>0.99</v>
+        <v>0.9</v>
       </c>
       <c r="H28" s="12">
         <f>E28*G28</f>
@@ -2441,6 +2714,16 @@
       <c r="K28" s="12">
         <f>K27+F28</f>
         <v/>
+      </c>
+      <c r="L28" s="10" t="inlineStr">
+        <is>
+          <t>MetaTrader 5, NinjaTrader, Tradovate, Qu</t>
+        </is>
+      </c>
+      <c r="M28" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -2454,7 +2737,7 @@
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>Foxx Funded</t>
+          <t>Evercrest Funding</t>
         </is>
       </c>
       <c r="D29" s="10" t="inlineStr">
@@ -2463,13 +2746,13 @@
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>1990</v>
+        <v>1437</v>
       </c>
       <c r="G29" s="13" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="H29" s="12">
         <f>E29*G29</f>
@@ -2486,6 +2769,16 @@
       <c r="K29" s="12">
         <f>K28+F29</f>
         <v/>
+      </c>
+      <c r="L29" s="10" t="inlineStr">
+        <is>
+          <t>MetaTrader 5, TradeLocker</t>
+        </is>
+      </c>
+      <c r="M29" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -2499,7 +2792,7 @@
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>Vanta Trading</t>
+          <t>FunderPro</t>
         </is>
       </c>
       <c r="D30" s="10" t="inlineStr">
@@ -2508,13 +2801,13 @@
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>125000</v>
+        <v>200000</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>498</v>
+        <v>989</v>
       </c>
       <c r="G30" s="13" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H30" s="12">
         <f>E30*G30</f>
@@ -2531,6 +2824,16 @@
       <c r="K30" s="12">
         <f>K29+F30</f>
         <v/>
+      </c>
+      <c r="L30" s="10" t="inlineStr">
+        <is>
+          <t>cTrader, TradeLocker</t>
+        </is>
+      </c>
+      <c r="M30" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="31">
@@ -2544,7 +2847,7 @@
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>Quantum Funding</t>
+          <t>FTMO</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr">
@@ -2553,13 +2856,13 @@
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>500000</v>
+        <v>400000</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>2145</v>
+        <v>1996</v>
       </c>
       <c r="G31" s="13" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H31" s="12">
         <f>E31*G31</f>
@@ -2576,6 +2879,16 @@
       <c r="K31" s="12">
         <f>K30+F31</f>
         <v/>
+      </c>
+      <c r="L31" s="10" t="inlineStr">
+        <is>
+          <t>MetaTrader 5, cTrader, TradingView</t>
+        </is>
+      </c>
+      <c r="M31" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -2589,7 +2902,7 @@
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>EverFunded</t>
+          <t>FTMO Crypto</t>
         </is>
       </c>
       <c r="D32" s="10" t="inlineStr">
@@ -2598,13 +2911,13 @@
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>200000</v>
+        <v>400000</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>878</v>
+        <v>1996</v>
       </c>
       <c r="G32" s="13" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H32" s="12">
         <f>E32*G32</f>
@@ -2621,6 +2934,16 @@
       <c r="K32" s="12">
         <f>K31+F32</f>
         <v/>
+      </c>
+      <c r="L32" s="10" t="inlineStr">
+        <is>
+          <t>MetaTrader 5, cTrader, TradingView</t>
+        </is>
+      </c>
+      <c r="M32" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="33">
@@ -2634,7 +2957,7 @@
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>FundedFX</t>
+          <t>Funded Trading Plus</t>
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr">
@@ -2646,7 +2969,7 @@
         <v>200000</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>900</v>
+        <v>999</v>
       </c>
       <c r="G33" s="13" t="n">
         <v>0.9</v>
@@ -2666,6 +2989,16 @@
       <c r="K33" s="12">
         <f>K32+F33</f>
         <v/>
+      </c>
+      <c r="L33" s="10" t="inlineStr">
+        <is>
+          <t>cTrader, Match-Trader, DXtrade</t>
+        </is>
+      </c>
+      <c r="M33" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -2679,7 +3012,7 @@
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t>Pipcy</t>
+          <t>Kubera Markets</t>
         </is>
       </c>
       <c r="D34" s="10" t="inlineStr">
@@ -2688,13 +3021,13 @@
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>100000</v>
+        <v>5000</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>459</v>
+        <v>25</v>
       </c>
       <c r="G34" s="13" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H34" s="12">
         <f>E34*G34</f>
@@ -2711,6 +3044,16 @@
       <c r="K34" s="12">
         <f>K33+F34</f>
         <v/>
+      </c>
+      <c r="L34" s="10" t="inlineStr">
+        <is>
+          <t>MT5</t>
+        </is>
+      </c>
+      <c r="M34" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="35">
@@ -2724,7 +3067,7 @@
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>IQ Capital</t>
+          <t>TradersFlow</t>
         </is>
       </c>
       <c r="D35" s="10" t="inlineStr">
@@ -2733,10 +3076,10 @@
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>1000000</v>
+        <v>400000</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>4750</v>
+        <v>2018</v>
       </c>
       <c r="G35" s="13" t="n">
         <v>0.9</v>
@@ -2756,6 +3099,16 @@
       <c r="K35" s="12">
         <f>K34+F35</f>
         <v/>
+      </c>
+      <c r="L35" s="10" t="inlineStr">
+        <is>
+          <t>MetaTrader 5</t>
+        </is>
+      </c>
+      <c r="M35" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="36">
@@ -2769,7 +3122,7 @@
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t>Evercrest Funding</t>
+          <t>CK Capital</t>
         </is>
       </c>
       <c r="D36" s="10" t="inlineStr">
@@ -2778,13 +3131,13 @@
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>300000</v>
+        <v>200000</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>1437</v>
+        <v>1056</v>
       </c>
       <c r="G36" s="13" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="H36" s="12">
         <f>E36*G36</f>
@@ -2801,6 +3154,16 @@
       <c r="K36" s="12">
         <f>K35+F36</f>
         <v/>
+      </c>
+      <c r="L36" s="10" t="inlineStr">
+        <is>
+          <t>TradeLocker</t>
+        </is>
+      </c>
+      <c r="M36" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="37">
@@ -2814,7 +3177,7 @@
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>Pipster</t>
+          <t>Funded Trader Markets</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
@@ -2823,10 +3186,10 @@
         </is>
       </c>
       <c r="E37" s="12" t="n">
-        <v>200000</v>
+        <v>1000000</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>958</v>
+        <v>5436</v>
       </c>
       <c r="G37" s="13" t="n">
         <v>0.9</v>
@@ -2846,6 +3209,16 @@
       <c r="K37" s="12">
         <f>K36+F37</f>
         <v/>
+      </c>
+      <c r="L37" s="10" t="inlineStr">
+        <is>
+          <t>cTrader, Match-Trader, TradeLocker</t>
+        </is>
+      </c>
+      <c r="M37" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -2859,7 +3232,7 @@
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>FunderPro</t>
+          <t>Velotrade</t>
         </is>
       </c>
       <c r="D38" s="10" t="inlineStr">
@@ -2871,7 +3244,7 @@
         <v>200000</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>989</v>
+        <v>1114</v>
       </c>
       <c r="G38" s="13" t="n">
         <v>0.9</v>
@@ -2891,6 +3264,16 @@
       <c r="K38" s="12">
         <f>K37+F38</f>
         <v/>
+      </c>
+      <c r="L38" s="10" t="inlineStr">
+        <is>
+          <t>DXtrade</t>
+        </is>
+      </c>
+      <c r="M38" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="39">
@@ -2904,7 +3287,7 @@
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>FTMO</t>
+          <t>The Trading Pit</t>
         </is>
       </c>
       <c r="D39" s="10" t="inlineStr">
@@ -2916,10 +3299,10 @@
         <v>400000</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>1996</v>
+        <v>2276</v>
       </c>
       <c r="G39" s="13" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="H39" s="12">
         <f>E39*G39</f>
@@ -2936,6 +3319,16 @@
       <c r="K39" s="12">
         <f>K38+F39</f>
         <v/>
+      </c>
+      <c r="L39" s="10" t="inlineStr">
+        <is>
+          <t>MT5</t>
+        </is>
+      </c>
+      <c r="M39" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -2949,7 +3342,7 @@
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>FTMO Crypto</t>
+          <t>Space Funded</t>
         </is>
       </c>
       <c r="D40" s="10" t="inlineStr">
@@ -2958,10 +3351,10 @@
         </is>
       </c>
       <c r="E40" s="12" t="n">
-        <v>400000</v>
+        <v>1000000</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>1996</v>
+        <v>5696</v>
       </c>
       <c r="G40" s="13" t="n">
         <v>0.9</v>
@@ -2981,6 +3374,16 @@
       <c r="K40" s="12">
         <f>K39+F40</f>
         <v/>
+      </c>
+      <c r="L40" s="10" t="inlineStr">
+        <is>
+          <t>MetaTrader 5</t>
+        </is>
+      </c>
+      <c r="M40" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="41">
@@ -2994,7 +3397,7 @@
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>Funded Trading Plus</t>
+          <t>FTMO US</t>
         </is>
       </c>
       <c r="D41" s="10" t="inlineStr">
@@ -3003,10 +3406,10 @@
         </is>
       </c>
       <c r="E41" s="12" t="n">
-        <v>200000</v>
+        <v>400000</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>999</v>
+        <v>2298</v>
       </c>
       <c r="G41" s="13" t="n">
         <v>0.9</v>
@@ -3026,6 +3429,16 @@
       <c r="K41" s="12">
         <f>K40+F41</f>
         <v/>
+      </c>
+      <c r="L41" s="10" t="inlineStr">
+        <is>
+          <t>MetaTrader 5, TradingView</t>
+        </is>
+      </c>
+      <c r="M41" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="42">
@@ -3039,7 +3452,7 @@
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t>Kubera Markets</t>
+          <t>Leveraged Crypto</t>
         </is>
       </c>
       <c r="D42" s="10" t="inlineStr">
@@ -3048,13 +3461,13 @@
         </is>
       </c>
       <c r="E42" s="12" t="n">
-        <v>5000</v>
+        <v>150000</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>25</v>
+        <v>980</v>
       </c>
       <c r="G42" s="13" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="H42" s="12">
         <f>E42*G42</f>
@@ -3071,6 +3484,16 @@
       <c r="K42" s="12">
         <f>K41+F42</f>
         <v/>
+      </c>
+      <c r="L42" s="10" t="inlineStr">
+        <is>
+          <t>MetaTrader 5</t>
+        </is>
+      </c>
+      <c r="M42" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="43">
@@ -3084,7 +3507,7 @@
       </c>
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t>Perps Fund</t>
+          <t>Paid To Trade</t>
         </is>
       </c>
       <c r="D43" s="10" t="inlineStr">
@@ -3093,13 +3516,13 @@
         </is>
       </c>
       <c r="E43" s="12" t="n">
-        <v>5000</v>
+        <v>100000</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>25</v>
+        <v>699</v>
       </c>
       <c r="G43" s="13" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H43" s="12">
         <f>E43*G43</f>
@@ -3116,6 +3539,16 @@
       <c r="K43" s="12">
         <f>K42+F43</f>
         <v/>
+      </c>
+      <c r="L43" s="10" t="inlineStr">
+        <is>
+          <t>Match-Trader</t>
+        </is>
+      </c>
+      <c r="M43" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="44">
@@ -3129,7 +3562,7 @@
       </c>
       <c r="C44" s="10" t="inlineStr">
         <is>
-          <t>TradersFlow</t>
+          <t>Capital Mint Markets</t>
         </is>
       </c>
       <c r="D44" s="10" t="inlineStr">
@@ -3138,10 +3571,10 @@
         </is>
       </c>
       <c r="E44" s="12" t="n">
-        <v>400000</v>
+        <v>100000</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>2018</v>
+        <v>699</v>
       </c>
       <c r="G44" s="13" t="n">
         <v>0.9</v>
@@ -3161,6 +3594,16 @@
       <c r="K44" s="12">
         <f>K43+F44</f>
         <v/>
+      </c>
+      <c r="L44" s="10" t="inlineStr">
+        <is>
+          <t>MetaTrader 5, Rithmic</t>
+        </is>
+      </c>
+      <c r="M44" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="45">
@@ -3174,7 +3617,7 @@
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t>CK Capital</t>
+          <t>The Whale Order</t>
         </is>
       </c>
       <c r="D45" s="10" t="inlineStr">
@@ -3183,13 +3626,13 @@
         </is>
       </c>
       <c r="E45" s="12" t="n">
-        <v>200000</v>
+        <v>2000000</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>1056</v>
+        <v>14000</v>
       </c>
       <c r="G45" s="13" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H45" s="12">
         <f>E45*G45</f>
@@ -3206,6 +3649,16 @@
       <c r="K45" s="12">
         <f>K44+F45</f>
         <v/>
+      </c>
+      <c r="L45" s="10" t="inlineStr">
+        <is>
+          <t>DXtrade</t>
+        </is>
+      </c>
+      <c r="M45" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="46">
@@ -3219,7 +3672,7 @@
       </c>
       <c r="C46" s="10" t="inlineStr">
         <is>
-          <t>Funded Trader Markets</t>
+          <t>We Fund Traders</t>
         </is>
       </c>
       <c r="D46" s="10" t="inlineStr">
@@ -3228,10 +3681,10 @@
         </is>
       </c>
       <c r="E46" s="12" t="n">
-        <v>1000000</v>
+        <v>925000</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>5436</v>
+        <v>6550</v>
       </c>
       <c r="G46" s="13" t="n">
         <v>0.9</v>
@@ -3251,6 +3704,16 @@
       <c r="K46" s="12">
         <f>K45+F46</f>
         <v/>
+      </c>
+      <c r="L46" s="10" t="inlineStr">
+        <is>
+          <t>cTrader, Match-Trader, DXtrade</t>
+        </is>
+      </c>
+      <c r="M46" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="47">
@@ -3264,7 +3727,7 @@
       </c>
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t>Velotrade</t>
+          <t>IF Crypto</t>
         </is>
       </c>
       <c r="D47" s="10" t="inlineStr">
@@ -3273,10 +3736,10 @@
         </is>
       </c>
       <c r="E47" s="12" t="n">
-        <v>200000</v>
+        <v>1000000</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>1114</v>
+        <v>7390</v>
       </c>
       <c r="G47" s="13" t="n">
         <v>0.9</v>
@@ -3296,6 +3759,16 @@
       <c r="K47" s="12">
         <f>K46+F47</f>
         <v/>
+      </c>
+      <c r="L47" s="10" t="inlineStr">
+        <is>
+          <t>cTrader, Match-Trader</t>
+        </is>
+      </c>
+      <c r="M47" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="48">
@@ -3309,7 +3782,7 @@
       </c>
       <c r="C48" s="10" t="inlineStr">
         <is>
-          <t>The Trading Pit</t>
+          <t>Instant Funding</t>
         </is>
       </c>
       <c r="D48" s="10" t="inlineStr">
@@ -3318,13 +3791,13 @@
         </is>
       </c>
       <c r="E48" s="12" t="n">
-        <v>400000</v>
+        <v>1000000</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>2276</v>
+        <v>7390</v>
       </c>
       <c r="G48" s="13" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H48" s="12">
         <f>E48*G48</f>
@@ -3341,6 +3814,16 @@
       <c r="K48" s="12">
         <f>K47+F48</f>
         <v/>
+      </c>
+      <c r="L48" s="10" t="inlineStr">
+        <is>
+          <t>MetaTrader 5, cTrader, Match-Trader</t>
+        </is>
+      </c>
+      <c r="M48" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="49">
@@ -3354,7 +3837,7 @@
       </c>
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t>Space Funded</t>
+          <t>Investabl</t>
         </is>
       </c>
       <c r="D49" s="10" t="inlineStr">
@@ -3363,13 +3846,13 @@
         </is>
       </c>
       <c r="E49" s="12" t="n">
-        <v>1000000</v>
+        <v>25000</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>5696</v>
+        <v>209</v>
       </c>
       <c r="G49" s="13" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="H49" s="12">
         <f>E49*G49</f>
@@ -3386,6 +3869,16 @@
       <c r="K49" s="12">
         <f>K48+F49</f>
         <v/>
+      </c>
+      <c r="L49" s="10" t="inlineStr">
+        <is>
+          <t>MetaTrader 5</t>
+        </is>
+      </c>
+      <c r="M49" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="50">
@@ -3399,7 +3892,7 @@
       </c>
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t>FTMO US</t>
+          <t>Kingdom Wealth Funding</t>
         </is>
       </c>
       <c r="D50" s="10" t="inlineStr">
@@ -3408,13 +3901,13 @@
         </is>
       </c>
       <c r="E50" s="12" t="n">
-        <v>400000</v>
+        <v>1000000</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>2298</v>
+        <v>8500</v>
       </c>
       <c r="G50" s="13" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="H50" s="12">
         <f>E50*G50</f>
@@ -3431,6 +3924,16 @@
       <c r="K50" s="12">
         <f>K49+F50</f>
         <v/>
+      </c>
+      <c r="L50" s="10" t="inlineStr">
+        <is>
+          <t>MT5</t>
+        </is>
+      </c>
+      <c r="M50" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="51">
@@ -3444,7 +3947,7 @@
       </c>
       <c r="C51" s="10" t="inlineStr">
         <is>
-          <t>Kickstart Trading</t>
+          <t>Ment Funding</t>
         </is>
       </c>
       <c r="D51" s="10" t="inlineStr">
@@ -3453,10 +3956,10 @@
         </is>
       </c>
       <c r="E51" s="12" t="n">
-        <v>1000000</v>
+        <v>190000</v>
       </c>
       <c r="F51" s="12" t="n">
-        <v>6500</v>
+        <v>7451</v>
       </c>
       <c r="G51" s="13" t="n">
         <v>0.9</v>
@@ -3476,6 +3979,16 @@
       <c r="K51" s="12">
         <f>K50+F51</f>
         <v/>
+      </c>
+      <c r="L51" s="10" t="inlineStr">
+        <is>
+          <t>cTrader, DXtrade</t>
+        </is>
+      </c>
+      <c r="M51" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="52">
@@ -3489,22 +4002,22 @@
       </c>
       <c r="C52" s="10" t="inlineStr">
         <is>
-          <t>Leveraged Crypto</t>
+          <t>HUMBPROP</t>
         </is>
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
-          <t>1 étape</t>
+          <t>2 étapes</t>
         </is>
       </c>
       <c r="E52" s="12" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>980</v>
+        <v>239</v>
       </c>
       <c r="G52" s="13" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="H52" s="12">
         <f>E52*G52</f>
@@ -3521,6 +4034,16 @@
       <c r="K52" s="12">
         <f>K51+F52</f>
         <v/>
+      </c>
+      <c r="L52" s="10" t="inlineStr">
+        <is>
+          <t>MT5</t>
+        </is>
+      </c>
+      <c r="M52" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="53">
@@ -3534,19 +4057,19 @@
       </c>
       <c r="C53" s="10" t="inlineStr">
         <is>
-          <t>Get Funded Now</t>
+          <t>FundedCobra</t>
         </is>
       </c>
       <c r="D53" s="10" t="inlineStr">
         <is>
-          <t>1 étape</t>
+          <t>2 étapes</t>
         </is>
       </c>
       <c r="E53" s="12" t="n">
-        <v>400000</v>
+        <v>200000</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>2625</v>
+        <v>594</v>
       </c>
       <c r="G53" s="13" t="n">
         <v>0.9</v>
@@ -3566,6 +4089,16 @@
       <c r="K53" s="12">
         <f>K52+F53</f>
         <v/>
+      </c>
+      <c r="L53" s="10" t="inlineStr">
+        <is>
+          <t>MetaTrader 5</t>
+        </is>
+      </c>
+      <c r="M53" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="54">
@@ -3579,19 +4112,19 @@
       </c>
       <c r="C54" s="10" t="inlineStr">
         <is>
-          <t>Paid To Trade</t>
+          <t>The Proven Trader</t>
         </is>
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
-          <t>1 étape</t>
+          <t>2 étapes</t>
         </is>
       </c>
       <c r="E54" s="12" t="n">
-        <v>100000</v>
+        <v>1000000</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>699</v>
+        <v>3000</v>
       </c>
       <c r="G54" s="13" t="n">
         <v>0.9</v>
@@ -3611,6 +4144,16 @@
       <c r="K54" s="12">
         <f>K53+F54</f>
         <v/>
+      </c>
+      <c r="L54" s="10" t="inlineStr">
+        <is>
+          <t>MetaTrader 5</t>
+        </is>
+      </c>
+      <c r="M54" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="55">
@@ -3624,22 +4167,22 @@
       </c>
       <c r="C55" s="10" t="inlineStr">
         <is>
-          <t>Capital Mint Markets</t>
+          <t>Core Funded</t>
         </is>
       </c>
       <c r="D55" s="10" t="inlineStr">
         <is>
-          <t>1 étape</t>
+          <t>2 étapes</t>
         </is>
       </c>
       <c r="E55" s="12" t="n">
-        <v>100000</v>
+        <v>500000</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>699</v>
+        <v>1695</v>
       </c>
       <c r="G55" s="13" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="H55" s="12">
         <f>E55*G55</f>
@@ -3656,6 +4199,16 @@
       <c r="K55" s="12">
         <f>K54+F55</f>
         <v/>
+      </c>
+      <c r="L55" s="10" t="inlineStr">
+        <is>
+          <t>cTrader, Match-Trader</t>
+        </is>
+      </c>
+      <c r="M55" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="56">
@@ -3669,19 +4222,19 @@
       </c>
       <c r="C56" s="10" t="inlineStr">
         <is>
-          <t>Propr</t>
+          <t>Zeno Traders</t>
         </is>
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
-          <t>1 étape</t>
+          <t>2 étapes</t>
         </is>
       </c>
       <c r="E56" s="12" t="n">
-        <v>300000</v>
+        <v>200000</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>2097</v>
+        <v>749</v>
       </c>
       <c r="G56" s="13" t="n">
         <v>0.8</v>
@@ -3701,6 +4254,16 @@
       <c r="K56" s="12">
         <f>K55+F56</f>
         <v/>
+      </c>
+      <c r="L56" s="10" t="inlineStr">
+        <is>
+          <t>cTrader, TradingView</t>
+        </is>
+      </c>
+      <c r="M56" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="57">
@@ -3714,19 +4277,19 @@
       </c>
       <c r="C57" s="10" t="inlineStr">
         <is>
-          <t>The Whale Order</t>
+          <t>T4TCapital</t>
         </is>
       </c>
       <c r="D57" s="10" t="inlineStr">
         <is>
-          <t>1 étape</t>
+          <t>2 étapes</t>
         </is>
       </c>
       <c r="E57" s="12" t="n">
-        <v>2000000</v>
+        <v>200000</v>
       </c>
       <c r="F57" s="12" t="n">
-        <v>14000</v>
+        <v>800</v>
       </c>
       <c r="G57" s="13" t="n">
         <v>0.9</v>
@@ -3746,6 +4309,16 @@
       <c r="K57" s="12">
         <f>K56+F57</f>
         <v/>
+      </c>
+      <c r="L57" s="10" t="inlineStr">
+        <is>
+          <t>MetaTrader 5, cTrader</t>
+        </is>
+      </c>
+      <c r="M57" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="58">
@@ -3759,19 +4332,19 @@
       </c>
       <c r="C58" s="10" t="inlineStr">
         <is>
-          <t>We Fund Traders</t>
+          <t>TrioFunded</t>
         </is>
       </c>
       <c r="D58" s="10" t="inlineStr">
         <is>
-          <t>1 étape</t>
+          <t>2 étapes</t>
         </is>
       </c>
       <c r="E58" s="12" t="n">
-        <v>925000</v>
+        <v>500000</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>6550</v>
+        <v>2104</v>
       </c>
       <c r="G58" s="13" t="n">
         <v>0.9</v>
@@ -3791,6 +4364,16 @@
       <c r="K58" s="12">
         <f>K57+F58</f>
         <v/>
+      </c>
+      <c r="L58" s="10" t="inlineStr">
+        <is>
+          <t>MetaTrader 5</t>
+        </is>
+      </c>
+      <c r="M58" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="59">
@@ -3804,22 +4387,22 @@
       </c>
       <c r="C59" s="10" t="inlineStr">
         <is>
-          <t>IF Crypto</t>
+          <t>Mainet Funded</t>
         </is>
       </c>
       <c r="D59" s="10" t="inlineStr">
         <is>
-          <t>1 étape</t>
+          <t>2 étapes</t>
         </is>
       </c>
       <c r="E59" s="12" t="n">
-        <v>1000000</v>
+        <v>700000</v>
       </c>
       <c r="F59" s="12" t="n">
-        <v>7390</v>
+        <v>2975</v>
       </c>
       <c r="G59" s="13" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="H59" s="12">
         <f>E59*G59</f>
@@ -3836,6 +4419,16 @@
       <c r="K59" s="12">
         <f>K58+F59</f>
         <v/>
+      </c>
+      <c r="L59" s="10" t="inlineStr">
+        <is>
+          <t>MT5</t>
+        </is>
+      </c>
+      <c r="M59" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="60">
@@ -3849,22 +4442,22 @@
       </c>
       <c r="C60" s="10" t="inlineStr">
         <is>
-          <t>Instant Funding</t>
+          <t>SFX Funded</t>
         </is>
       </c>
       <c r="D60" s="10" t="inlineStr">
         <is>
-          <t>1 étape</t>
+          <t>2 étapes</t>
         </is>
       </c>
       <c r="E60" s="12" t="n">
-        <v>1000000</v>
+        <v>495000</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>7390</v>
+        <v>2125</v>
       </c>
       <c r="G60" s="13" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H60" s="12">
         <f>E60*G60</f>
@@ -3881,6 +4474,16 @@
       <c r="K60" s="12">
         <f>K59+F60</f>
         <v/>
+      </c>
+      <c r="L60" s="10" t="inlineStr">
+        <is>
+          <t>Match-Trader</t>
+        </is>
+      </c>
+      <c r="M60" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="61">
@@ -3894,19 +4497,19 @@
       </c>
       <c r="C61" s="10" t="inlineStr">
         <is>
-          <t>HyperStack</t>
+          <t>Ultimate Traders</t>
         </is>
       </c>
       <c r="D61" s="10" t="inlineStr">
         <is>
-          <t>1 étape</t>
+          <t>2 étapes</t>
         </is>
       </c>
       <c r="E61" s="12" t="n">
-        <v>100000</v>
+        <v>400000</v>
       </c>
       <c r="F61" s="12" t="n">
-        <v>799</v>
+        <v>1798</v>
       </c>
       <c r="G61" s="13" t="n">
         <v>0.9</v>
@@ -3926,6 +4529,16 @@
       <c r="K61" s="12">
         <f>K60+F61</f>
         <v/>
+      </c>
+      <c r="L61" s="10" t="inlineStr">
+        <is>
+          <t>MT5</t>
+        </is>
+      </c>
+      <c r="M61" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="62">
@@ -3939,22 +4552,22 @@
       </c>
       <c r="C62" s="10" t="inlineStr">
         <is>
-          <t>Investabl</t>
+          <t>Funded Roll</t>
         </is>
       </c>
       <c r="D62" s="10" t="inlineStr">
         <is>
-          <t>1 étape</t>
+          <t>2 étapes</t>
         </is>
       </c>
       <c r="E62" s="12" t="n">
-        <v>25000</v>
+        <v>200000</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>209</v>
+        <v>899</v>
       </c>
       <c r="G62" s="13" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H62" s="12">
         <f>E62*G62</f>
@@ -3971,6 +4584,16 @@
       <c r="K62" s="12">
         <f>K61+F62</f>
         <v/>
+      </c>
+      <c r="L62" s="10" t="inlineStr">
+        <is>
+          <t>MetaTrader 5</t>
+        </is>
+      </c>
+      <c r="M62" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="63">
@@ -3984,19 +4607,19 @@
       </c>
       <c r="C63" s="10" t="inlineStr">
         <is>
-          <t>Kingdom Wealth Funding</t>
+          <t>NowTradeFunded</t>
         </is>
       </c>
       <c r="D63" s="10" t="inlineStr">
         <is>
-          <t>1 étape</t>
+          <t>2 étapes</t>
         </is>
       </c>
       <c r="E63" s="12" t="n">
-        <v>1000000</v>
+        <v>200000</v>
       </c>
       <c r="F63" s="12" t="n">
-        <v>8500</v>
+        <v>900</v>
       </c>
       <c r="G63" s="13" t="n">
         <v>0.8</v>
@@ -4016,6 +4639,16 @@
       <c r="K63" s="12">
         <f>K62+F63</f>
         <v/>
+      </c>
+      <c r="L63" s="10" t="inlineStr">
+        <is>
+          <t>cTrader</t>
+        </is>
+      </c>
+      <c r="M63" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="64">
@@ -4029,19 +4662,19 @@
       </c>
       <c r="C64" s="10" t="inlineStr">
         <is>
-          <t>DojoTraders</t>
+          <t>Fill88</t>
         </is>
       </c>
       <c r="D64" s="10" t="inlineStr">
         <is>
-          <t>1 étape</t>
+          <t>2 étapes</t>
         </is>
       </c>
       <c r="E64" s="12" t="n">
-        <v>500000</v>
+        <v>640000</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>4250</v>
+        <v>2885</v>
       </c>
       <c r="G64" s="13" t="n">
         <v>0.9</v>
@@ -4061,6 +4694,16 @@
       <c r="K64" s="12">
         <f>K63+F64</f>
         <v/>
+      </c>
+      <c r="L64" s="10" t="inlineStr">
+        <is>
+          <t>MetaTrader 5, cTrader, Match-Trader</t>
+        </is>
+      </c>
+      <c r="M64" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="65">
@@ -4074,19 +4717,19 @@
       </c>
       <c r="C65" s="10" t="inlineStr">
         <is>
-          <t>Dojifunded</t>
+          <t>Pro Traders Fund</t>
         </is>
       </c>
       <c r="D65" s="10" t="inlineStr">
         <is>
-          <t>1 étape</t>
+          <t>2 étapes</t>
         </is>
       </c>
       <c r="E65" s="12" t="n">
-        <v>100000</v>
+        <v>900000</v>
       </c>
       <c r="F65" s="12" t="n">
-        <v>892</v>
+        <v>4197</v>
       </c>
       <c r="G65" s="13" t="n">
         <v>0.9</v>
@@ -4106,6 +4749,16 @@
       <c r="K65" s="12">
         <f>K64+F65</f>
         <v/>
+      </c>
+      <c r="L65" s="10" t="inlineStr">
+        <is>
+          <t>MT5</t>
+        </is>
+      </c>
+      <c r="M65" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="66">
@@ -4119,22 +4772,22 @@
       </c>
       <c r="C66" s="10" t="inlineStr">
         <is>
-          <t>AI Prop</t>
+          <t>Clarity Traders</t>
         </is>
       </c>
       <c r="D66" s="10" t="inlineStr">
         <is>
-          <t>1 étape</t>
+          <t>2 étapes</t>
         </is>
       </c>
       <c r="E66" s="12" t="n">
-        <v>200000</v>
+        <v>300000</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>1976</v>
+        <v>1399</v>
       </c>
       <c r="G66" s="13" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="H66" s="12">
         <f>E66*G66</f>
@@ -4151,6 +4804,16 @@
       <c r="K66" s="12">
         <f>K65+F66</f>
         <v/>
+      </c>
+      <c r="L66" s="10" t="inlineStr">
+        <is>
+          <t>MetaTrader 5, TradeLocker</t>
+        </is>
+      </c>
+      <c r="M66" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="67">
@@ -4164,22 +4827,22 @@
       </c>
       <c r="C67" s="10" t="inlineStr">
         <is>
-          <t>HyperScaled</t>
+          <t>ArroxFund</t>
         </is>
       </c>
       <c r="D67" s="10" t="inlineStr">
         <is>
-          <t>1 étape</t>
+          <t>2 étapes</t>
         </is>
       </c>
       <c r="E67" s="12" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="F67" s="12" t="n">
-        <v>999</v>
+        <v>708</v>
       </c>
       <c r="G67" s="13" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="H67" s="12">
         <f>E67*G67</f>
@@ -4196,6 +4859,16 @@
       <c r="K67" s="12">
         <f>K66+F67</f>
         <v/>
+      </c>
+      <c r="L67" s="10" t="inlineStr">
+        <is>
+          <t>cTrader, Match-Trader</t>
+        </is>
+      </c>
+      <c r="M67" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="68">
@@ -4209,22 +4882,22 @@
       </c>
       <c r="C68" s="10" t="inlineStr">
         <is>
-          <t>FX Trader's EDGE</t>
+          <t>BrightFunded</t>
         </is>
       </c>
       <c r="D68" s="10" t="inlineStr">
         <is>
-          <t>1 étape</t>
+          <t>2 étapes</t>
         </is>
       </c>
       <c r="E68" s="12" t="n">
-        <v>925000</v>
+        <v>400000</v>
       </c>
       <c r="F68" s="12" t="n">
-        <v>9250</v>
+        <v>1894</v>
       </c>
       <c r="G68" s="13" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="H68" s="12">
         <f>E68*G68</f>
@@ -4241,6 +4914,16 @@
       <c r="K68" s="12">
         <f>K67+F68</f>
         <v/>
+      </c>
+      <c r="L68" s="10" t="inlineStr">
+        <is>
+          <t>cTrader, DXtrade</t>
+        </is>
+      </c>
+      <c r="M68" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="69">
@@ -4254,22 +4937,22 @@
       </c>
       <c r="C69" s="10" t="inlineStr">
         <is>
-          <t>BloomFunded</t>
+          <t>NEOM Funded</t>
         </is>
       </c>
       <c r="D69" s="10" t="inlineStr">
         <is>
-          <t>1 étape</t>
+          <t>2 étapes</t>
         </is>
       </c>
       <c r="E69" s="12" t="n">
-        <v>50000</v>
+        <v>400000</v>
       </c>
       <c r="F69" s="12" t="n">
-        <v>580</v>
+        <v>1940</v>
       </c>
       <c r="G69" s="13" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H69" s="12">
         <f>E69*G69</f>
@@ -4286,6 +4969,16 @@
       <c r="K69" s="12">
         <f>K68+F69</f>
         <v/>
+      </c>
+      <c r="L69" s="10" t="inlineStr">
+        <is>
+          <t>MetaTrader 5</t>
+        </is>
+      </c>
+      <c r="M69" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="70">
@@ -4299,22 +4992,22 @@
       </c>
       <c r="C70" s="10" t="inlineStr">
         <is>
-          <t>FundedWealth</t>
+          <t>NYS Markets</t>
         </is>
       </c>
       <c r="D70" s="10" t="inlineStr">
         <is>
-          <t>1 étape</t>
+          <t>2 étapes</t>
         </is>
       </c>
       <c r="E70" s="12" t="n">
-        <v>2500000</v>
+        <v>400000</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>48499</v>
+        <v>1974</v>
       </c>
       <c r="G70" s="13" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H70" s="12">
         <f>E70*G70</f>
@@ -4331,6 +5024,16 @@
       <c r="K70" s="12">
         <f>K69+F70</f>
         <v/>
+      </c>
+      <c r="L70" s="10" t="inlineStr">
+        <is>
+          <t>MetaTrader 5, Quantower, TradingView</t>
+        </is>
+      </c>
+      <c r="M70" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="71">
@@ -4344,22 +5047,22 @@
       </c>
       <c r="C71" s="10" t="inlineStr">
         <is>
-          <t>Ment Funding</t>
+          <t>Sway Funded</t>
         </is>
       </c>
       <c r="D71" s="10" t="inlineStr">
         <is>
-          <t>1 étape</t>
+          <t>2 étapes</t>
         </is>
       </c>
       <c r="E71" s="12" t="n">
-        <v>190000</v>
+        <v>1000000</v>
       </c>
       <c r="F71" s="12" t="n">
-        <v>7451</v>
+        <v>4945</v>
       </c>
       <c r="G71" s="13" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H71" s="12">
         <f>E71*G71</f>
@@ -4376,6 +5079,16 @@
       <c r="K71" s="12">
         <f>K70+F71</f>
         <v/>
+      </c>
+      <c r="L71" s="10" t="inlineStr">
+        <is>
+          <t>cTrader</t>
+        </is>
+      </c>
+      <c r="M71" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="72">
@@ -4389,7 +5102,7 @@
       </c>
       <c r="C72" s="10" t="inlineStr">
         <is>
-          <t>HUMBPROP</t>
+          <t>Exclusive Funded Programme</t>
         </is>
       </c>
       <c r="D72" s="10" t="inlineStr">
@@ -4398,13 +5111,13 @@
         </is>
       </c>
       <c r="E72" s="12" t="n">
-        <v>100000</v>
+        <v>300000</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>239</v>
+        <v>1497</v>
       </c>
       <c r="G72" s="13" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="H72" s="12">
         <f>E72*G72</f>
@@ -4421,6 +5134,16 @@
       <c r="K72" s="12">
         <f>K71+F72</f>
         <v/>
+      </c>
+      <c r="L72" s="10" t="inlineStr">
+        <is>
+          <t>MetaTrader 5</t>
+        </is>
+      </c>
+      <c r="M72" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="73">
@@ -4434,7 +5157,7 @@
       </c>
       <c r="C73" s="10" t="inlineStr">
         <is>
-          <t>FundedCobra</t>
+          <t>Quant Funded</t>
         </is>
       </c>
       <c r="D73" s="10" t="inlineStr">
@@ -4443,13 +5166,13 @@
         </is>
       </c>
       <c r="E73" s="12" t="n">
-        <v>200000</v>
+        <v>400000</v>
       </c>
       <c r="F73" s="12" t="n">
-        <v>594</v>
+        <v>1996</v>
       </c>
       <c r="G73" s="13" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="H73" s="12">
         <f>E73*G73</f>
@@ -4466,6 +5189,16 @@
       <c r="K73" s="12">
         <f>K72+F73</f>
         <v/>
+      </c>
+      <c r="L73" s="10" t="inlineStr">
+        <is>
+          <t>MetaTrader 5</t>
+        </is>
+      </c>
+      <c r="M73" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="74">
@@ -4479,7 +5212,7 @@
       </c>
       <c r="C74" s="10" t="inlineStr">
         <is>
-          <t>The Proven Trader</t>
+          <t>IC Funded</t>
         </is>
       </c>
       <c r="D74" s="10" t="inlineStr">
@@ -4488,10 +5221,10 @@
         </is>
       </c>
       <c r="E74" s="12" t="n">
-        <v>1000000</v>
+        <v>500000</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>3000</v>
+        <v>2495</v>
       </c>
       <c r="G74" s="13" t="n">
         <v>0.9</v>
@@ -4511,6 +5244,16 @@
       <c r="K74" s="12">
         <f>K73+F74</f>
         <v/>
+      </c>
+      <c r="L74" s="10" t="inlineStr">
+        <is>
+          <t>MetaTrader 5, cTrader</t>
+        </is>
+      </c>
+      <c r="M74" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="75">
@@ -4524,7 +5267,7 @@
       </c>
       <c r="C75" s="10" t="inlineStr">
         <is>
-          <t>Core Funded</t>
+          <t>Exclusive Markets Prop</t>
         </is>
       </c>
       <c r="D75" s="10" t="inlineStr">
@@ -4533,13 +5276,13 @@
         </is>
       </c>
       <c r="E75" s="12" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="F75" s="12" t="n">
-        <v>1695</v>
+        <v>1497</v>
       </c>
       <c r="G75" s="13" t="n">
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
       <c r="H75" s="12">
         <f>E75*G75</f>
@@ -4556,6 +5299,16 @@
       <c r="K75" s="12">
         <f>K74+F75</f>
         <v/>
+      </c>
+      <c r="L75" s="10" t="inlineStr">
+        <is>
+          <t>MetaTrader 5</t>
+        </is>
+      </c>
+      <c r="M75" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="76">
@@ -4569,7 +5322,7 @@
       </c>
       <c r="C76" s="10" t="inlineStr">
         <is>
-          <t>FundingRock</t>
+          <t>Bold Fund</t>
         </is>
       </c>
       <c r="D76" s="10" t="inlineStr">
@@ -4578,13 +5331,13 @@
         </is>
       </c>
       <c r="E76" s="12" t="n">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>700</v>
+        <v>499</v>
       </c>
       <c r="G76" s="13" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="H76" s="12">
         <f>E76*G76</f>
@@ -4601,6 +5354,16 @@
       <c r="K76" s="12">
         <f>K75+F76</f>
         <v/>
+      </c>
+      <c r="L76" s="10" t="inlineStr">
+        <is>
+          <t>TradeLocker</t>
+        </is>
+      </c>
+      <c r="M76" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="77">
@@ -4614,7 +5377,7 @@
       </c>
       <c r="C77" s="10" t="inlineStr">
         <is>
-          <t>BullRush</t>
+          <t>TTT Markets</t>
         </is>
       </c>
       <c r="D77" s="10" t="inlineStr">
@@ -4623,10 +5386,10 @@
         </is>
       </c>
       <c r="E77" s="12" t="n">
-        <v>200000</v>
+        <v>600000</v>
       </c>
       <c r="F77" s="12" t="n">
-        <v>718</v>
+        <v>2994</v>
       </c>
       <c r="G77" s="13" t="n">
         <v>0.9</v>
@@ -4646,6 +5409,16 @@
       <c r="K77" s="12">
         <f>K76+F77</f>
         <v/>
+      </c>
+      <c r="L77" s="10" t="inlineStr">
+        <is>
+          <t>MetaTrader 5</t>
+        </is>
+      </c>
+      <c r="M77" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="78">
@@ -4659,7 +5432,7 @@
       </c>
       <c r="C78" s="10" t="inlineStr">
         <is>
-          <t>Zeno Traders</t>
+          <t>Instant Funding Pakistan</t>
         </is>
       </c>
       <c r="D78" s="10" t="inlineStr">
@@ -4668,13 +5441,13 @@
         </is>
       </c>
       <c r="E78" s="12" t="n">
-        <v>200000</v>
+        <v>1000000</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>749</v>
+        <v>4990</v>
       </c>
       <c r="G78" s="13" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H78" s="12">
         <f>E78*G78</f>
@@ -4691,6 +5464,16 @@
       <c r="K78" s="12">
         <f>K77+F78</f>
         <v/>
+      </c>
+      <c r="L78" s="10" t="inlineStr">
+        <is>
+          <t>cTrader, Match-Trader</t>
+        </is>
+      </c>
+      <c r="M78" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="79">
@@ -4704,7 +5487,7 @@
       </c>
       <c r="C79" s="10" t="inlineStr">
         <is>
-          <t>MFunded</t>
+          <t>Vertex Funding</t>
         </is>
       </c>
       <c r="D79" s="10" t="inlineStr">
@@ -4713,13 +5496,13 @@
         </is>
       </c>
       <c r="E79" s="12" t="n">
-        <v>100000</v>
+        <v>500000</v>
       </c>
       <c r="F79" s="12" t="n">
-        <v>399</v>
+        <v>2525</v>
       </c>
       <c r="G79" s="13" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H79" s="12">
         <f>E79*G79</f>
@@ -4736,6 +5519,16 @@
       <c r="K79" s="12">
         <f>K78+F79</f>
         <v/>
+      </c>
+      <c r="L79" s="10" t="inlineStr">
+        <is>
+          <t>cTrader, Match-Trader, DXtrade</t>
+        </is>
+      </c>
+      <c r="M79" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="80">
@@ -4749,7 +5542,7 @@
       </c>
       <c r="C80" s="10" t="inlineStr">
         <is>
-          <t>T4TCapital</t>
+          <t>Cyber Funded</t>
         </is>
       </c>
       <c r="D80" s="10" t="inlineStr">
@@ -4761,7 +5554,7 @@
         <v>200000</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>800</v>
+        <v>1038</v>
       </c>
       <c r="G80" s="13" t="n">
         <v>0.9</v>
@@ -4781,6 +5574,16 @@
       <c r="K80" s="12">
         <f>K79+F80</f>
         <v/>
+      </c>
+      <c r="L80" s="10" t="inlineStr">
+        <is>
+          <t>MetaTrader 5, cTrader, Match-Trader, Tra</t>
+        </is>
+      </c>
+      <c r="M80" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="81">
@@ -4794,7 +5597,7 @@
       </c>
       <c r="C81" s="10" t="inlineStr">
         <is>
-          <t>Quant Tekel (QT | FUNDED)</t>
+          <t>Audacity Capital</t>
         </is>
       </c>
       <c r="D81" s="10" t="inlineStr">
@@ -4803,13 +5606,13 @@
         </is>
       </c>
       <c r="E81" s="12" t="n">
-        <v>300000</v>
+        <v>400000</v>
       </c>
       <c r="F81" s="12" t="n">
-        <v>1260</v>
+        <v>2098</v>
       </c>
       <c r="G81" s="13" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H81" s="12">
         <f>E81*G81</f>
@@ -4826,6 +5629,16 @@
       <c r="K81" s="12">
         <f>K80+F81</f>
         <v/>
+      </c>
+      <c r="L81" s="10" t="inlineStr">
+        <is>
+          <t>MetaTrader 5, DXtrade</t>
+        </is>
+      </c>
+      <c r="M81" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="82">
@@ -4839,7 +5652,7 @@
       </c>
       <c r="C82" s="10" t="inlineStr">
         <is>
-          <t>TrioFunded</t>
+          <t>FNC Funding</t>
         </is>
       </c>
       <c r="D82" s="10" t="inlineStr">
@@ -4851,7 +5664,7 @@
         <v>500000</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>2104</v>
+        <v>2625</v>
       </c>
       <c r="G82" s="13" t="n">
         <v>0.9</v>
@@ -4871,6 +5684,16 @@
       <c r="K82" s="12">
         <f>K81+F82</f>
         <v/>
+      </c>
+      <c r="L82" s="10" t="inlineStr">
+        <is>
+          <t>cTrader, Match-Trader, DXtrade</t>
+        </is>
+      </c>
+      <c r="M82" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="83">
@@ -4884,7 +5707,7 @@
       </c>
       <c r="C83" s="10" t="inlineStr">
         <is>
-          <t>EverBlue Trader</t>
+          <t>thePropTrade</t>
         </is>
       </c>
       <c r="D83" s="10" t="inlineStr">
@@ -4896,10 +5719,10 @@
         <v>400000</v>
       </c>
       <c r="F83" s="12" t="n">
-        <v>1699</v>
+        <v>2116</v>
       </c>
       <c r="G83" s="13" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H83" s="12">
         <f>E83*G83</f>
@@ -4916,6 +5739,16 @@
       <c r="K83" s="12">
         <f>K82+F83</f>
         <v/>
+      </c>
+      <c r="L83" s="10" t="inlineStr">
+        <is>
+          <t>cTrader, TradeLocker, Rithmic</t>
+        </is>
+      </c>
+      <c r="M83" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="84">
@@ -4929,7 +5762,7 @@
       </c>
       <c r="C84" s="10" t="inlineStr">
         <is>
-          <t>Mainet Funded</t>
+          <t>LegionFunding</t>
         </is>
       </c>
       <c r="D84" s="10" t="inlineStr">
@@ -4938,13 +5771,13 @@
         </is>
       </c>
       <c r="E84" s="12" t="n">
-        <v>700000</v>
+        <v>400000</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>2975</v>
+        <v>2116</v>
       </c>
       <c r="G84" s="13" t="n">
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
       <c r="H84" s="12">
         <f>E84*G84</f>
@@ -4961,6 +5794,16 @@
       <c r="K84" s="12">
         <f>K83+F84</f>
         <v/>
+      </c>
+      <c r="L84" s="10" t="inlineStr">
+        <is>
+          <t>MetaTrader 5</t>
+        </is>
+      </c>
+      <c r="M84" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="85">
@@ -4974,7 +5817,7 @@
       </c>
       <c r="C85" s="10" t="inlineStr">
         <is>
-          <t>SFX Funded</t>
+          <t>Prop Number One</t>
         </is>
       </c>
       <c r="D85" s="10" t="inlineStr">
@@ -4983,10 +5826,10 @@
         </is>
       </c>
       <c r="E85" s="12" t="n">
-        <v>495000</v>
+        <v>300000</v>
       </c>
       <c r="F85" s="12" t="n">
-        <v>2125</v>
+        <v>1592</v>
       </c>
       <c r="G85" s="13" t="n">
         <v>1</v>
@@ -5006,6 +5849,16 @@
       <c r="K85" s="12">
         <f>K84+F85</f>
         <v/>
+      </c>
+      <c r="L85" s="10" t="inlineStr">
+        <is>
+          <t>MetaTrader 5, cTrader, Match-Trader, Tra</t>
+        </is>
+      </c>
+      <c r="M85" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="86">
@@ -5019,7 +5872,7 @@
       </c>
       <c r="C86" s="10" t="inlineStr">
         <is>
-          <t>Ultimate Traders</t>
+          <t>MasterFunders</t>
         </is>
       </c>
       <c r="D86" s="10" t="inlineStr">
@@ -5028,13 +5881,13 @@
         </is>
       </c>
       <c r="E86" s="12" t="n">
-        <v>400000</v>
+        <v>100000</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v>1798</v>
+        <v>549</v>
       </c>
       <c r="G86" s="13" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="H86" s="12">
         <f>E86*G86</f>
@@ -5051,6 +5904,16 @@
       <c r="K86" s="12">
         <f>K85+F86</f>
         <v/>
+      </c>
+      <c r="L86" s="10" t="inlineStr">
+        <is>
+          <t>Match-Trader, TradingView</t>
+        </is>
+      </c>
+      <c r="M86" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="87">
@@ -5064,7 +5927,7 @@
       </c>
       <c r="C87" s="10" t="inlineStr">
         <is>
-          <t>TradersEdgeFX</t>
+          <t>WSFunded</t>
         </is>
       </c>
       <c r="D87" s="10" t="inlineStr">
@@ -5073,10 +5936,10 @@
         </is>
       </c>
       <c r="E87" s="12" t="n">
-        <v>200000</v>
+        <v>400000</v>
       </c>
       <c r="F87" s="12" t="n">
-        <v>899</v>
+        <v>2236</v>
       </c>
       <c r="G87" s="13" t="n">
         <v>0.8</v>
@@ -5096,6 +5959,16 @@
       <c r="K87" s="12">
         <f>K86+F87</f>
         <v/>
+      </c>
+      <c r="L87" s="10" t="inlineStr">
+        <is>
+          <t>MetaTrader 5, cTrader, Match-Trader</t>
+        </is>
+      </c>
+      <c r="M87" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="88">
@@ -5109,7 +5982,7 @@
       </c>
       <c r="C88" s="10" t="inlineStr">
         <is>
-          <t>Funded Roll</t>
+          <t>Prop Funders</t>
         </is>
       </c>
       <c r="D88" s="10" t="inlineStr">
@@ -5118,13 +5991,13 @@
         </is>
       </c>
       <c r="E88" s="12" t="n">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="F88" s="12" t="n">
-        <v>899</v>
+        <v>579</v>
       </c>
       <c r="G88" s="13" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="H88" s="12">
         <f>E88*G88</f>
@@ -5141,6 +6014,16 @@
       <c r="K88" s="12">
         <f>K87+F88</f>
         <v/>
+      </c>
+      <c r="L88" s="10" t="inlineStr">
+        <is>
+          <t>cTrader, Match-Trader, DXtrade</t>
+        </is>
+      </c>
+      <c r="M88" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="89">
@@ -5154,7 +6037,7 @@
       </c>
       <c r="C89" s="10" t="inlineStr">
         <is>
-          <t>NowTradeFunded</t>
+          <t>Tradeify Crypto</t>
         </is>
       </c>
       <c r="D89" s="10" t="inlineStr">
@@ -5163,13 +6046,13 @@
         </is>
       </c>
       <c r="E89" s="12" t="n">
-        <v>200000</v>
+        <v>300000</v>
       </c>
       <c r="F89" s="12" t="n">
-        <v>900</v>
+        <v>1740</v>
       </c>
       <c r="G89" s="13" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="H89" s="12">
         <f>E89*G89</f>
@@ -5186,6 +6069,16 @@
       <c r="K89" s="12">
         <f>K88+F89</f>
         <v/>
+      </c>
+      <c r="L89" s="10" t="inlineStr">
+        <is>
+          <t>MetaTrader 5, DXtrade</t>
+        </is>
+      </c>
+      <c r="M89" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="90">
@@ -5199,7 +6092,7 @@
       </c>
       <c r="C90" s="10" t="inlineStr">
         <is>
-          <t>OFunded</t>
+          <t>Tradeify 247</t>
         </is>
       </c>
       <c r="D90" s="10" t="inlineStr">
@@ -5208,13 +6101,13 @@
         </is>
       </c>
       <c r="E90" s="12" t="n">
-        <v>250000</v>
+        <v>300000</v>
       </c>
       <c r="F90" s="12" t="n">
-        <v>1125</v>
+        <v>1740</v>
       </c>
       <c r="G90" s="13" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="H90" s="12">
         <f>E90*G90</f>
@@ -5231,6 +6124,16 @@
       <c r="K90" s="12">
         <f>K89+F90</f>
         <v/>
+      </c>
+      <c r="L90" s="10" t="inlineStr">
+        <is>
+          <t>MetaTrader 5, DXtrade</t>
+        </is>
+      </c>
+      <c r="M90" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="91">
@@ -5244,7 +6147,7 @@
       </c>
       <c r="C91" s="10" t="inlineStr">
         <is>
-          <t>GoFunding</t>
+          <t>The Upside Funding</t>
         </is>
       </c>
       <c r="D91" s="10" t="inlineStr">
@@ -5253,13 +6156,13 @@
         </is>
       </c>
       <c r="E91" s="12" t="n">
-        <v>800000</v>
+        <v>100000</v>
       </c>
       <c r="F91" s="12" t="n">
-        <v>3600</v>
+        <v>589</v>
       </c>
       <c r="G91" s="13" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="H91" s="12">
         <f>E91*G91</f>
@@ -5276,6 +6179,16 @@
       <c r="K91" s="12">
         <f>K90+F91</f>
         <v/>
+      </c>
+      <c r="L91" s="10" t="inlineStr">
+        <is>
+          <t>MetaTrader 5</t>
+        </is>
+      </c>
+      <c r="M91" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="92">
@@ -5289,7 +6202,7 @@
       </c>
       <c r="C92" s="10" t="inlineStr">
         <is>
-          <t>Fill88</t>
+          <t>NextGen Funding</t>
         </is>
       </c>
       <c r="D92" s="10" t="inlineStr">
@@ -5298,10 +6211,10 @@
         </is>
       </c>
       <c r="E92" s="12" t="n">
-        <v>640000</v>
+        <v>200000</v>
       </c>
       <c r="F92" s="12" t="n">
-        <v>2885</v>
+        <v>1178</v>
       </c>
       <c r="G92" s="13" t="n">
         <v>0.9</v>
@@ -5321,6 +6234,16 @@
       <c r="K92" s="12">
         <f>K91+F92</f>
         <v/>
+      </c>
+      <c r="L92" s="10" t="inlineStr">
+        <is>
+          <t>MetaTrader 5, cTrader</t>
+        </is>
+      </c>
+      <c r="M92" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="93">
@@ -5334,7 +6257,7 @@
       </c>
       <c r="C93" s="10" t="inlineStr">
         <is>
-          <t>Pro Traders Fund</t>
+          <t>Eightcap Challenges</t>
         </is>
       </c>
       <c r="D93" s="10" t="inlineStr">
@@ -5343,13 +6266,13 @@
         </is>
       </c>
       <c r="E93" s="12" t="n">
-        <v>900000</v>
+        <v>600000</v>
       </c>
       <c r="F93" s="12" t="n">
-        <v>4197</v>
+        <v>3594</v>
       </c>
       <c r="G93" s="13" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H93" s="12">
         <f>E93*G93</f>
@@ -5366,6 +6289,16 @@
       <c r="K93" s="12">
         <f>K92+F93</f>
         <v/>
+      </c>
+      <c r="L93" s="10" t="inlineStr">
+        <is>
+          <t>MetaTrader 5, TradeLocker, TradingView</t>
+        </is>
+      </c>
+      <c r="M93" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="94">
@@ -5379,7 +6312,7 @@
       </c>
       <c r="C94" s="10" t="inlineStr">
         <is>
-          <t>Clarity Traders</t>
+          <t>PropFunding</t>
         </is>
       </c>
       <c r="D94" s="10" t="inlineStr">
@@ -5388,13 +6321,13 @@
         </is>
       </c>
       <c r="E94" s="12" t="n">
-        <v>300000</v>
+        <v>25000</v>
       </c>
       <c r="F94" s="12" t="n">
-        <v>1399</v>
+        <v>150</v>
       </c>
       <c r="G94" s="13" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="H94" s="12">
         <f>E94*G94</f>
@@ -5411,6 +6344,16 @@
       <c r="K94" s="12">
         <f>K93+F94</f>
         <v/>
+      </c>
+      <c r="L94" s="10" t="inlineStr">
+        <is>
+          <t>MetaTrader 5</t>
+        </is>
+      </c>
+      <c r="M94" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="95">
@@ -5424,7 +6367,7 @@
       </c>
       <c r="C95" s="10" t="inlineStr">
         <is>
-          <t>ArroxFund</t>
+          <t>Crypto Fund Trader</t>
         </is>
       </c>
       <c r="D95" s="10" t="inlineStr">
@@ -5433,10 +6376,10 @@
         </is>
       </c>
       <c r="E95" s="12" t="n">
-        <v>150000</v>
+        <v>200000</v>
       </c>
       <c r="F95" s="12" t="n">
-        <v>708</v>
+        <v>1250</v>
       </c>
       <c r="G95" s="13" t="n">
         <v>0.8</v>
@@ -5456,6 +6399,16 @@
       <c r="K95" s="12">
         <f>K94+F95</f>
         <v/>
+      </c>
+      <c r="L95" s="10" t="inlineStr">
+        <is>
+          <t>MetaTrader 5, Match-Trader</t>
+        </is>
+      </c>
+      <c r="M95" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="96">
@@ -5469,7 +6422,7 @@
       </c>
       <c r="C96" s="10" t="inlineStr">
         <is>
-          <t>BrightFunded</t>
+          <t>Myfundedcapital</t>
         </is>
       </c>
       <c r="D96" s="10" t="inlineStr">
@@ -5478,13 +6431,13 @@
         </is>
       </c>
       <c r="E96" s="12" t="n">
-        <v>400000</v>
+        <v>300000</v>
       </c>
       <c r="F96" s="12" t="n">
-        <v>1894</v>
+        <v>1905</v>
       </c>
       <c r="G96" s="13" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H96" s="12">
         <f>E96*G96</f>
@@ -5501,6 +6454,16 @@
       <c r="K96" s="12">
         <f>K95+F96</f>
         <v/>
+      </c>
+      <c r="L96" s="10" t="inlineStr">
+        <is>
+          <t>cTrader, Match-Trader, DXtrade</t>
+        </is>
+      </c>
+      <c r="M96" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="97">
@@ -5514,7 +6477,7 @@
       </c>
       <c r="C97" s="10" t="inlineStr">
         <is>
-          <t>Mubite</t>
+          <t>Key to Prop</t>
         </is>
       </c>
       <c r="D97" s="10" t="inlineStr">
@@ -5523,13 +6486,13 @@
         </is>
       </c>
       <c r="E97" s="12" t="n">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="F97" s="12" t="n">
-        <v>949</v>
+        <v>650</v>
       </c>
       <c r="G97" s="13" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H97" s="12">
         <f>E97*G97</f>
@@ -5546,6 +6509,16 @@
       <c r="K97" s="12">
         <f>K96+F97</f>
         <v/>
+      </c>
+      <c r="L97" s="10" t="inlineStr">
+        <is>
+          <t>MT5</t>
+        </is>
+      </c>
+      <c r="M97" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="98">
@@ -5559,7 +6532,7 @@
       </c>
       <c r="C98" s="10" t="inlineStr">
         <is>
-          <t>Seven Go Funding</t>
+          <t>Texaris</t>
         </is>
       </c>
       <c r="D98" s="10" t="inlineStr">
@@ -5568,10 +6541,10 @@
         </is>
       </c>
       <c r="E98" s="12" t="n">
-        <v>1000000</v>
+        <v>400000</v>
       </c>
       <c r="F98" s="12" t="n">
-        <v>4800</v>
+        <v>2796</v>
       </c>
       <c r="G98" s="13" t="n">
         <v>0.8</v>
@@ -5591,6 +6564,16 @@
       <c r="K98" s="12">
         <f>K97+F98</f>
         <v/>
+      </c>
+      <c r="L98" s="10" t="inlineStr">
+        <is>
+          <t>TradeLocker, TradingView</t>
+        </is>
+      </c>
+      <c r="M98" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="99">
@@ -5604,7 +6587,7 @@
       </c>
       <c r="C99" s="10" t="inlineStr">
         <is>
-          <t>Mockapital</t>
+          <t>Upcomers</t>
         </is>
       </c>
       <c r="D99" s="10" t="inlineStr">
@@ -5613,13 +6596,13 @@
         </is>
       </c>
       <c r="E99" s="12" t="n">
-        <v>300000</v>
+        <v>4000000</v>
       </c>
       <c r="F99" s="12" t="n">
-        <v>1450</v>
+        <v>30795</v>
       </c>
       <c r="G99" s="13" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="H99" s="12">
         <f>E99*G99</f>
@@ -5636,6 +6619,16 @@
       <c r="K99" s="12">
         <f>K98+F99</f>
         <v/>
+      </c>
+      <c r="L99" s="10" t="inlineStr">
+        <is>
+          <t>cTrader, Match-Trader, TradeLocker, DXtr</t>
+        </is>
+      </c>
+      <c r="M99" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="100">
@@ -5649,7 +6642,7 @@
       </c>
       <c r="C100" s="10" t="inlineStr">
         <is>
-          <t>NeomAAA Funds (NEOM Funded)</t>
+          <t>Finotive Funding</t>
         </is>
       </c>
       <c r="D100" s="10" t="inlineStr">
@@ -5658,13 +6651,13 @@
         </is>
       </c>
       <c r="E100" s="12" t="n">
-        <v>400000</v>
+        <v>1400000</v>
       </c>
       <c r="F100" s="12" t="n">
-        <v>1940</v>
+        <v>11200</v>
       </c>
       <c r="G100" s="13" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H100" s="12">
         <f>E100*G100</f>
@@ -5681,6 +6674,16 @@
       <c r="K100" s="12">
         <f>K99+F100</f>
         <v/>
+      </c>
+      <c r="L100" s="10" t="inlineStr">
+        <is>
+          <t>MetaTrader 5, Match-Trader</t>
+        </is>
+      </c>
+      <c r="M100" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="101">
@@ -5694,7 +6697,7 @@
       </c>
       <c r="C101" s="10" t="inlineStr">
         <is>
-          <t>NEOM Funded</t>
+          <t>Thetradercapital</t>
         </is>
       </c>
       <c r="D101" s="10" t="inlineStr">
@@ -5703,13 +6706,13 @@
         </is>
       </c>
       <c r="E101" s="12" t="n">
-        <v>400000</v>
+        <v>3000</v>
       </c>
       <c r="F101" s="12" t="n">
-        <v>1940</v>
+        <v>55</v>
       </c>
       <c r="G101" s="13" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="H101" s="12">
         <f>E101*G101</f>
@@ -5726,6 +6729,16 @@
       <c r="K101" s="12">
         <f>K100+F101</f>
         <v/>
+      </c>
+      <c r="L101" s="10" t="inlineStr">
+        <is>
+          <t>MT5</t>
+        </is>
+      </c>
+      <c r="M101" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="102">
@@ -5739,7 +6752,7 @@
       </c>
       <c r="C102" s="10" t="inlineStr">
         <is>
-          <t>Nordic Funder</t>
+          <t>NairaFunded</t>
         </is>
       </c>
       <c r="D102" s="10" t="inlineStr">
@@ -5748,13 +6761,13 @@
         </is>
       </c>
       <c r="E102" s="12" t="n">
-        <v>500000</v>
+        <v>1500000</v>
       </c>
       <c r="F102" s="12" t="n">
-        <v>2450</v>
+        <v>58000</v>
       </c>
       <c r="G102" s="13" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="H102" s="12">
         <f>E102*G102</f>
@@ -5771,6 +6784,16 @@
       <c r="K102" s="12">
         <f>K101+F102</f>
         <v/>
+      </c>
+      <c r="L102" s="10" t="inlineStr">
+        <is>
+          <t>MT5</t>
+        </is>
+      </c>
+      <c r="M102" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="103">
@@ -5784,7 +6807,7 @@
       </c>
       <c r="C103" s="10" t="inlineStr">
         <is>
-          <t>NYS Markets</t>
+          <t>NairaProp</t>
         </is>
       </c>
       <c r="D103" s="10" t="inlineStr">
@@ -5793,13 +6816,13 @@
         </is>
       </c>
       <c r="E103" s="12" t="n">
-        <v>400000</v>
+        <v>3000000</v>
       </c>
       <c r="F103" s="12" t="n">
-        <v>1974</v>
+        <v>135000</v>
       </c>
       <c r="G103" s="13" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="H103" s="12">
         <f>E103*G103</f>
@@ -5816,6 +6839,16 @@
       <c r="K103" s="12">
         <f>K102+F103</f>
         <v/>
+      </c>
+      <c r="L103" s="10" t="inlineStr">
+        <is>
+          <t>MT5</t>
+        </is>
+      </c>
+      <c r="M103" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="104">
@@ -5829,19 +6862,19 @@
       </c>
       <c r="C104" s="10" t="inlineStr">
         <is>
-          <t>Sway Funded</t>
+          <t>The5ers</t>
         </is>
       </c>
       <c r="D104" s="10" t="inlineStr">
         <is>
-          <t>2 étapes</t>
+          <t>3 étapes</t>
         </is>
       </c>
       <c r="E104" s="12" t="n">
-        <v>1000000</v>
+        <v>120000</v>
       </c>
       <c r="F104" s="12" t="n">
-        <v>4945</v>
+        <v>117</v>
       </c>
       <c r="G104" s="13" t="n">
         <v>1</v>
@@ -5861,6 +6894,16 @@
       <c r="K104" s="12">
         <f>K103+F104</f>
         <v/>
+      </c>
+      <c r="L104" s="10" t="inlineStr">
+        <is>
+          <t>MetaTrader 5</t>
+        </is>
+      </c>
+      <c r="M104" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="105">
@@ -5874,22 +6917,22 @@
       </c>
       <c r="C105" s="10" t="inlineStr">
         <is>
-          <t>Exclusive Funded Programme</t>
+          <t>The5ers Crypto</t>
         </is>
       </c>
       <c r="D105" s="10" t="inlineStr">
         <is>
-          <t>2 étapes</t>
+          <t>3 étapes</t>
         </is>
       </c>
       <c r="E105" s="12" t="n">
-        <v>300000</v>
+        <v>120000</v>
       </c>
       <c r="F105" s="12" t="n">
-        <v>1497</v>
+        <v>117</v>
       </c>
       <c r="G105" s="13" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="H105" s="12">
         <f>E105*G105</f>
@@ -5906,6 +6949,16 @@
       <c r="K105" s="12">
         <f>K104+F105</f>
         <v/>
+      </c>
+      <c r="L105" s="10" t="inlineStr">
+        <is>
+          <t>cTrader, TradingView</t>
+        </is>
+      </c>
+      <c r="M105" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="106">
@@ -5919,22 +6972,22 @@
       </c>
       <c r="C106" s="10" t="inlineStr">
         <is>
-          <t>Quant Funded</t>
+          <t>Htrader</t>
         </is>
       </c>
       <c r="D106" s="10" t="inlineStr">
         <is>
-          <t>2 étapes</t>
+          <t>3 étapes</t>
         </is>
       </c>
       <c r="E106" s="12" t="n">
-        <v>400000</v>
+        <v>300000</v>
       </c>
       <c r="F106" s="12" t="n">
-        <v>1996</v>
+        <v>798</v>
       </c>
       <c r="G106" s="13" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="H106" s="12">
         <f>E106*G106</f>
@@ -5951,6 +7004,16 @@
       <c r="K106" s="12">
         <f>K105+F106</f>
         <v/>
+      </c>
+      <c r="L106" s="10" t="inlineStr">
+        <is>
+          <t>MetaTrader 5</t>
+        </is>
+      </c>
+      <c r="M106" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="107">
@@ -5964,22 +7027,22 @@
       </c>
       <c r="C107" s="10" t="inlineStr">
         <is>
-          <t>IC Funded</t>
+          <t>Atlas Funded</t>
         </is>
       </c>
       <c r="D107" s="10" t="inlineStr">
         <is>
-          <t>2 étapes</t>
+          <t>3 étapes</t>
         </is>
       </c>
       <c r="E107" s="12" t="n">
-        <v>500000</v>
+        <v>400000</v>
       </c>
       <c r="F107" s="12" t="n">
-        <v>2495</v>
+        <v>1182</v>
       </c>
       <c r="G107" s="13" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H107" s="12">
         <f>E107*G107</f>
@@ -5996,6 +7059,16 @@
       <c r="K107" s="12">
         <f>K106+F107</f>
         <v/>
+      </c>
+      <c r="L107" s="10" t="inlineStr">
+        <is>
+          <t>MetaTrader 5, TradeLocker, Rithmic</t>
+        </is>
+      </c>
+      <c r="M107" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="108">
@@ -6009,19 +7082,19 @@
       </c>
       <c r="C108" s="10" t="inlineStr">
         <is>
-          <t>Exclusive Markets Prop</t>
+          <t>Get Leveraged</t>
         </is>
       </c>
       <c r="D108" s="10" t="inlineStr">
         <is>
-          <t>2 étapes</t>
+          <t>3 étapes</t>
         </is>
       </c>
       <c r="E108" s="12" t="n">
-        <v>300000</v>
+        <v>1000000</v>
       </c>
       <c r="F108" s="12" t="n">
-        <v>1497</v>
+        <v>2996</v>
       </c>
       <c r="G108" s="13" t="n">
         <v>0.8</v>
@@ -6041,6 +7114,16 @@
       <c r="K108" s="12">
         <f>K107+F108</f>
         <v/>
+      </c>
+      <c r="L108" s="10" t="inlineStr">
+        <is>
+          <t>cTrader</t>
+        </is>
+      </c>
+      <c r="M108" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="109">
@@ -6054,22 +7137,22 @@
       </c>
       <c r="C109" s="10" t="inlineStr">
         <is>
-          <t>Bold Fund</t>
+          <t>Leveraged</t>
         </is>
       </c>
       <c r="D109" s="10" t="inlineStr">
         <is>
-          <t>2 étapes</t>
+          <t>3 étapes</t>
         </is>
       </c>
       <c r="E109" s="12" t="n">
-        <v>100000</v>
+        <v>1000000</v>
       </c>
       <c r="F109" s="12" t="n">
-        <v>499</v>
+        <v>2996</v>
       </c>
       <c r="G109" s="13" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="H109" s="12">
         <f>E109*G109</f>
@@ -6086,6 +7169,16 @@
       <c r="K109" s="12">
         <f>K108+F109</f>
         <v/>
+      </c>
+      <c r="L109" s="10" t="inlineStr">
+        <is>
+          <t>MetaTrader 5, cTrader</t>
+        </is>
+      </c>
+      <c r="M109" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="110">
@@ -6099,22 +7192,22 @@
       </c>
       <c r="C110" s="10" t="inlineStr">
         <is>
-          <t>TTT Markets</t>
+          <t>AquaFunded</t>
         </is>
       </c>
       <c r="D110" s="10" t="inlineStr">
         <is>
-          <t>2 étapes</t>
+          <t>3 étapes</t>
         </is>
       </c>
       <c r="E110" s="12" t="n">
-        <v>600000</v>
+        <v>400000</v>
       </c>
       <c r="F110" s="12" t="n">
-        <v>2994</v>
+        <v>1354</v>
       </c>
       <c r="G110" s="13" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H110" s="12">
         <f>E110*G110</f>
@@ -6131,6 +7224,16 @@
       <c r="K110" s="12">
         <f>K109+F110</f>
         <v/>
+      </c>
+      <c r="L110" s="10" t="inlineStr">
+        <is>
+          <t>MetaTrader 5, cTrader, TradeLocker, Rith</t>
+        </is>
+      </c>
+      <c r="M110" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="111">
@@ -6144,19 +7247,19 @@
       </c>
       <c r="C111" s="10" t="inlineStr">
         <is>
-          <t>Instant Funding Pakistan</t>
+          <t>Blink Funding</t>
         </is>
       </c>
       <c r="D111" s="10" t="inlineStr">
         <is>
-          <t>2 étapes</t>
+          <t>3 étapes</t>
         </is>
       </c>
       <c r="E111" s="12" t="n">
-        <v>1000000</v>
+        <v>500000</v>
       </c>
       <c r="F111" s="12" t="n">
-        <v>4990</v>
+        <v>1800</v>
       </c>
       <c r="G111" s="13" t="n">
         <v>0.9</v>
@@ -6176,6 +7279,16 @@
       <c r="K111" s="12">
         <f>K110+F111</f>
         <v/>
+      </c>
+      <c r="L111" s="10" t="inlineStr">
+        <is>
+          <t>cTrader, Match-Trader, DXtrade</t>
+        </is>
+      </c>
+      <c r="M111" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="112">
@@ -6189,19 +7302,19 @@
       </c>
       <c r="C112" s="10" t="inlineStr">
         <is>
-          <t>Super Funded</t>
+          <t>Orion Funded</t>
         </is>
       </c>
       <c r="D112" s="10" t="inlineStr">
         <is>
-          <t>2 étapes</t>
+          <t>3 étapes</t>
         </is>
       </c>
       <c r="E112" s="12" t="n">
-        <v>200000</v>
+        <v>400000</v>
       </c>
       <c r="F112" s="12" t="n">
-        <v>999</v>
+        <v>1478</v>
       </c>
       <c r="G112" s="13" t="n">
         <v>0.9</v>
@@ -6221,6 +7334,16 @@
       <c r="K112" s="12">
         <f>K111+F112</f>
         <v/>
+      </c>
+      <c r="L112" s="10" t="inlineStr">
+        <is>
+          <t>cTrader, Match-Trader</t>
+        </is>
+      </c>
+      <c r="M112" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="113">
@@ -6234,22 +7357,22 @@
       </c>
       <c r="C113" s="10" t="inlineStr">
         <is>
-          <t>The Nomad Trader</t>
+          <t>Monevis</t>
         </is>
       </c>
       <c r="D113" s="10" t="inlineStr">
         <is>
-          <t>2 étapes</t>
+          <t>3 étapes</t>
         </is>
       </c>
       <c r="E113" s="12" t="n">
-        <v>400000</v>
+        <v>200000</v>
       </c>
       <c r="F113" s="12" t="n">
-        <v>2000</v>
+        <v>770</v>
       </c>
       <c r="G113" s="13" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="H113" s="12">
         <f>E113*G113</f>
@@ -6266,6 +7389,16 @@
       <c r="K113" s="12">
         <f>K112+F113</f>
         <v/>
+      </c>
+      <c r="L113" s="10" t="inlineStr">
+        <is>
+          <t>MT5</t>
+        </is>
+      </c>
+      <c r="M113" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="114">
@@ -6279,22 +7412,22 @@
       </c>
       <c r="C114" s="10" t="inlineStr">
         <is>
-          <t>Investiqa</t>
+          <t>Get Crypto Funded</t>
         </is>
       </c>
       <c r="D114" s="10" t="inlineStr">
         <is>
-          <t>2 étapes</t>
+          <t>3 étapes</t>
         </is>
       </c>
       <c r="E114" s="12" t="n">
-        <v>1000000</v>
+        <v>400000</v>
       </c>
       <c r="F114" s="12" t="n">
-        <v>5040</v>
+        <v>1648</v>
       </c>
       <c r="G114" s="13" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="H114" s="12">
         <f>E114*G114</f>
@@ -6311,6 +7444,16 @@
       <c r="K114" s="12">
         <f>K113+F114</f>
         <v/>
+      </c>
+      <c r="L114" s="10" t="inlineStr">
+        <is>
+          <t>MetaTrader 5, cTrader, Match-Trader</t>
+        </is>
+      </c>
+      <c r="M114" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="115">
@@ -6324,22 +7467,22 @@
       </c>
       <c r="C115" s="10" t="inlineStr">
         <is>
-          <t>Vertex Funding</t>
+          <t>Fintokei</t>
         </is>
       </c>
       <c r="D115" s="10" t="inlineStr">
         <is>
-          <t>2 étapes</t>
+          <t>3 étapes</t>
         </is>
       </c>
       <c r="E115" s="12" t="n">
-        <v>500000</v>
+        <v>700000</v>
       </c>
       <c r="F115" s="12" t="n">
-        <v>2525</v>
+        <v>2933</v>
       </c>
       <c r="G115" s="13" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H115" s="12">
         <f>E115*G115</f>
@@ -6356,6 +7499,16 @@
       <c r="K115" s="12">
         <f>K114+F115</f>
         <v/>
+      </c>
+      <c r="L115" s="10" t="inlineStr">
+        <is>
+          <t>MetaTrader 5, cTrader, TradingView</t>
+        </is>
+      </c>
+      <c r="M115" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="116">
@@ -6369,22 +7522,22 @@
       </c>
       <c r="C116" s="10" t="inlineStr">
         <is>
-          <t>Cyber Funded</t>
+          <t>FundedHive</t>
         </is>
       </c>
       <c r="D116" s="10" t="inlineStr">
         <is>
-          <t>2 étapes</t>
+          <t>Instant</t>
         </is>
       </c>
       <c r="E116" s="12" t="n">
-        <v>200000</v>
+        <v>1000000</v>
       </c>
       <c r="F116" s="12" t="n">
-        <v>1038</v>
+        <v>349</v>
       </c>
       <c r="G116" s="13" t="n">
-        <v>0.9</v>
+        <v>0.99</v>
       </c>
       <c r="H116" s="12">
         <f>E116*G116</f>
@@ -6401,6 +7554,16 @@
       <c r="K116" s="12">
         <f>K115+F116</f>
         <v/>
+      </c>
+      <c r="L116" s="10" t="inlineStr">
+        <is>
+          <t>cTrader</t>
+        </is>
+      </c>
+      <c r="M116" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="117">
@@ -6414,22 +7577,22 @@
       </c>
       <c r="C117" s="10" t="inlineStr">
         <is>
-          <t>Audacity Capital</t>
+          <t>Audacity Capital (FTP Instant Funding)</t>
         </is>
       </c>
       <c r="D117" s="10" t="inlineStr">
         <is>
-          <t>2 étapes</t>
+          <t>Instant</t>
         </is>
       </c>
       <c r="E117" s="12" t="n">
-        <v>400000</v>
+        <v>240000</v>
       </c>
       <c r="F117" s="12" t="n">
-        <v>2098</v>
+        <v>1365</v>
       </c>
       <c r="G117" s="13" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="H117" s="12">
         <f>E117*G117</f>
@@ -6446,6 +7609,16 @@
       <c r="K117" s="12">
         <f>K116+F117</f>
         <v/>
+      </c>
+      <c r="L117" s="10" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="M117" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="118">
@@ -6459,19 +7632,19 @@
       </c>
       <c r="C118" s="10" t="inlineStr">
         <is>
-          <t>FNC Funding</t>
+          <t>FundedForge</t>
         </is>
       </c>
       <c r="D118" s="10" t="inlineStr">
         <is>
-          <t>2 étapes</t>
+          <t>Instant</t>
         </is>
       </c>
       <c r="E118" s="12" t="n">
-        <v>500000</v>
+        <v>100000</v>
       </c>
       <c r="F118" s="12" t="n">
-        <v>2625</v>
+        <v>650</v>
       </c>
       <c r="G118" s="13" t="n">
         <v>0.9</v>
@@ -6491,6 +7664,16 @@
       <c r="K118" s="12">
         <f>K117+F118</f>
         <v/>
+      </c>
+      <c r="L118" s="10" t="inlineStr">
+        <is>
+          <t>cTrader, Match-Trader, DXtrade</t>
+        </is>
+      </c>
+      <c r="M118" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="119">
@@ -6504,22 +7687,22 @@
       </c>
       <c r="C119" s="10" t="inlineStr">
         <is>
-          <t>thePropTrade</t>
+          <t>BuoyTrade</t>
         </is>
       </c>
       <c r="D119" s="10" t="inlineStr">
         <is>
-          <t>2 étapes</t>
+          <t>Instant</t>
         </is>
       </c>
       <c r="E119" s="12" t="n">
-        <v>400000</v>
+        <v>40000</v>
       </c>
       <c r="F119" s="12" t="n">
-        <v>2116</v>
+        <v>1980</v>
       </c>
       <c r="G119" s="13" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="H119" s="12">
         <f>E119*G119</f>
@@ -6536,6 +7719,16 @@
       <c r="K119" s="12">
         <f>K118+F119</f>
         <v/>
+      </c>
+      <c r="L119" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MetaTrader </t>
+        </is>
+      </c>
+      <c r="M119" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="120">
@@ -6549,22 +7742,22 @@
       </c>
       <c r="C120" s="10" t="inlineStr">
         <is>
-          <t>LegionFunding</t>
+          <t>PipFarm</t>
         </is>
       </c>
       <c r="D120" s="10" t="inlineStr">
         <is>
-          <t>2 étapes</t>
+          <t>1 étape</t>
         </is>
       </c>
       <c r="E120" s="12" t="n">
-        <v>400000</v>
+        <v>600000</v>
       </c>
       <c r="F120" s="12" t="n">
-        <v>2116</v>
+        <v>2360</v>
       </c>
       <c r="G120" s="13" t="n">
-        <v>0.8</v>
+        <v>0.99</v>
       </c>
       <c r="H120" s="12">
         <f>E120*G120</f>
@@ -6581,6 +7774,16 @@
       <c r="K120" s="12">
         <f>K119+F120</f>
         <v/>
+      </c>
+      <c r="L120" s="10" t="inlineStr">
+        <is>
+          <t>cTrader</t>
+        </is>
+      </c>
+      <c r="M120" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="121">
@@ -6594,22 +7797,22 @@
       </c>
       <c r="C121" s="10" t="inlineStr">
         <is>
-          <t>Prop Number One</t>
+          <t>Vanta Trading</t>
         </is>
       </c>
       <c r="D121" s="10" t="inlineStr">
         <is>
-          <t>2 étapes</t>
+          <t>1 étape</t>
         </is>
       </c>
       <c r="E121" s="12" t="n">
-        <v>300000</v>
+        <v>125000</v>
       </c>
       <c r="F121" s="12" t="n">
-        <v>1592</v>
+        <v>498</v>
       </c>
       <c r="G121" s="13" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="H121" s="12">
         <f>E121*G121</f>
@@ -6626,6 +7829,16 @@
       <c r="K121" s="12">
         <f>K120+F121</f>
         <v/>
+      </c>
+      <c r="L121" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vanta Trading Desk </t>
+        </is>
+      </c>
+      <c r="M121" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="122">
@@ -6639,22 +7852,22 @@
       </c>
       <c r="C122" s="10" t="inlineStr">
         <is>
-          <t>MasterFunders</t>
+          <t>FundedFX</t>
         </is>
       </c>
       <c r="D122" s="10" t="inlineStr">
         <is>
-          <t>2 étapes</t>
+          <t>1 étape</t>
         </is>
       </c>
       <c r="E122" s="12" t="n">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="F122" s="12" t="n">
-        <v>549</v>
+        <v>900</v>
       </c>
       <c r="G122" s="13" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H122" s="12">
         <f>E122*G122</f>
@@ -6671,6 +7884,16 @@
       <c r="K122" s="12">
         <f>K121+F122</f>
         <v/>
+      </c>
+      <c r="L122" s="10" t="inlineStr">
+        <is>
+          <t>Match Trader only</t>
+        </is>
+      </c>
+      <c r="M122" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="123">
@@ -6684,22 +7907,22 @@
       </c>
       <c r="C123" s="10" t="inlineStr">
         <is>
-          <t>WSFunded</t>
+          <t>Pipster</t>
         </is>
       </c>
       <c r="D123" s="10" t="inlineStr">
         <is>
-          <t>2 étapes</t>
+          <t>1 étape</t>
         </is>
       </c>
       <c r="E123" s="12" t="n">
-        <v>400000</v>
+        <v>200000</v>
       </c>
       <c r="F123" s="12" t="n">
-        <v>2236</v>
+        <v>958</v>
       </c>
       <c r="G123" s="13" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H123" s="12">
         <f>E123*G123</f>
@@ -6716,6 +7939,16 @@
       <c r="K123" s="12">
         <f>K122+F123</f>
         <v/>
+      </c>
+      <c r="L123" s="10" t="inlineStr">
+        <is>
+          <t>Match-Trader</t>
+        </is>
+      </c>
+      <c r="M123" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="124">
@@ -6729,22 +7962,22 @@
       </c>
       <c r="C124" s="10" t="inlineStr">
         <is>
-          <t>FT9JA</t>
+          <t>Perps Fund</t>
         </is>
       </c>
       <c r="D124" s="10" t="inlineStr">
         <is>
-          <t>2 étapes</t>
+          <t>1 étape</t>
         </is>
       </c>
       <c r="E124" s="12" t="n">
-        <v>25000</v>
+        <v>5000</v>
       </c>
       <c r="F124" s="12" t="n">
-        <v>141</v>
+        <v>25</v>
       </c>
       <c r="G124" s="13" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="H124" s="12">
         <f>E124*G124</f>
@@ -6761,6 +7994,16 @@
       <c r="K124" s="12">
         <f>K123+F124</f>
         <v/>
+      </c>
+      <c r="L124" s="10" t="inlineStr">
+        <is>
+          <t>Proprietary terminal + REST API</t>
+        </is>
+      </c>
+      <c r="M124" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="125">
@@ -6774,22 +8017,22 @@
       </c>
       <c r="C125" s="10" t="inlineStr">
         <is>
-          <t>Prop Funders</t>
+          <t>Kickstart Trading</t>
         </is>
       </c>
       <c r="D125" s="10" t="inlineStr">
         <is>
-          <t>2 étapes</t>
+          <t>1 étape</t>
         </is>
       </c>
       <c r="E125" s="12" t="n">
-        <v>100000</v>
+        <v>1000000</v>
       </c>
       <c r="F125" s="12" t="n">
-        <v>579</v>
+        <v>6500</v>
       </c>
       <c r="G125" s="13" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="H125" s="12">
         <f>E125*G125</f>
@@ -6806,6 +8049,16 @@
       <c r="K125" s="12">
         <f>K124+F125</f>
         <v/>
+      </c>
+      <c r="L125" s="10" t="inlineStr">
+        <is>
+          <t>cTrader, DXtrade, Rithmic, Volumetrica</t>
+        </is>
+      </c>
+      <c r="M125" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="126">
@@ -6819,22 +8072,22 @@
       </c>
       <c r="C126" s="10" t="inlineStr">
         <is>
-          <t>Tradeify Crypto</t>
+          <t>Get Funded Now</t>
         </is>
       </c>
       <c r="D126" s="10" t="inlineStr">
         <is>
-          <t>2 étapes</t>
+          <t>1 étape</t>
         </is>
       </c>
       <c r="E126" s="12" t="n">
-        <v>300000</v>
+        <v>400000</v>
       </c>
       <c r="F126" s="12" t="n">
-        <v>1740</v>
+        <v>2625</v>
       </c>
       <c r="G126" s="13" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="H126" s="12">
         <f>E126*G126</f>
@@ -6851,6 +8104,16 @@
       <c r="K126" s="12">
         <f>K125+F126</f>
         <v/>
+      </c>
+      <c r="L126" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not named on the official site </t>
+        </is>
+      </c>
+      <c r="M126" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="127">
@@ -6864,22 +8127,22 @@
       </c>
       <c r="C127" s="10" t="inlineStr">
         <is>
-          <t>Tradeify 247</t>
+          <t>Propr</t>
         </is>
       </c>
       <c r="D127" s="10" t="inlineStr">
         <is>
-          <t>2 étapes</t>
+          <t>1 étape</t>
         </is>
       </c>
       <c r="E127" s="12" t="n">
         <v>300000</v>
       </c>
       <c r="F127" s="12" t="n">
-        <v>1740</v>
+        <v>2097</v>
       </c>
       <c r="G127" s="13" t="n">
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
       <c r="H127" s="12">
         <f>E127*G127</f>
@@ -6896,6 +8159,16 @@
       <c r="K127" s="12">
         <f>K126+F127</f>
         <v/>
+      </c>
+      <c r="L127" s="10" t="inlineStr">
+        <is>
+          <t>Proprietary web app plus REST API with P</t>
+        </is>
+      </c>
+      <c r="M127" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="128">
@@ -6909,19 +8182,19 @@
       </c>
       <c r="C128" s="10" t="inlineStr">
         <is>
-          <t>Funded Mission</t>
+          <t>HyperStack</t>
         </is>
       </c>
       <c r="D128" s="10" t="inlineStr">
         <is>
-          <t>2 étapes</t>
+          <t>1 étape</t>
         </is>
       </c>
       <c r="E128" s="12" t="n">
-        <v>1000000</v>
+        <v>100000</v>
       </c>
       <c r="F128" s="12" t="n">
-        <v>5883</v>
+        <v>799</v>
       </c>
       <c r="G128" s="13" t="n">
         <v>0.9</v>
@@ -6941,6 +8214,16 @@
       <c r="K128" s="12">
         <f>K127+F128</f>
         <v/>
+      </c>
+      <c r="L128" s="10" t="inlineStr">
+        <is>
+          <t>Mirrors your Hyperliquid wallet trades i</t>
+        </is>
+      </c>
+      <c r="M128" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="129">
@@ -6954,22 +8237,22 @@
       </c>
       <c r="C129" s="10" t="inlineStr">
         <is>
-          <t>The Upside Funding</t>
+          <t>DojoTraders</t>
         </is>
       </c>
       <c r="D129" s="10" t="inlineStr">
         <is>
-          <t>2 étapes</t>
+          <t>1 étape</t>
         </is>
       </c>
       <c r="E129" s="12" t="n">
-        <v>100000</v>
+        <v>500000</v>
       </c>
       <c r="F129" s="12" t="n">
-        <v>589</v>
+        <v>4250</v>
       </c>
       <c r="G129" s="13" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="H129" s="12">
         <f>E129*G129</f>
@@ -6986,6 +8269,16 @@
       <c r="K129" s="12">
         <f>K128+F129</f>
         <v/>
+      </c>
+      <c r="L129" s="10" t="inlineStr">
+        <is>
+          <t>cTrader, DXtrade, Rithmic</t>
+        </is>
+      </c>
+      <c r="M129" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="130">
@@ -6999,19 +8292,19 @@
       </c>
       <c r="C130" s="10" t="inlineStr">
         <is>
-          <t>NextGen Funding</t>
+          <t>Dojifunded</t>
         </is>
       </c>
       <c r="D130" s="10" t="inlineStr">
         <is>
-          <t>2 étapes</t>
+          <t>1 étape</t>
         </is>
       </c>
       <c r="E130" s="12" t="n">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="F130" s="12" t="n">
-        <v>1178</v>
+        <v>892</v>
       </c>
       <c r="G130" s="13" t="n">
         <v>0.9</v>
@@ -7031,6 +8324,16 @@
       <c r="K130" s="12">
         <f>K129+F130</f>
         <v/>
+      </c>
+      <c r="L130" s="10" t="inlineStr">
+        <is>
+          <t>Proprietary web terminal + public REST/W</t>
+        </is>
+      </c>
+      <c r="M130" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="131">
@@ -7044,22 +8347,22 @@
       </c>
       <c r="C131" s="10" t="inlineStr">
         <is>
-          <t>LevaFX</t>
+          <t>AI Prop</t>
         </is>
       </c>
       <c r="D131" s="10" t="inlineStr">
         <is>
-          <t>2 étapes</t>
+          <t>1 étape</t>
         </is>
       </c>
       <c r="E131" s="12" t="n">
-        <v>25000</v>
+        <v>200000</v>
       </c>
       <c r="F131" s="12" t="n">
-        <v>149</v>
+        <v>1976</v>
       </c>
       <c r="G131" s="13" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="H131" s="12">
         <f>E131*G131</f>
@@ -7076,6 +8379,16 @@
       <c r="K131" s="12">
         <f>K130+F131</f>
         <v/>
+      </c>
+      <c r="L131" s="10" t="inlineStr">
+        <is>
+          <t>cTrader</t>
+        </is>
+      </c>
+      <c r="M131" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="132">
@@ -7089,19 +8402,19 @@
       </c>
       <c r="C132" s="10" t="inlineStr">
         <is>
-          <t>Eightcap Challenges</t>
+          <t>HyperScaled</t>
         </is>
       </c>
       <c r="D132" s="10" t="inlineStr">
         <is>
-          <t>2 étapes</t>
+          <t>1 étape</t>
         </is>
       </c>
       <c r="E132" s="12" t="n">
-        <v>600000</v>
+        <v>100000</v>
       </c>
       <c r="F132" s="12" t="n">
-        <v>3594</v>
+        <v>999</v>
       </c>
       <c r="G132" s="13" t="n">
         <v>1</v>
@@ -7121,6 +8434,16 @@
       <c r="K132" s="12">
         <f>K131+F132</f>
         <v/>
+      </c>
+      <c r="L132" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mirrors your Hyperliquid wallet trades </t>
+        </is>
+      </c>
+      <c r="M132" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="133">
@@ -7134,22 +8457,22 @@
       </c>
       <c r="C133" s="10" t="inlineStr">
         <is>
-          <t>PropFunding</t>
+          <t>FX Trader's EDGE</t>
         </is>
       </c>
       <c r="D133" s="10" t="inlineStr">
         <is>
-          <t>2 étapes</t>
+          <t>1 étape</t>
         </is>
       </c>
       <c r="E133" s="12" t="n">
-        <v>25000</v>
+        <v>925000</v>
       </c>
       <c r="F133" s="12" t="n">
-        <v>150</v>
+        <v>9250</v>
       </c>
       <c r="G133" s="13" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="H133" s="12">
         <f>E133*G133</f>
@@ -7166,6 +8489,16 @@
       <c r="K133" s="12">
         <f>K132+F133</f>
         <v/>
+      </c>
+      <c r="L133" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not named on the funding page </t>
+        </is>
+      </c>
+      <c r="M133" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="134">
@@ -7179,22 +8512,22 @@
       </c>
       <c r="C134" s="10" t="inlineStr">
         <is>
-          <t>Tradexprop</t>
+          <t>BloomFunded</t>
         </is>
       </c>
       <c r="D134" s="10" t="inlineStr">
         <is>
-          <t>2 étapes</t>
+          <t>1 étape</t>
         </is>
       </c>
       <c r="E134" s="12" t="n">
-        <v>1000000</v>
+        <v>50000</v>
       </c>
       <c r="F134" s="12" t="n">
-        <v>6150</v>
+        <v>580</v>
       </c>
       <c r="G134" s="13" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="H134" s="12">
         <f>E134*G134</f>
@@ -7211,6 +8544,16 @@
       <c r="K134" s="12">
         <f>K133+F134</f>
         <v/>
+      </c>
+      <c r="L134" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not named anywhere on the official site </t>
+        </is>
+      </c>
+      <c r="M134" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="135">
@@ -7224,22 +8567,22 @@
       </c>
       <c r="C135" s="10" t="inlineStr">
         <is>
-          <t>Crypto Fund Trader</t>
+          <t>FundedWealth</t>
         </is>
       </c>
       <c r="D135" s="10" t="inlineStr">
         <is>
-          <t>2 étapes</t>
+          <t>1 étape</t>
         </is>
       </c>
       <c r="E135" s="12" t="n">
-        <v>200000</v>
+        <v>2500000</v>
       </c>
       <c r="F135" s="12" t="n">
-        <v>1250</v>
+        <v>48499</v>
       </c>
       <c r="G135" s="13" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H135" s="12">
         <f>E135*G135</f>
@@ -7256,6 +8599,16 @@
       <c r="K135" s="12">
         <f>K134+F135</f>
         <v/>
+      </c>
+      <c r="L135" s="10" t="inlineStr">
+        <is>
+          <t>Proprietary in-house web terminal + Andr</t>
+        </is>
+      </c>
+      <c r="M135" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="136">
@@ -7269,7 +8622,7 @@
       </c>
       <c r="C136" s="10" t="inlineStr">
         <is>
-          <t>Myfundedcapital</t>
+          <t>FundingRock</t>
         </is>
       </c>
       <c r="D136" s="10" t="inlineStr">
@@ -7278,13 +8631,13 @@
         </is>
       </c>
       <c r="E136" s="12" t="n">
-        <v>300000</v>
+        <v>200000</v>
       </c>
       <c r="F136" s="12" t="n">
-        <v>1905</v>
+        <v>700</v>
       </c>
       <c r="G136" s="13" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="H136" s="12">
         <f>E136*G136</f>
@@ -7301,6 +8654,16 @@
       <c r="K136" s="12">
         <f>K135+F136</f>
         <v/>
+      </c>
+      <c r="L136" s="10" t="inlineStr">
+        <is>
+          <t>cTrader, TradeLocker</t>
+        </is>
+      </c>
+      <c r="M136" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="137">
@@ -7314,7 +8677,7 @@
       </c>
       <c r="C137" s="10" t="inlineStr">
         <is>
-          <t>Key to Prop</t>
+          <t>BullRush</t>
         </is>
       </c>
       <c r="D137" s="10" t="inlineStr">
@@ -7323,13 +8686,13 @@
         </is>
       </c>
       <c r="E137" s="12" t="n">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="F137" s="12" t="n">
-        <v>650</v>
+        <v>718</v>
       </c>
       <c r="G137" s="13" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H137" s="12">
         <f>E137*G137</f>
@@ -7346,6 +8709,16 @@
       <c r="K137" s="12">
         <f>K136+F137</f>
         <v/>
+      </c>
+      <c r="L137" s="10" t="inlineStr">
+        <is>
+          <t>cTrader, DXtrade</t>
+        </is>
+      </c>
+      <c r="M137" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="138">
@@ -7359,7 +8732,7 @@
       </c>
       <c r="C138" s="10" t="inlineStr">
         <is>
-          <t>Hyper Funding</t>
+          <t>MFunded</t>
         </is>
       </c>
       <c r="D138" s="10" t="inlineStr">
@@ -7368,13 +8741,13 @@
         </is>
       </c>
       <c r="E138" s="12" t="n">
-        <v>1000000</v>
+        <v>100000</v>
       </c>
       <c r="F138" s="12" t="n">
-        <v>6803</v>
+        <v>399</v>
       </c>
       <c r="G138" s="13" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="H138" s="12">
         <f>E138*G138</f>
@@ -7391,6 +8764,16 @@
       <c r="K138" s="12">
         <f>K137+F138</f>
         <v/>
+      </c>
+      <c r="L138" s="10" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="M138" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="139">
@@ -7404,7 +8787,7 @@
       </c>
       <c r="C139" s="10" t="inlineStr">
         <is>
-          <t>Texaris</t>
+          <t>Quant Tekel (QT | FUNDED)</t>
         </is>
       </c>
       <c r="D139" s="10" t="inlineStr">
@@ -7413,10 +8796,10 @@
         </is>
       </c>
       <c r="E139" s="12" t="n">
-        <v>400000</v>
+        <v>300000</v>
       </c>
       <c r="F139" s="12" t="n">
-        <v>2796</v>
+        <v>1260</v>
       </c>
       <c r="G139" s="13" t="n">
         <v>0.8</v>
@@ -7436,6 +8819,16 @@
       <c r="K139" s="12">
         <f>K138+F139</f>
         <v/>
+      </c>
+      <c r="L139" s="10" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="M139" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="140">
@@ -7449,7 +8842,7 @@
       </c>
       <c r="C140" s="10" t="inlineStr">
         <is>
-          <t>Upcomers</t>
+          <t>EverBlue Trader</t>
         </is>
       </c>
       <c r="D140" s="10" t="inlineStr">
@@ -7458,13 +8851,13 @@
         </is>
       </c>
       <c r="E140" s="12" t="n">
-        <v>4000000</v>
+        <v>400000</v>
       </c>
       <c r="F140" s="12" t="n">
-        <v>30795</v>
+        <v>1699</v>
       </c>
       <c r="G140" s="13" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="H140" s="12">
         <f>E140*G140</f>
@@ -7481,6 +8874,16 @@
       <c r="K140" s="12">
         <f>K139+F140</f>
         <v/>
+      </c>
+      <c r="L140" s="10" t="inlineStr">
+        <is>
+          <t>TradeLocker</t>
+        </is>
+      </c>
+      <c r="M140" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="141">
@@ -7494,7 +8897,7 @@
       </c>
       <c r="C141" s="10" t="inlineStr">
         <is>
-          <t>Nova Funded</t>
+          <t>TradersEdgeFX</t>
         </is>
       </c>
       <c r="D141" s="10" t="inlineStr">
@@ -7503,13 +8906,13 @@
         </is>
       </c>
       <c r="E141" s="12" t="n">
-        <v>1000000</v>
+        <v>200000</v>
       </c>
       <c r="F141" s="12" t="n">
-        <v>7920</v>
+        <v>899</v>
       </c>
       <c r="G141" s="13" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="H141" s="12">
         <f>E141*G141</f>
@@ -7526,6 +8929,16 @@
       <c r="K141" s="12">
         <f>K140+F141</f>
         <v/>
+      </c>
+      <c r="L141" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not named anywhere on the public site </t>
+        </is>
+      </c>
+      <c r="M141" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="142">
@@ -7539,7 +8952,7 @@
       </c>
       <c r="C142" s="10" t="inlineStr">
         <is>
-          <t>Finotive Funding</t>
+          <t>OFunded</t>
         </is>
       </c>
       <c r="D142" s="10" t="inlineStr">
@@ -7548,13 +8961,13 @@
         </is>
       </c>
       <c r="E142" s="12" t="n">
-        <v>1400000</v>
+        <v>250000</v>
       </c>
       <c r="F142" s="12" t="n">
-        <v>11200</v>
+        <v>1125</v>
       </c>
       <c r="G142" s="13" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H142" s="12">
         <f>E142*G142</f>
@@ -7571,6 +8984,16 @@
       <c r="K142" s="12">
         <f>K141+F142</f>
         <v/>
+      </c>
+      <c r="L142" s="10" t="inlineStr">
+        <is>
+          <t>cTrader, DXtrade</t>
+        </is>
+      </c>
+      <c r="M142" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="143">
@@ -7584,7 +9007,7 @@
       </c>
       <c r="C143" s="10" t="inlineStr">
         <is>
-          <t>Thetradercapital</t>
+          <t>GoFunding</t>
         </is>
       </c>
       <c r="D143" s="10" t="inlineStr">
@@ -7593,13 +9016,13 @@
         </is>
       </c>
       <c r="E143" s="12" t="n">
-        <v>3000</v>
+        <v>800000</v>
       </c>
       <c r="F143" s="12" t="n">
-        <v>55</v>
+        <v>3600</v>
       </c>
       <c r="G143" s="13" t="n">
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
       <c r="H143" s="12">
         <f>E143*G143</f>
@@ -7616,6 +9039,16 @@
       <c r="K143" s="12">
         <f>K142+F143</f>
         <v/>
+      </c>
+      <c r="L143" s="10" t="inlineStr">
+        <is>
+          <t>cTrader, Match-Trader, DXtrade</t>
+        </is>
+      </c>
+      <c r="M143" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="144">
@@ -7629,7 +9062,7 @@
       </c>
       <c r="C144" s="10" t="inlineStr">
         <is>
-          <t>NairaFunded</t>
+          <t>Mubite</t>
         </is>
       </c>
       <c r="D144" s="10" t="inlineStr">
@@ -7638,13 +9071,13 @@
         </is>
       </c>
       <c r="E144" s="12" t="n">
-        <v>1500000</v>
+        <v>200000</v>
       </c>
       <c r="F144" s="12" t="n">
-        <v>58000</v>
+        <v>949</v>
       </c>
       <c r="G144" s="13" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="H144" s="12">
         <f>E144*G144</f>
@@ -7661,6 +9094,16 @@
       <c r="K144" s="12">
         <f>K143+F144</f>
         <v/>
+      </c>
+      <c r="L144" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bybit </t>
+        </is>
+      </c>
+      <c r="M144" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="145">
@@ -7674,7 +9117,7 @@
       </c>
       <c r="C145" s="10" t="inlineStr">
         <is>
-          <t>NairaProp</t>
+          <t>Seven Go Funding</t>
         </is>
       </c>
       <c r="D145" s="10" t="inlineStr">
@@ -7683,13 +9126,13 @@
         </is>
       </c>
       <c r="E145" s="12" t="n">
-        <v>3000000</v>
+        <v>1000000</v>
       </c>
       <c r="F145" s="12" t="n">
-        <v>135000</v>
+        <v>4800</v>
       </c>
       <c r="G145" s="13" t="n">
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
       <c r="H145" s="12">
         <f>E145*G145</f>
@@ -7706,6 +9149,16 @@
       <c r="K145" s="12">
         <f>K144+F145</f>
         <v/>
+      </c>
+      <c r="L145" s="10" t="inlineStr">
+        <is>
+          <t>cTrader, Match-Trader, DXtrade</t>
+        </is>
+      </c>
+      <c r="M145" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="146">
@@ -7719,7 +9172,7 @@
       </c>
       <c r="C146" s="10" t="inlineStr">
         <is>
-          <t>The Concept Trading</t>
+          <t>Mockapital</t>
         </is>
       </c>
       <c r="D146" s="10" t="inlineStr">
@@ -7731,10 +9184,10 @@
         <v>300000</v>
       </c>
       <c r="F146" s="12" t="n">
-        <v>15000</v>
+        <v>1450</v>
       </c>
       <c r="G146" s="13" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="H146" s="12">
         <f>E146*G146</f>
@@ -7751,6 +9204,16 @@
       <c r="K146" s="12">
         <f>K145+F146</f>
         <v/>
+      </c>
+      <c r="L146" s="10" t="inlineStr">
+        <is>
+          <t>cTrader, Match-Trader, DXtrade</t>
+        </is>
+      </c>
+      <c r="M146" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="147">
@@ -7764,22 +9227,22 @@
       </c>
       <c r="C147" s="10" t="inlineStr">
         <is>
-          <t>The5ers</t>
+          <t>NeomAAA Funds (NEOM Funded)</t>
         </is>
       </c>
       <c r="D147" s="10" t="inlineStr">
         <is>
-          <t>3 étapes</t>
+          <t>2 étapes</t>
         </is>
       </c>
       <c r="E147" s="12" t="n">
-        <v>120000</v>
+        <v>400000</v>
       </c>
       <c r="F147" s="12" t="n">
-        <v>117</v>
+        <v>1940</v>
       </c>
       <c r="G147" s="13" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H147" s="12">
         <f>E147*G147</f>
@@ -7796,6 +9259,16 @@
       <c r="K147" s="12">
         <f>K146+F147</f>
         <v/>
+      </c>
+      <c r="L147" s="10" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="M147" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="148">
@@ -7809,22 +9282,22 @@
       </c>
       <c r="C148" s="10" t="inlineStr">
         <is>
-          <t>The5ers Crypto</t>
+          <t>Nordic Funder</t>
         </is>
       </c>
       <c r="D148" s="10" t="inlineStr">
         <is>
-          <t>3 étapes</t>
+          <t>2 étapes</t>
         </is>
       </c>
       <c r="E148" s="12" t="n">
-        <v>120000</v>
+        <v>500000</v>
       </c>
       <c r="F148" s="12" t="n">
-        <v>117</v>
+        <v>2450</v>
       </c>
       <c r="G148" s="13" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H148" s="12">
         <f>E148*G148</f>
@@ -7841,6 +9314,16 @@
       <c r="K148" s="12">
         <f>K147+F148</f>
         <v/>
+      </c>
+      <c r="L148" s="10" t="inlineStr">
+        <is>
+          <t>cTrader, Match-Trader, DXtrade</t>
+        </is>
+      </c>
+      <c r="M148" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="149">
@@ -7854,22 +9337,22 @@
       </c>
       <c r="C149" s="10" t="inlineStr">
         <is>
-          <t>Htrader</t>
+          <t>Super Funded</t>
         </is>
       </c>
       <c r="D149" s="10" t="inlineStr">
         <is>
-          <t>3 étapes</t>
+          <t>2 étapes</t>
         </is>
       </c>
       <c r="E149" s="12" t="n">
-        <v>300000</v>
+        <v>200000</v>
       </c>
       <c r="F149" s="12" t="n">
-        <v>798</v>
+        <v>999</v>
       </c>
       <c r="G149" s="13" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="H149" s="12">
         <f>E149*G149</f>
@@ -7886,6 +9369,16 @@
       <c r="K149" s="12">
         <f>K148+F149</f>
         <v/>
+      </c>
+      <c r="L149" s="10" t="inlineStr">
+        <is>
+          <t>TradeLocker, DXtrade</t>
+        </is>
+      </c>
+      <c r="M149" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="150">
@@ -7899,22 +9392,22 @@
       </c>
       <c r="C150" s="10" t="inlineStr">
         <is>
-          <t>Atlas Funded</t>
+          <t>The Nomad Trader</t>
         </is>
       </c>
       <c r="D150" s="10" t="inlineStr">
         <is>
-          <t>3 étapes</t>
+          <t>2 étapes</t>
         </is>
       </c>
       <c r="E150" s="12" t="n">
         <v>400000</v>
       </c>
       <c r="F150" s="12" t="n">
-        <v>1182</v>
+        <v>2000</v>
       </c>
       <c r="G150" s="13" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="H150" s="12">
         <f>E150*G150</f>
@@ -7931,6 +9424,16 @@
       <c r="K150" s="12">
         <f>K149+F150</f>
         <v/>
+      </c>
+      <c r="L150" s="10" t="inlineStr">
+        <is>
+          <t>cTrader, DXtrade, Rithmic, TradingView</t>
+        </is>
+      </c>
+      <c r="M150" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="151">
@@ -7944,22 +9447,22 @@
       </c>
       <c r="C151" s="10" t="inlineStr">
         <is>
-          <t>Get Leveraged</t>
+          <t>Investiqa</t>
         </is>
       </c>
       <c r="D151" s="10" t="inlineStr">
         <is>
-          <t>3 étapes</t>
+          <t>2 étapes</t>
         </is>
       </c>
       <c r="E151" s="12" t="n">
         <v>1000000</v>
       </c>
       <c r="F151" s="12" t="n">
-        <v>2996</v>
+        <v>5040</v>
       </c>
       <c r="G151" s="13" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H151" s="12">
         <f>E151*G151</f>
@@ -7976,6 +9479,16 @@
       <c r="K151" s="12">
         <f>K150+F151</f>
         <v/>
+      </c>
+      <c r="L151" s="10" t="inlineStr">
+        <is>
+          <t>cTrader, Match-Trader, DXtrade</t>
+        </is>
+      </c>
+      <c r="M151" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="152">
@@ -7989,22 +9502,22 @@
       </c>
       <c r="C152" s="10" t="inlineStr">
         <is>
-          <t>Leveraged</t>
+          <t>FT9JA</t>
         </is>
       </c>
       <c r="D152" s="10" t="inlineStr">
         <is>
-          <t>3 étapes</t>
+          <t>2 étapes</t>
         </is>
       </c>
       <c r="E152" s="12" t="n">
-        <v>1000000</v>
+        <v>25000</v>
       </c>
       <c r="F152" s="12" t="n">
-        <v>2996</v>
+        <v>141</v>
       </c>
       <c r="G152" s="13" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H152" s="12">
         <f>E152*G152</f>
@@ -8021,6 +9534,16 @@
       <c r="K152" s="12">
         <f>K151+F152</f>
         <v/>
+      </c>
+      <c r="L152" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Broker accounts at IC Markets and FXTM </t>
+        </is>
+      </c>
+      <c r="M152" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="153">
@@ -8034,22 +9557,22 @@
       </c>
       <c r="C153" s="10" t="inlineStr">
         <is>
-          <t>AquaFunded</t>
+          <t>Funded Mission</t>
         </is>
       </c>
       <c r="D153" s="10" t="inlineStr">
         <is>
-          <t>3 étapes</t>
+          <t>2 étapes</t>
         </is>
       </c>
       <c r="E153" s="12" t="n">
-        <v>400000</v>
+        <v>1000000</v>
       </c>
       <c r="F153" s="12" t="n">
-        <v>1354</v>
+        <v>5883</v>
       </c>
       <c r="G153" s="13" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H153" s="12">
         <f>E153*G153</f>
@@ -8066,6 +9589,16 @@
       <c r="K153" s="12">
         <f>K152+F153</f>
         <v/>
+      </c>
+      <c r="L153" s="10" t="inlineStr">
+        <is>
+          <t>cTrader, Match-Trader</t>
+        </is>
+      </c>
+      <c r="M153" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="154">
@@ -8079,19 +9612,19 @@
       </c>
       <c r="C154" s="10" t="inlineStr">
         <is>
-          <t>Lark Funding</t>
+          <t>LevaFX</t>
         </is>
       </c>
       <c r="D154" s="10" t="inlineStr">
         <is>
-          <t>3 étapes</t>
+          <t>2 étapes</t>
         </is>
       </c>
       <c r="E154" s="12" t="n">
-        <v>400000</v>
+        <v>25000</v>
       </c>
       <c r="F154" s="12" t="n">
-        <v>1400</v>
+        <v>149</v>
       </c>
       <c r="G154" s="13" t="n">
         <v>0.9</v>
@@ -8111,6 +9644,16 @@
       <c r="K154" s="12">
         <f>K153+F154</f>
         <v/>
+      </c>
+      <c r="L154" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proprietary 'LEVA Terminal' </t>
+        </is>
+      </c>
+      <c r="M154" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="155">
@@ -8124,19 +9667,19 @@
       </c>
       <c r="C155" s="10" t="inlineStr">
         <is>
-          <t>Blink Funding</t>
+          <t>Tradexprop</t>
         </is>
       </c>
       <c r="D155" s="10" t="inlineStr">
         <is>
-          <t>3 étapes</t>
+          <t>2 étapes</t>
         </is>
       </c>
       <c r="E155" s="12" t="n">
-        <v>500000</v>
+        <v>1000000</v>
       </c>
       <c r="F155" s="12" t="n">
-        <v>1800</v>
+        <v>6150</v>
       </c>
       <c r="G155" s="13" t="n">
         <v>0.9</v>
@@ -8156,6 +9699,16 @@
       <c r="K155" s="12">
         <f>K154+F155</f>
         <v/>
+      </c>
+      <c r="L155" s="10" t="inlineStr">
+        <is>
+          <t>cTrader, DXtrade</t>
+        </is>
+      </c>
+      <c r="M155" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="156">
@@ -8169,19 +9722,19 @@
       </c>
       <c r="C156" s="10" t="inlineStr">
         <is>
-          <t>Orion Funded</t>
+          <t>Hyper Funding</t>
         </is>
       </c>
       <c r="D156" s="10" t="inlineStr">
         <is>
-          <t>3 étapes</t>
+          <t>2 étapes</t>
         </is>
       </c>
       <c r="E156" s="12" t="n">
-        <v>400000</v>
+        <v>1000000</v>
       </c>
       <c r="F156" s="12" t="n">
-        <v>1478</v>
+        <v>6803</v>
       </c>
       <c r="G156" s="13" t="n">
         <v>0.9</v>
@@ -8201,6 +9754,16 @@
       <c r="K156" s="12">
         <f>K155+F156</f>
         <v/>
+      </c>
+      <c r="L156" s="10" t="inlineStr">
+        <is>
+          <t>cTrader, DXtrade</t>
+        </is>
+      </c>
+      <c r="M156" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="157">
@@ -8214,19 +9777,19 @@
       </c>
       <c r="C157" s="10" t="inlineStr">
         <is>
-          <t>Monevis</t>
+          <t>Nova Funded</t>
         </is>
       </c>
       <c r="D157" s="10" t="inlineStr">
         <is>
-          <t>3 étapes</t>
+          <t>2 étapes</t>
         </is>
       </c>
       <c r="E157" s="12" t="n">
-        <v>200000</v>
+        <v>1000000</v>
       </c>
       <c r="F157" s="12" t="n">
-        <v>770</v>
+        <v>7920</v>
       </c>
       <c r="G157" s="13" t="n">
         <v>0.9</v>
@@ -8246,6 +9809,16 @@
       <c r="K157" s="12">
         <f>K156+F157</f>
         <v/>
+      </c>
+      <c r="L157" s="10" t="inlineStr">
+        <is>
+          <t>cTrader, DXtrade, Rithmic, TradingView</t>
+        </is>
+      </c>
+      <c r="M157" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="158">
@@ -8259,22 +9832,22 @@
       </c>
       <c r="C158" s="10" t="inlineStr">
         <is>
-          <t>Turbo Trade Fund</t>
+          <t>The Concept Trading</t>
         </is>
       </c>
       <c r="D158" s="10" t="inlineStr">
         <is>
-          <t>3 étapes</t>
+          <t>2 étapes</t>
         </is>
       </c>
       <c r="E158" s="12" t="n">
-        <v>200000</v>
+        <v>300000</v>
       </c>
       <c r="F158" s="12" t="n">
-        <v>799</v>
+        <v>15000</v>
       </c>
       <c r="G158" s="13" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H158" s="12">
         <f>E158*G158</f>
@@ -8291,6 +9864,16 @@
       <c r="K158" s="12">
         <f>K157+F158</f>
         <v/>
+      </c>
+      <c r="L158" s="10" t="inlineStr">
+        <is>
+          <t>TradeLocker</t>
+        </is>
+      </c>
+      <c r="M158" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="159">
@@ -8304,7 +9887,7 @@
       </c>
       <c r="C159" s="10" t="inlineStr">
         <is>
-          <t>Get Crypto Funded</t>
+          <t>Lark Funding</t>
         </is>
       </c>
       <c r="D159" s="10" t="inlineStr">
@@ -8316,10 +9899,10 @@
         <v>400000</v>
       </c>
       <c r="F159" s="12" t="n">
-        <v>1648</v>
+        <v>1400</v>
       </c>
       <c r="G159" s="13" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="H159" s="12">
         <f>E159*G159</f>
@@ -8336,6 +9919,16 @@
       <c r="K159" s="12">
         <f>K158+F159</f>
         <v/>
+      </c>
+      <c r="L159" s="10" t="inlineStr">
+        <is>
+          <t>cTrader, Match-Trader, DXtrade</t>
+        </is>
+      </c>
+      <c r="M159" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="160">
@@ -8349,7 +9942,7 @@
       </c>
       <c r="C160" s="10" t="inlineStr">
         <is>
-          <t>Fintokei</t>
+          <t>Turbo Trade Fund</t>
         </is>
       </c>
       <c r="D160" s="10" t="inlineStr">
@@ -8358,13 +9951,13 @@
         </is>
       </c>
       <c r="E160" s="12" t="n">
-        <v>700000</v>
+        <v>200000</v>
       </c>
       <c r="F160" s="12" t="n">
-        <v>2933</v>
+        <v>799</v>
       </c>
       <c r="G160" s="13" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="H160" s="12">
         <f>E160*G160</f>
@@ -8381,6 +9974,16 @@
       <c r="K160" s="12">
         <f>K159+F160</f>
         <v/>
+      </c>
+      <c r="L160" s="10" t="inlineStr">
+        <is>
+          <t>Match-Trader</t>
+        </is>
+      </c>
+      <c r="M160" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="161">
@@ -8427,12 +10030,22 @@
         <f>K160+F161</f>
         <v/>
       </c>
+      <c r="L161" s="10" t="inlineStr">
+        <is>
+          <t>cTrader, Match-Trader, DXtrade</t>
+        </is>
+      </c>
+      <c r="M161" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="10" t="n">
         <v>161</v>
       </c>
-      <c r="B162" s="14" t="inlineStr">
+      <c r="B162" s="15" t="inlineStr">
         <is>
           <t>Futures</t>
         </is>
@@ -8471,13 +10084,23 @@
       <c r="K162" s="12">
         <f>K161+F162</f>
         <v/>
+      </c>
+      <c r="L162" s="10" t="inlineStr">
+        <is>
+          <t>Rithmic, Volumetrica, TradingView</t>
+        </is>
+      </c>
+      <c r="M162" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="10" t="n">
         <v>162</v>
       </c>
-      <c r="B163" s="14" t="inlineStr">
+      <c r="B163" s="15" t="inlineStr">
         <is>
           <t>Futures</t>
         </is>
@@ -8516,13 +10139,23 @@
       <c r="K163" s="12">
         <f>K162+F163</f>
         <v/>
+      </c>
+      <c r="L163" s="10" t="inlineStr">
+        <is>
+          <t>NinjaTrader, Tradovate, Rithmic, Quantow</t>
+        </is>
+      </c>
+      <c r="M163" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="10" t="n">
         <v>163</v>
       </c>
-      <c r="B164" s="14" t="inlineStr">
+      <c r="B164" s="15" t="inlineStr">
         <is>
           <t>Futures</t>
         </is>
@@ -8561,13 +10194,23 @@
       <c r="K164" s="12">
         <f>K163+F164</f>
         <v/>
+      </c>
+      <c r="L164" s="10" t="inlineStr">
+        <is>
+          <t>NinjaTrader, Tradovate, Rithmic, Quantow</t>
+        </is>
+      </c>
+      <c r="M164" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="10" t="n">
         <v>164</v>
       </c>
-      <c r="B165" s="14" t="inlineStr">
+      <c r="B165" s="15" t="inlineStr">
         <is>
           <t>Futures</t>
         </is>
@@ -8606,13 +10249,23 @@
       <c r="K165" s="12">
         <f>K164+F165</f>
         <v/>
+      </c>
+      <c r="L165" s="10" t="inlineStr">
+        <is>
+          <t>Quantower, Volumetrica</t>
+        </is>
+      </c>
+      <c r="M165" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="10" t="n">
         <v>165</v>
       </c>
-      <c r="B166" s="14" t="inlineStr">
+      <c r="B166" s="15" t="inlineStr">
         <is>
           <t>Futures</t>
         </is>
@@ -8651,13 +10304,23 @@
       <c r="K166" s="12">
         <f>K165+F166</f>
         <v/>
+      </c>
+      <c r="L166" s="10" t="inlineStr">
+        <is>
+          <t>NinjaTrader, Tradovate, Quantower, Tradi</t>
+        </is>
+      </c>
+      <c r="M166" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="10" t="n">
         <v>166</v>
       </c>
-      <c r="B167" s="14" t="inlineStr">
+      <c r="B167" s="15" t="inlineStr">
         <is>
           <t>Futures</t>
         </is>
@@ -8696,13 +10359,23 @@
       <c r="K167" s="12">
         <f>K166+F167</f>
         <v/>
+      </c>
+      <c r="L167" s="10" t="inlineStr">
+        <is>
+          <t>NinjaTrader, Tradovate, Quantower, Tradi</t>
+        </is>
+      </c>
+      <c r="M167" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="10" t="n">
         <v>167</v>
       </c>
-      <c r="B168" s="14" t="inlineStr">
+      <c r="B168" s="15" t="inlineStr">
         <is>
           <t>Futures</t>
         </is>
@@ -8741,13 +10414,23 @@
       <c r="K168" s="12">
         <f>K167+F168</f>
         <v/>
+      </c>
+      <c r="L168" s="10" t="inlineStr">
+        <is>
+          <t>NinjaTrader, Rithmic</t>
+        </is>
+      </c>
+      <c r="M168" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="10" t="n">
         <v>168</v>
       </c>
-      <c r="B169" s="14" t="inlineStr">
+      <c r="B169" s="15" t="inlineStr">
         <is>
           <t>Futures</t>
         </is>
@@ -8786,13 +10469,23 @@
       <c r="K169" s="12">
         <f>K168+F169</f>
         <v/>
+      </c>
+      <c r="L169" s="10" t="inlineStr">
+        <is>
+          <t>NinjaTrader, Quantower, Volumetrica</t>
+        </is>
+      </c>
+      <c r="M169" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="10" t="n">
         <v>169</v>
       </c>
-      <c r="B170" s="14" t="inlineStr">
+      <c r="B170" s="15" t="inlineStr">
         <is>
           <t>Futures</t>
         </is>
@@ -8831,13 +10524,23 @@
       <c r="K170" s="12">
         <f>K169+F170</f>
         <v/>
+      </c>
+      <c r="L170" s="10" t="inlineStr">
+        <is>
+          <t>Quantower, Volumetrica</t>
+        </is>
+      </c>
+      <c r="M170" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="10" t="n">
         <v>170</v>
       </c>
-      <c r="B171" s="14" t="inlineStr">
+      <c r="B171" s="15" t="inlineStr">
         <is>
           <t>Futures</t>
         </is>
@@ -8876,13 +10579,23 @@
       <c r="K171" s="12">
         <f>K170+F171</f>
         <v/>
+      </c>
+      <c r="L171" s="10" t="inlineStr">
+        <is>
+          <t>NinjaTrader, Tradovate, TradingView</t>
+        </is>
+      </c>
+      <c r="M171" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="10" t="n">
         <v>171</v>
       </c>
-      <c r="B172" s="14" t="inlineStr">
+      <c r="B172" s="15" t="inlineStr">
         <is>
           <t>Futures</t>
         </is>
@@ -8921,13 +10634,23 @@
       <c r="K172" s="12">
         <f>K171+F172</f>
         <v/>
+      </c>
+      <c r="L172" s="10" t="inlineStr">
+        <is>
+          <t>NinjaTrader, Tradovate, Rithmic, Quantow</t>
+        </is>
+      </c>
+      <c r="M172" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="10" t="n">
         <v>172</v>
       </c>
-      <c r="B173" s="14" t="inlineStr">
+      <c r="B173" s="15" t="inlineStr">
         <is>
           <t>Futures</t>
         </is>
@@ -8966,13 +10689,23 @@
       <c r="K173" s="12">
         <f>K172+F173</f>
         <v/>
+      </c>
+      <c r="L173" s="10" t="inlineStr">
+        <is>
+          <t>NinjaTrader, Tradovate, Rithmic, Quantow</t>
+        </is>
+      </c>
+      <c r="M173" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="10" t="n">
         <v>173</v>
       </c>
-      <c r="B174" s="14" t="inlineStr">
+      <c r="B174" s="15" t="inlineStr">
         <is>
           <t>Futures</t>
         </is>
@@ -9011,13 +10744,23 @@
       <c r="K174" s="12">
         <f>K173+F174</f>
         <v/>
+      </c>
+      <c r="L174" s="10" t="inlineStr">
+        <is>
+          <t>NinjaTrader, Rithmic, Quantower</t>
+        </is>
+      </c>
+      <c r="M174" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="10" t="n">
         <v>174</v>
       </c>
-      <c r="B175" s="14" t="inlineStr">
+      <c r="B175" s="15" t="inlineStr">
         <is>
           <t>Futures</t>
         </is>
@@ -9056,13 +10799,23 @@
       <c r="K175" s="12">
         <f>K174+F175</f>
         <v/>
+      </c>
+      <c r="L175" s="10" t="inlineStr">
+        <is>
+          <t>Rithmic, Volumetrica</t>
+        </is>
+      </c>
+      <c r="M175" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="10" t="n">
         <v>175</v>
       </c>
-      <c r="B176" s="14" t="inlineStr">
+      <c r="B176" s="15" t="inlineStr">
         <is>
           <t>Futures</t>
         </is>
@@ -9101,13 +10854,23 @@
       <c r="K176" s="12">
         <f>K175+F176</f>
         <v/>
+      </c>
+      <c r="L176" s="10" t="inlineStr">
+        <is>
+          <t>Volumetrica</t>
+        </is>
+      </c>
+      <c r="M176" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="10" t="n">
         <v>176</v>
       </c>
-      <c r="B177" s="14" t="inlineStr">
+      <c r="B177" s="15" t="inlineStr">
         <is>
           <t>Futures</t>
         </is>
@@ -9146,13 +10909,23 @@
       <c r="K177" s="12">
         <f>K176+F177</f>
         <v/>
+      </c>
+      <c r="L177" s="10" t="inlineStr">
+        <is>
+          <t>NinjaTrader, Tradovate, Quantower, Tradi</t>
+        </is>
+      </c>
+      <c r="M177" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="10" t="n">
         <v>177</v>
       </c>
-      <c r="B178" s="14" t="inlineStr">
+      <c r="B178" s="15" t="inlineStr">
         <is>
           <t>Futures</t>
         </is>
@@ -9191,13 +10964,23 @@
       <c r="K178" s="12">
         <f>K177+F178</f>
         <v/>
+      </c>
+      <c r="L178" s="10" t="inlineStr">
+        <is>
+          <t>NinjaTrader, Rithmic, Quantower</t>
+        </is>
+      </c>
+      <c r="M178" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="10" t="n">
         <v>178</v>
       </c>
-      <c r="B179" s="14" t="inlineStr">
+      <c r="B179" s="15" t="inlineStr">
         <is>
           <t>Futures</t>
         </is>
@@ -9236,13 +11019,23 @@
       <c r="K179" s="12">
         <f>K178+F179</f>
         <v/>
+      </c>
+      <c r="L179" s="10" t="inlineStr">
+        <is>
+          <t>Proprietary perps platform with REST, We</t>
+        </is>
+      </c>
+      <c r="M179" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="10" t="n">
         <v>179</v>
       </c>
-      <c r="B180" s="14" t="inlineStr">
+      <c r="B180" s="15" t="inlineStr">
         <is>
           <t>Futures</t>
         </is>
@@ -9281,13 +11074,23 @@
       <c r="K180" s="12">
         <f>K179+F180</f>
         <v/>
+      </c>
+      <c r="L180" s="10" t="inlineStr">
+        <is>
+          <t>Custom-built web terminal</t>
+        </is>
+      </c>
+      <c r="M180" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="10" t="n">
         <v>180</v>
       </c>
-      <c r="B181" s="14" t="inlineStr">
+      <c r="B181" s="15" t="inlineStr">
         <is>
           <t>Futures</t>
         </is>
@@ -9326,13 +11129,23 @@
       <c r="K181" s="12">
         <f>K180+F181</f>
         <v/>
+      </c>
+      <c r="L181" s="10" t="inlineStr">
+        <is>
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="M181" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="10" t="n">
         <v>181</v>
       </c>
-      <c r="B182" s="14" t="inlineStr">
+      <c r="B182" s="15" t="inlineStr">
         <is>
           <t>Futures</t>
         </is>
@@ -9371,13 +11184,23 @@
       <c r="K182" s="12">
         <f>K181+F182</f>
         <v/>
+      </c>
+      <c r="L182" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nelogica Profit One / Profit Pro </t>
+        </is>
+      </c>
+      <c r="M182" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="10" t="n">
         <v>182</v>
       </c>
-      <c r="B183" s="14" t="inlineStr">
+      <c r="B183" s="15" t="inlineStr">
         <is>
           <t>Futures</t>
         </is>
@@ -9416,13 +11239,23 @@
       <c r="K183" s="12">
         <f>K182+F183</f>
         <v/>
+      </c>
+      <c r="L183" s="10" t="inlineStr">
+        <is>
+          <t>Typed REST + WebSocket API and open SDKs</t>
+        </is>
+      </c>
+      <c r="M183" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="10" t="n">
         <v>183</v>
       </c>
-      <c r="B184" s="14" t="inlineStr">
+      <c r="B184" s="15" t="inlineStr">
         <is>
           <t>Futures</t>
         </is>
@@ -9461,13 +11294,23 @@
       <c r="K184" s="12">
         <f>K183+F184</f>
         <v/>
+      </c>
+      <c r="L184" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proprietary web platform/dashboard only </t>
+        </is>
+      </c>
+      <c r="M184" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="10" t="n">
         <v>184</v>
       </c>
-      <c r="B185" s="14" t="inlineStr">
+      <c r="B185" s="15" t="inlineStr">
         <is>
           <t>Futures</t>
         </is>
@@ -9506,13 +11349,23 @@
       <c r="K185" s="12">
         <f>K184+F185</f>
         <v/>
+      </c>
+      <c r="L185" s="10" t="inlineStr">
+        <is>
+          <t>cTrader, DXtrade</t>
+        </is>
+      </c>
+      <c r="M185" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="10" t="n">
         <v>185</v>
       </c>
-      <c r="B186" s="14" t="inlineStr">
+      <c r="B186" s="15" t="inlineStr">
         <is>
           <t>Futures</t>
         </is>
@@ -9551,13 +11404,23 @@
       <c r="K186" s="12">
         <f>K185+F186</f>
         <v/>
+      </c>
+      <c r="L186" s="10" t="inlineStr">
+        <is>
+          <t>NinjaTrader, Rithmic, Volumetrica</t>
+        </is>
+      </c>
+      <c r="M186" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="10" t="n">
         <v>186</v>
       </c>
-      <c r="B187" s="14" t="inlineStr">
+      <c r="B187" s="15" t="inlineStr">
         <is>
           <t>Futures</t>
         </is>
@@ -9596,13 +11459,23 @@
       <c r="K187" s="12">
         <f>K186+F187</f>
         <v/>
+      </c>
+      <c r="L187" s="10" t="inlineStr">
+        <is>
+          <t>NinjaTrader, Tradovate, Rithmic, Quantow</t>
+        </is>
+      </c>
+      <c r="M187" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="10" t="n">
         <v>187</v>
       </c>
-      <c r="B188" s="14" t="inlineStr">
+      <c r="B188" s="15" t="inlineStr">
         <is>
           <t>Futures</t>
         </is>
@@ -9641,13 +11514,23 @@
       <c r="K188" s="12">
         <f>K187+F188</f>
         <v/>
+      </c>
+      <c r="L188" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Profit </t>
+        </is>
+      </c>
+      <c r="M188" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="10" t="n">
         <v>188</v>
       </c>
-      <c r="B189" s="14" t="inlineStr">
+      <c r="B189" s="15" t="inlineStr">
         <is>
           <t>Futures</t>
         </is>
@@ -9686,13 +11569,23 @@
       <c r="K189" s="12">
         <f>K188+F189</f>
         <v/>
+      </c>
+      <c r="L189" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Profit One </t>
+        </is>
+      </c>
+      <c r="M189" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="10" t="n">
         <v>189</v>
       </c>
-      <c r="B190" s="14" t="inlineStr">
+      <c r="B190" s="15" t="inlineStr">
         <is>
           <t>Futures</t>
         </is>
@@ -9731,6 +11624,16 @@
       <c r="K190" s="12">
         <f>K189+F190</f>
         <v/>
+      </c>
+      <c r="L190" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bybit demo </t>
+        </is>
+      </c>
+      <c r="M190" s="10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -9841,7 +11744,7 @@
         <f>E2-0</f>
         <v/>
       </c>
-      <c r="G2" s="15">
+      <c r="G2" s="16">
         <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E2),0)</f>
         <v/>
       </c>
@@ -9853,7 +11756,7 @@
         <f>G2-H2</f>
         <v/>
       </c>
-      <c r="J2" s="15">
+      <c r="J2" s="16">
         <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E2),0))*Paramètres!$B$3</f>
         <v/>
       </c>
@@ -9886,7 +11789,7 @@
         <f>E3-E2</f>
         <v/>
       </c>
-      <c r="G3" s="15">
+      <c r="G3" s="16">
         <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E3),0)</f>
         <v/>
       </c>
@@ -9898,7 +11801,7 @@
         <f>G3-H3</f>
         <v/>
       </c>
-      <c r="J3" s="15">
+      <c r="J3" s="16">
         <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E3),0))*Paramètres!$B$3</f>
         <v/>
       </c>
@@ -9931,7 +11834,7 @@
         <f>E4-E3</f>
         <v/>
       </c>
-      <c r="G4" s="15">
+      <c r="G4" s="16">
         <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E4),0)</f>
         <v/>
       </c>
@@ -9943,7 +11846,7 @@
         <f>G4-H4</f>
         <v/>
       </c>
-      <c r="J4" s="15">
+      <c r="J4" s="16">
         <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E4),0))*Paramètres!$B$3</f>
         <v/>
       </c>
@@ -9976,7 +11879,7 @@
         <f>E5-E4</f>
         <v/>
       </c>
-      <c r="G5" s="15">
+      <c r="G5" s="16">
         <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E5),0)</f>
         <v/>
       </c>
@@ -9988,7 +11891,7 @@
         <f>G5-H5</f>
         <v/>
       </c>
-      <c r="J5" s="15">
+      <c r="J5" s="16">
         <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E5),0))*Paramètres!$B$3</f>
         <v/>
       </c>
@@ -10021,7 +11924,7 @@
         <f>E6-E5</f>
         <v/>
       </c>
-      <c r="G6" s="15">
+      <c r="G6" s="16">
         <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E6),0)</f>
         <v/>
       </c>
@@ -10033,7 +11936,7 @@
         <f>G6-H6</f>
         <v/>
       </c>
-      <c r="J6" s="15">
+      <c r="J6" s="16">
         <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E6),0))*Paramètres!$B$3</f>
         <v/>
       </c>
@@ -10066,7 +11969,7 @@
         <f>E7-E6</f>
         <v/>
       </c>
-      <c r="G7" s="15">
+      <c r="G7" s="16">
         <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E7),0)</f>
         <v/>
       </c>
@@ -10078,7 +11981,7 @@
         <f>G7-H7</f>
         <v/>
       </c>
-      <c r="J7" s="15">
+      <c r="J7" s="16">
         <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E7),0))*Paramètres!$B$3</f>
         <v/>
       </c>
@@ -10111,7 +12014,7 @@
         <f>E8-E7</f>
         <v/>
       </c>
-      <c r="G8" s="15">
+      <c r="G8" s="16">
         <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E8),0)</f>
         <v/>
       </c>
@@ -10123,7 +12026,7 @@
         <f>G8-H8</f>
         <v/>
       </c>
-      <c r="J8" s="15">
+      <c r="J8" s="16">
         <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E8),0))*Paramètres!$B$3</f>
         <v/>
       </c>
@@ -10156,7 +12059,7 @@
         <f>E9-E8</f>
         <v/>
       </c>
-      <c r="G9" s="15">
+      <c r="G9" s="16">
         <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E9),0)</f>
         <v/>
       </c>
@@ -10168,7 +12071,7 @@
         <f>G9-H9</f>
         <v/>
       </c>
-      <c r="J9" s="15">
+      <c r="J9" s="16">
         <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E9),0))*Paramètres!$B$3</f>
         <v/>
       </c>
@@ -10201,7 +12104,7 @@
         <f>E10-E9</f>
         <v/>
       </c>
-      <c r="G10" s="15">
+      <c r="G10" s="16">
         <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E10),0)</f>
         <v/>
       </c>
@@ -10213,7 +12116,7 @@
         <f>G10-H10</f>
         <v/>
       </c>
-      <c r="J10" s="15">
+      <c r="J10" s="16">
         <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E10),0))*Paramètres!$B$3</f>
         <v/>
       </c>
@@ -10246,7 +12149,7 @@
         <f>E11-E10</f>
         <v/>
       </c>
-      <c r="G11" s="15">
+      <c r="G11" s="16">
         <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E11),0)</f>
         <v/>
       </c>
@@ -10258,7 +12161,7 @@
         <f>G11-H11</f>
         <v/>
       </c>
-      <c r="J11" s="15">
+      <c r="J11" s="16">
         <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E11),0))*Paramètres!$B$3</f>
         <v/>
       </c>
@@ -10291,7 +12194,7 @@
         <f>E12-E11</f>
         <v/>
       </c>
-      <c r="G12" s="15">
+      <c r="G12" s="16">
         <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E12),0)</f>
         <v/>
       </c>
@@ -10303,7 +12206,7 @@
         <f>G12-H12</f>
         <v/>
       </c>
-      <c r="J12" s="15">
+      <c r="J12" s="16">
         <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E12),0))*Paramètres!$B$3</f>
         <v/>
       </c>
@@ -10336,7 +12239,7 @@
         <f>E13-E12</f>
         <v/>
       </c>
-      <c r="G13" s="15">
+      <c r="G13" s="16">
         <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E13),0)</f>
         <v/>
       </c>
@@ -10348,7 +12251,7 @@
         <f>G13-H13</f>
         <v/>
       </c>
-      <c r="J13" s="15">
+      <c r="J13" s="16">
         <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E13),0))*Paramètres!$B$3</f>
         <v/>
       </c>
@@ -10381,7 +12284,7 @@
         <f>E14-E13</f>
         <v/>
       </c>
-      <c r="G14" s="15">
+      <c r="G14" s="16">
         <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E14),0)</f>
         <v/>
       </c>
@@ -10393,7 +12296,7 @@
         <f>G14-H14</f>
         <v/>
       </c>
-      <c r="J14" s="15">
+      <c r="J14" s="16">
         <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E14),0))*Paramètres!$B$3</f>
         <v/>
       </c>
@@ -10426,7 +12329,7 @@
         <f>E15-E14</f>
         <v/>
       </c>
-      <c r="G15" s="15">
+      <c r="G15" s="16">
         <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E15),0)</f>
         <v/>
       </c>
@@ -10438,7 +12341,7 @@
         <f>G15-H15</f>
         <v/>
       </c>
-      <c r="J15" s="15">
+      <c r="J15" s="16">
         <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E15),0))*Paramètres!$B$3</f>
         <v/>
       </c>
@@ -10471,7 +12374,7 @@
         <f>E16-E15</f>
         <v/>
       </c>
-      <c r="G16" s="15">
+      <c r="G16" s="16">
         <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E16),0)</f>
         <v/>
       </c>
@@ -10483,7 +12386,7 @@
         <f>G16-H16</f>
         <v/>
       </c>
-      <c r="J16" s="15">
+      <c r="J16" s="16">
         <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E16),0))*Paramètres!$B$3</f>
         <v/>
       </c>
@@ -10516,7 +12419,7 @@
         <f>E17-E16</f>
         <v/>
       </c>
-      <c r="G17" s="15">
+      <c r="G17" s="16">
         <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E17),0)</f>
         <v/>
       </c>
@@ -10528,7 +12431,7 @@
         <f>G17-H17</f>
         <v/>
       </c>
-      <c r="J17" s="15">
+      <c r="J17" s="16">
         <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E17),0))*Paramètres!$B$3</f>
         <v/>
       </c>
@@ -10561,7 +12464,7 @@
         <f>E18-E17</f>
         <v/>
       </c>
-      <c r="G18" s="15">
+      <c r="G18" s="16">
         <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E18),0)</f>
         <v/>
       </c>
@@ -10573,7 +12476,7 @@
         <f>G18-H18</f>
         <v/>
       </c>
-      <c r="J18" s="15">
+      <c r="J18" s="16">
         <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E18),0))*Paramètres!$B$3</f>
         <v/>
       </c>
@@ -10606,7 +12509,7 @@
         <f>E19-E18</f>
         <v/>
       </c>
-      <c r="G19" s="15">
+      <c r="G19" s="16">
         <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E19),0)</f>
         <v/>
       </c>
@@ -10618,7 +12521,7 @@
         <f>G19-H19</f>
         <v/>
       </c>
-      <c r="J19" s="15">
+      <c r="J19" s="16">
         <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E19),0))*Paramètres!$B$3</f>
         <v/>
       </c>
@@ -10651,7 +12554,7 @@
         <f>E20-E19</f>
         <v/>
       </c>
-      <c r="G20" s="15">
+      <c r="G20" s="16">
         <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E20),0)</f>
         <v/>
       </c>
@@ -10663,7 +12566,7 @@
         <f>G20-H20</f>
         <v/>
       </c>
-      <c r="J20" s="15">
+      <c r="J20" s="16">
         <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E20),0))*Paramètres!$B$3</f>
         <v/>
       </c>
@@ -10696,7 +12599,7 @@
         <f>E21-E20</f>
         <v/>
       </c>
-      <c r="G21" s="15">
+      <c r="G21" s="16">
         <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E21),0)</f>
         <v/>
       </c>
@@ -10708,7 +12611,7 @@
         <f>G21-H21</f>
         <v/>
       </c>
-      <c r="J21" s="15">
+      <c r="J21" s="16">
         <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E21),0))*Paramètres!$B$3</f>
         <v/>
       </c>
@@ -10741,7 +12644,7 @@
         <f>E22-E21</f>
         <v/>
       </c>
-      <c r="G22" s="15">
+      <c r="G22" s="16">
         <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E22),0)</f>
         <v/>
       </c>
@@ -10753,7 +12656,7 @@
         <f>G22-H22</f>
         <v/>
       </c>
-      <c r="J22" s="15">
+      <c r="J22" s="16">
         <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E22),0))*Paramètres!$B$3</f>
         <v/>
       </c>
@@ -10786,7 +12689,7 @@
         <f>E23-E22</f>
         <v/>
       </c>
-      <c r="G23" s="15">
+      <c r="G23" s="16">
         <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E23),0)</f>
         <v/>
       </c>
@@ -10798,7 +12701,7 @@
         <f>G23-H23</f>
         <v/>
       </c>
-      <c r="J23" s="15">
+      <c r="J23" s="16">
         <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E23),0))*Paramètres!$B$3</f>
         <v/>
       </c>
@@ -10831,7 +12734,7 @@
         <f>E24-E23</f>
         <v/>
       </c>
-      <c r="G24" s="15">
+      <c r="G24" s="16">
         <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E24),0)</f>
         <v/>
       </c>
@@ -10843,7 +12746,7 @@
         <f>G24-H24</f>
         <v/>
       </c>
-      <c r="J24" s="15">
+      <c r="J24" s="16">
         <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E24),0))*Paramètres!$B$3</f>
         <v/>
       </c>
@@ -10876,7 +12779,7 @@
         <f>E25-E24</f>
         <v/>
       </c>
-      <c r="G25" s="15">
+      <c r="G25" s="16">
         <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E25),0)</f>
         <v/>
       </c>
@@ -10888,7 +12791,7 @@
         <f>G25-H25</f>
         <v/>
       </c>
-      <c r="J25" s="15">
+      <c r="J25" s="16">
         <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E25),0))*Paramètres!$B$3</f>
         <v/>
       </c>
@@ -10921,7 +12824,7 @@
         <f>E26-E25</f>
         <v/>
       </c>
-      <c r="G26" s="15">
+      <c r="G26" s="16">
         <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E26),0)</f>
         <v/>
       </c>
@@ -10933,7 +12836,7 @@
         <f>G26-H26</f>
         <v/>
       </c>
-      <c r="J26" s="15">
+      <c r="J26" s="16">
         <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E26),0))*Paramètres!$B$3</f>
         <v/>
       </c>
@@ -10966,7 +12869,7 @@
         <f>E27-E26</f>
         <v/>
       </c>
-      <c r="G27" s="15">
+      <c r="G27" s="16">
         <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E27),0)</f>
         <v/>
       </c>
@@ -10978,7 +12881,7 @@
         <f>G27-H27</f>
         <v/>
       </c>
-      <c r="J27" s="15">
+      <c r="J27" s="16">
         <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E27),0))*Paramètres!$B$3</f>
         <v/>
       </c>
@@ -11011,7 +12914,7 @@
         <f>E28-E27</f>
         <v/>
       </c>
-      <c r="G28" s="15">
+      <c r="G28" s="16">
         <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E28),0)</f>
         <v/>
       </c>
@@ -11023,7 +12926,7 @@
         <f>G28-H28</f>
         <v/>
       </c>
-      <c r="J28" s="15">
+      <c r="J28" s="16">
         <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E28),0))*Paramètres!$B$3</f>
         <v/>
       </c>
@@ -11056,7 +12959,7 @@
         <f>E29-E28</f>
         <v/>
       </c>
-      <c r="G29" s="15">
+      <c r="G29" s="16">
         <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E29),0)</f>
         <v/>
       </c>
@@ -11068,7 +12971,7 @@
         <f>G29-H29</f>
         <v/>
       </c>
-      <c r="J29" s="15">
+      <c r="J29" s="16">
         <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E29),0))*Paramètres!$B$3</f>
         <v/>
       </c>
@@ -11101,7 +13004,7 @@
         <f>E30-E29</f>
         <v/>
       </c>
-      <c r="G30" s="15">
+      <c r="G30" s="16">
         <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E30),0)</f>
         <v/>
       </c>
@@ -11113,7 +13016,7 @@
         <f>G30-H30</f>
         <v/>
       </c>
-      <c r="J30" s="15">
+      <c r="J30" s="16">
         <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E30),0))*Paramètres!$B$3</f>
         <v/>
       </c>
@@ -11146,7 +13049,7 @@
         <f>E31-E30</f>
         <v/>
       </c>
-      <c r="G31" s="15">
+      <c r="G31" s="16">
         <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E31),0)</f>
         <v/>
       </c>
@@ -11158,7 +13061,7 @@
         <f>G31-H31</f>
         <v/>
       </c>
-      <c r="J31" s="15">
+      <c r="J31" s="16">
         <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E31),0))*Paramètres!$B$3</f>
         <v/>
       </c>
@@ -11191,7 +13094,7 @@
         <f>E32-E31</f>
         <v/>
       </c>
-      <c r="G32" s="15">
+      <c r="G32" s="16">
         <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E32),0)</f>
         <v/>
       </c>
@@ -11203,7 +13106,7 @@
         <f>G32-H32</f>
         <v/>
       </c>
-      <c r="J32" s="15">
+      <c r="J32" s="16">
         <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E32),0))*Paramètres!$B$3</f>
         <v/>
       </c>
@@ -11236,7 +13139,7 @@
         <f>E33-E32</f>
         <v/>
       </c>
-      <c r="G33" s="15">
+      <c r="G33" s="16">
         <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E33),0)</f>
         <v/>
       </c>
@@ -11248,7 +13151,7 @@
         <f>G33-H33</f>
         <v/>
       </c>
-      <c r="J33" s="15">
+      <c r="J33" s="16">
         <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E33),0))*Paramètres!$B$3</f>
         <v/>
       </c>
@@ -11281,7 +13184,7 @@
         <f>E34-E33</f>
         <v/>
       </c>
-      <c r="G34" s="15">
+      <c r="G34" s="16">
         <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E34),0)</f>
         <v/>
       </c>
@@ -11293,7 +13196,7 @@
         <f>G34-H34</f>
         <v/>
       </c>
-      <c r="J34" s="15">
+      <c r="J34" s="16">
         <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E34),0))*Paramètres!$B$3</f>
         <v/>
       </c>
@@ -11326,7 +13229,7 @@
         <f>E35-E34</f>
         <v/>
       </c>
-      <c r="G35" s="15">
+      <c r="G35" s="16">
         <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E35),0)</f>
         <v/>
       </c>
@@ -11338,7 +13241,7 @@
         <f>G35-H35</f>
         <v/>
       </c>
-      <c r="J35" s="15">
+      <c r="J35" s="16">
         <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E35),0))*Paramètres!$B$3</f>
         <v/>
       </c>
@@ -11371,7 +13274,7 @@
         <f>E36-E35</f>
         <v/>
       </c>
-      <c r="G36" s="15">
+      <c r="G36" s="16">
         <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E36),0)</f>
         <v/>
       </c>
@@ -11383,7 +13286,7 @@
         <f>G36-H36</f>
         <v/>
       </c>
-      <c r="J36" s="15">
+      <c r="J36" s="16">
         <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E36),0))*Paramètres!$B$3</f>
         <v/>
       </c>
@@ -11416,7 +13319,7 @@
         <f>E37-E36</f>
         <v/>
       </c>
-      <c r="G37" s="15">
+      <c r="G37" s="16">
         <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E37),0)</f>
         <v/>
       </c>
@@ -11428,7 +13331,7 @@
         <f>G37-H37</f>
         <v/>
       </c>
-      <c r="J37" s="15">
+      <c r="J37" s="16">
         <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E37),0))*Paramètres!$B$3</f>
         <v/>
       </c>
@@ -11461,7 +13364,7 @@
         <f>E38-E37</f>
         <v/>
       </c>
-      <c r="G38" s="15">
+      <c r="G38" s="16">
         <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E38),0)</f>
         <v/>
       </c>
@@ -11473,7 +13376,7 @@
         <f>G38-H38</f>
         <v/>
       </c>
-      <c r="J38" s="15">
+      <c r="J38" s="16">
         <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E38),0))*Paramètres!$B$3</f>
         <v/>
       </c>
@@ -11506,7 +13409,7 @@
         <f>E39-E38</f>
         <v/>
       </c>
-      <c r="G39" s="15">
+      <c r="G39" s="16">
         <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E39),0)</f>
         <v/>
       </c>
@@ -11518,7 +13421,7 @@
         <f>G39-H39</f>
         <v/>
       </c>
-      <c r="J39" s="15">
+      <c r="J39" s="16">
         <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E39),0))*Paramètres!$B$3</f>
         <v/>
       </c>
@@ -11551,7 +13454,7 @@
         <f>E40-E39</f>
         <v/>
       </c>
-      <c r="G40" s="15">
+      <c r="G40" s="16">
         <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E40),0)</f>
         <v/>
       </c>
@@ -11563,7 +13466,7 @@
         <f>G40-H40</f>
         <v/>
       </c>
-      <c r="J40" s="15">
+      <c r="J40" s="16">
         <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E40),0))*Paramètres!$B$3</f>
         <v/>
       </c>
@@ -11596,7 +13499,7 @@
         <f>E41-E40</f>
         <v/>
       </c>
-      <c r="G41" s="15">
+      <c r="G41" s="16">
         <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E41),0)</f>
         <v/>
       </c>
@@ -11608,7 +13511,7 @@
         <f>G41-H41</f>
         <v/>
       </c>
-      <c r="J41" s="15">
+      <c r="J41" s="16">
         <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E41),0))*Paramètres!$B$3</f>
         <v/>
       </c>
@@ -11641,7 +13544,7 @@
         <f>E42-E41</f>
         <v/>
       </c>
-      <c r="G42" s="15">
+      <c r="G42" s="16">
         <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E42),0)</f>
         <v/>
       </c>
@@ -11653,7 +13556,7 @@
         <f>G42-H42</f>
         <v/>
       </c>
-      <c r="J42" s="15">
+      <c r="J42" s="16">
         <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E42),0))*Paramètres!$B$3</f>
         <v/>
       </c>
@@ -11686,7 +13589,7 @@
         <f>E43-E42</f>
         <v/>
       </c>
-      <c r="G43" s="15">
+      <c r="G43" s="16">
         <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E43),0)</f>
         <v/>
       </c>
@@ -11698,7 +13601,7 @@
         <f>G43-H43</f>
         <v/>
       </c>
-      <c r="J43" s="15">
+      <c r="J43" s="16">
         <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E43),0))*Paramètres!$B$3</f>
         <v/>
       </c>
@@ -11731,7 +13634,7 @@
         <f>E44-E43</f>
         <v/>
       </c>
-      <c r="G44" s="15">
+      <c r="G44" s="16">
         <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E44),0)</f>
         <v/>
       </c>
@@ -11743,7 +13646,7 @@
         <f>G44-H44</f>
         <v/>
       </c>
-      <c r="J44" s="15">
+      <c r="J44" s="16">
         <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E44),0))*Paramètres!$B$3</f>
         <v/>
       </c>
@@ -11776,7 +13679,7 @@
         <f>E45-E44</f>
         <v/>
       </c>
-      <c r="G45" s="15">
+      <c r="G45" s="16">
         <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E45),0)</f>
         <v/>
       </c>
@@ -11788,7 +13691,7 @@
         <f>G45-H45</f>
         <v/>
       </c>
-      <c r="J45" s="15">
+      <c r="J45" s="16">
         <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E45),0))*Paramètres!$B$3</f>
         <v/>
       </c>
@@ -11821,7 +13724,7 @@
         <f>E46-E45</f>
         <v/>
       </c>
-      <c r="G46" s="15">
+      <c r="G46" s="16">
         <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E46),0)</f>
         <v/>
       </c>
@@ -11833,7 +13736,7 @@
         <f>G46-H46</f>
         <v/>
       </c>
-      <c r="J46" s="15">
+      <c r="J46" s="16">
         <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E46),0))*Paramètres!$B$3</f>
         <v/>
       </c>
@@ -11866,7 +13769,7 @@
         <f>E47-E46</f>
         <v/>
       </c>
-      <c r="G47" s="15">
+      <c r="G47" s="16">
         <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E47),0)</f>
         <v/>
       </c>
@@ -11878,7 +13781,7 @@
         <f>G47-H47</f>
         <v/>
       </c>
-      <c r="J47" s="15">
+      <c r="J47" s="16">
         <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E47),0))*Paramètres!$B$3</f>
         <v/>
       </c>
@@ -11911,7 +13814,7 @@
         <f>E48-E47</f>
         <v/>
       </c>
-      <c r="G48" s="15">
+      <c r="G48" s="16">
         <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E48),0)</f>
         <v/>
       </c>
@@ -11923,7 +13826,7 @@
         <f>G48-H48</f>
         <v/>
       </c>
-      <c r="J48" s="15">
+      <c r="J48" s="16">
         <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E48),0))*Paramètres!$B$3</f>
         <v/>
       </c>
@@ -11956,7 +13859,7 @@
         <f>E49-E48</f>
         <v/>
       </c>
-      <c r="G49" s="15">
+      <c r="G49" s="16">
         <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E49),0)</f>
         <v/>
       </c>
@@ -11968,7 +13871,7 @@
         <f>G49-H49</f>
         <v/>
       </c>
-      <c r="J49" s="15">
+      <c r="J49" s="16">
         <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E49),0))*Paramètres!$B$3</f>
         <v/>
       </c>
@@ -12001,7 +13904,7 @@
         <f>E50-E49</f>
         <v/>
       </c>
-      <c r="G50" s="15">
+      <c r="G50" s="16">
         <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E50),0)</f>
         <v/>
       </c>
@@ -12013,7 +13916,7 @@
         <f>G50-H50</f>
         <v/>
       </c>
-      <c r="J50" s="15">
+      <c r="J50" s="16">
         <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E50),0))*Paramètres!$B$3</f>
         <v/>
       </c>
@@ -12046,7 +13949,7 @@
         <f>E51-E50</f>
         <v/>
       </c>
-      <c r="G51" s="15">
+      <c r="G51" s="16">
         <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E51),0)</f>
         <v/>
       </c>
@@ -12058,7 +13961,7 @@
         <f>G51-H51</f>
         <v/>
       </c>
-      <c r="J51" s="15">
+      <c r="J51" s="16">
         <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E51),0))*Paramètres!$B$3</f>
         <v/>
       </c>
@@ -12091,7 +13994,7 @@
         <f>E52-E51</f>
         <v/>
       </c>
-      <c r="G52" s="15">
+      <c r="G52" s="16">
         <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E52),0)</f>
         <v/>
       </c>
@@ -12103,7 +14006,7 @@
         <f>G52-H52</f>
         <v/>
       </c>
-      <c r="J52" s="15">
+      <c r="J52" s="16">
         <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E52),0))*Paramètres!$B$3</f>
         <v/>
       </c>
@@ -12136,7 +14039,7 @@
         <f>E53-E52</f>
         <v/>
       </c>
-      <c r="G53" s="15">
+      <c r="G53" s="16">
         <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E53),0)</f>
         <v/>
       </c>
@@ -12148,7 +14051,7 @@
         <f>G53-H53</f>
         <v/>
       </c>
-      <c r="J53" s="15">
+      <c r="J53" s="16">
         <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E53),0))*Paramètres!$B$3</f>
         <v/>
       </c>
@@ -12181,7 +14084,7 @@
         <f>E54-E53</f>
         <v/>
       </c>
-      <c r="G54" s="15">
+      <c r="G54" s="16">
         <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E54),0)</f>
         <v/>
       </c>
@@ -12193,7 +14096,7 @@
         <f>G54-H54</f>
         <v/>
       </c>
-      <c r="J54" s="15">
+      <c r="J54" s="16">
         <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E54),0))*Paramètres!$B$3</f>
         <v/>
       </c>
@@ -12226,7 +14129,7 @@
         <f>E55-E54</f>
         <v/>
       </c>
-      <c r="G55" s="15">
+      <c r="G55" s="16">
         <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E55),0)</f>
         <v/>
       </c>
@@ -12238,7 +14141,7 @@
         <f>G55-H55</f>
         <v/>
       </c>
-      <c r="J55" s="15">
+      <c r="J55" s="16">
         <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E55),0))*Paramètres!$B$3</f>
         <v/>
       </c>
@@ -12271,7 +14174,7 @@
         <f>E56-E55</f>
         <v/>
       </c>
-      <c r="G56" s="15">
+      <c r="G56" s="16">
         <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E56),0)</f>
         <v/>
       </c>
@@ -12283,7 +14186,7 @@
         <f>G56-H56</f>
         <v/>
       </c>
-      <c r="J56" s="15">
+      <c r="J56" s="16">
         <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E56),0))*Paramètres!$B$3</f>
         <v/>
       </c>
@@ -12316,7 +14219,7 @@
         <f>E57-E56</f>
         <v/>
       </c>
-      <c r="G57" s="15">
+      <c r="G57" s="16">
         <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E57),0)</f>
         <v/>
       </c>
@@ -12328,7 +14231,7 @@
         <f>G57-H57</f>
         <v/>
       </c>
-      <c r="J57" s="15">
+      <c r="J57" s="16">
         <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E57),0))*Paramètres!$B$3</f>
         <v/>
       </c>
@@ -12361,7 +14264,7 @@
         <f>E58-E57</f>
         <v/>
       </c>
-      <c r="G58" s="15">
+      <c r="G58" s="16">
         <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E58),0)</f>
         <v/>
       </c>
@@ -12373,7 +14276,7 @@
         <f>G58-H58</f>
         <v/>
       </c>
-      <c r="J58" s="15">
+      <c r="J58" s="16">
         <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E58),0))*Paramètres!$B$3</f>
         <v/>
       </c>
@@ -12406,7 +14309,7 @@
         <f>E59-E58</f>
         <v/>
       </c>
-      <c r="G59" s="15">
+      <c r="G59" s="16">
         <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E59),0)</f>
         <v/>
       </c>
@@ -12418,7 +14321,7 @@
         <f>G59-H59</f>
         <v/>
       </c>
-      <c r="J59" s="15">
+      <c r="J59" s="16">
         <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E59),0))*Paramètres!$B$3</f>
         <v/>
       </c>
@@ -12451,7 +14354,7 @@
         <f>E60-E59</f>
         <v/>
       </c>
-      <c r="G60" s="15">
+      <c r="G60" s="16">
         <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E60),0)</f>
         <v/>
       </c>
@@ -12463,7 +14366,7 @@
         <f>G60-H60</f>
         <v/>
       </c>
-      <c r="J60" s="15">
+      <c r="J60" s="16">
         <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E60),0))*Paramètres!$B$3</f>
         <v/>
       </c>
@@ -12496,7 +14399,7 @@
         <f>E61-E60</f>
         <v/>
       </c>
-      <c r="G61" s="15">
+      <c r="G61" s="16">
         <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E61),0)</f>
         <v/>
       </c>
@@ -12508,7 +14411,7 @@
         <f>G61-H61</f>
         <v/>
       </c>
-      <c r="J61" s="15">
+      <c r="J61" s="16">
         <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E61),0))*Paramètres!$B$3</f>
         <v/>
       </c>
@@ -12532,7 +14435,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="17" t="inlineStr">
         <is>
           <t>Graphiques (se redessinent avec les paramètres)</t>
         </is>

--- a/docs/plan-scaling-diversifie.xlsx
+++ b/docs/plan-scaling-diversifie.xlsx
@@ -254,7 +254,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Simulation'!H1</f>
+              <f>'Simulation'!F1</f>
             </strRef>
           </tx>
           <spPr>
@@ -277,7 +277,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Simulation'!$H$2:$H$61</f>
+              <f>'Simulation'!$F$2:$F$61</f>
             </numRef>
           </val>
         </ser>
@@ -286,7 +286,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Simulation'!I1</f>
+              <f>'Simulation'!G1</f>
             </strRef>
           </tx>
           <spPr>
@@ -309,7 +309,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Simulation'!$I$2:$I$61</f>
+              <f>'Simulation'!$G$2:$G$61</f>
             </numRef>
           </val>
         </ser>
@@ -390,7 +390,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Revenu mensuel potentiel</a:t>
+              <a:t>Revenu mensuel net</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -522,7 +522,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Simulation'!E1</f>
+              <f>'Simulation'!B1</f>
             </strRef>
           </tx>
           <spPr>
@@ -545,7 +545,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Simulation'!$E$2:$E$61</f>
+              <f>'Simulation'!$B$2:$B$61</f>
             </numRef>
           </val>
         </ser>
@@ -11647,20 +11647,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K61"/>
+  <dimension ref="A1:J61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -11671,52 +11670,47 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>Capital financé début ($)</t>
+          <t>Firmes détenues ce mois</t>
         </is>
       </c>
       <c r="C1" s="9" t="inlineStr">
         <is>
+          <t>Capital financé actif ($)</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>Payout brut du mois ($)</t>
+        </is>
+      </c>
+      <c r="E1" s="9" t="inlineStr">
+        <is>
           <t>Payout net du mois ($)</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
-        <is>
-          <t>Réinvesti cumulé ($)</t>
-        </is>
-      </c>
-      <c r="E1" s="9" t="inlineStr">
-        <is>
-          <t>Firmes détenues</t>
-        </is>
-      </c>
       <c r="F1" s="9" t="inlineStr">
         <is>
+          <t>dont CFD ($)</t>
+        </is>
+      </c>
+      <c r="G1" s="9" t="inlineStr">
+        <is>
+          <t>dont Futures ($)</t>
+        </is>
+      </c>
+      <c r="H1" s="9" t="inlineStr">
+        <is>
+          <t>Payout net cumulé ($)</t>
+        </is>
+      </c>
+      <c r="I1" s="9" t="inlineStr">
+        <is>
           <t>Nouvelles firmes ce mois</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
-        <is>
-          <t>Capital financé fin ($)</t>
-        </is>
-      </c>
-      <c r="H1" s="9" t="inlineStr">
-        <is>
-          <t>dont CFD ($)</t>
-        </is>
-      </c>
-      <c r="I1" s="9" t="inlineStr">
-        <is>
-          <t>dont Futures ($)</t>
-        </is>
-      </c>
       <c r="J1" s="9" t="inlineStr">
         <is>
-          <t>Revenu mensuel potentiel ($)</t>
-        </is>
-      </c>
-      <c r="K1" s="9" t="inlineStr">
-        <is>
-          <t>Trésorerie ($)</t>
+          <t>Revenu mensuel net ($)</t>
         </is>
       </c>
     </row>
@@ -11724,44 +11718,40 @@
       <c r="A2" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="12">
-        <f>Paramètres!$B$5</f>
-        <v/>
-      </c>
-      <c r="C2" s="12">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,0),0))*Paramètres!$B$3</f>
+      <c r="B2" s="10">
+        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;0))</f>
+        <v/>
+      </c>
+      <c r="C2" s="16">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,B2),0)</f>
         <v/>
       </c>
       <c r="D2" s="12">
-        <f>C2</f>
-        <v/>
-      </c>
-      <c r="E2" s="10">
-        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;D2))</f>
-        <v/>
-      </c>
-      <c r="F2" s="10">
-        <f>E2-0</f>
-        <v/>
-      </c>
-      <c r="G2" s="16">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E2),0)</f>
+        <f>C2*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="E2" s="16">
+        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,B2),0))*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="F2" s="12">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(B2,160)),0)</f>
+        <v/>
+      </c>
+      <c r="G2" s="12">
+        <f>C2-F2</f>
         <v/>
       </c>
       <c r="H2" s="12">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(E2,160)),0)</f>
-        <v/>
-      </c>
-      <c r="I2" s="12">
-        <f>G2-H2</f>
-        <v/>
-      </c>
-      <c r="J2" s="16">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E2),0))*Paramètres!$B$3</f>
-        <v/>
-      </c>
-      <c r="K2" s="12">
-        <f>D2-IFERROR(INDEX('Plan d''achat'!$K$2:$K$190,E2),0)</f>
+        <f>E2</f>
+        <v/>
+      </c>
+      <c r="I2" s="10">
+        <f>B2</f>
+        <v/>
+      </c>
+      <c r="J2" s="12">
+        <f>E2</f>
         <v/>
       </c>
     </row>
@@ -11769,44 +11759,40 @@
       <c r="A3" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="12">
-        <f>G2</f>
-        <v/>
-      </c>
-      <c r="C3" s="12">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E2),0))*Paramètres!$B$3</f>
+      <c r="B3" s="10">
+        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;H2))</f>
+        <v/>
+      </c>
+      <c r="C3" s="16">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,B3),0)</f>
         <v/>
       </c>
       <c r="D3" s="12">
-        <f>D2+C3</f>
-        <v/>
-      </c>
-      <c r="E3" s="10">
-        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;D3))</f>
-        <v/>
-      </c>
-      <c r="F3" s="10">
-        <f>E3-E2</f>
-        <v/>
-      </c>
-      <c r="G3" s="16">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E3),0)</f>
+        <f>C3*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="E3" s="16">
+        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,B3),0))*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="F3" s="12">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(B3,160)),0)</f>
+        <v/>
+      </c>
+      <c r="G3" s="12">
+        <f>C3-F3</f>
         <v/>
       </c>
       <c r="H3" s="12">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(E3,160)),0)</f>
-        <v/>
-      </c>
-      <c r="I3" s="12">
-        <f>G3-H3</f>
-        <v/>
-      </c>
-      <c r="J3" s="16">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E3),0))*Paramètres!$B$3</f>
-        <v/>
-      </c>
-      <c r="K3" s="12">
-        <f>D3-IFERROR(INDEX('Plan d''achat'!$K$2:$K$190,E3),0)</f>
+        <f>H2+E3</f>
+        <v/>
+      </c>
+      <c r="I3" s="10">
+        <f>B3-B2</f>
+        <v/>
+      </c>
+      <c r="J3" s="12">
+        <f>E3</f>
         <v/>
       </c>
     </row>
@@ -11814,44 +11800,40 @@
       <c r="A4" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="12">
-        <f>G3</f>
-        <v/>
-      </c>
-      <c r="C4" s="12">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E3),0))*Paramètres!$B$3</f>
+      <c r="B4" s="10">
+        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;H3))</f>
+        <v/>
+      </c>
+      <c r="C4" s="16">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,B4),0)</f>
         <v/>
       </c>
       <c r="D4" s="12">
-        <f>D3+C4</f>
-        <v/>
-      </c>
-      <c r="E4" s="10">
-        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;D4))</f>
-        <v/>
-      </c>
-      <c r="F4" s="10">
-        <f>E4-E3</f>
-        <v/>
-      </c>
-      <c r="G4" s="16">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E4),0)</f>
+        <f>C4*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="E4" s="16">
+        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,B4),0))*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="F4" s="12">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(B4,160)),0)</f>
+        <v/>
+      </c>
+      <c r="G4" s="12">
+        <f>C4-F4</f>
         <v/>
       </c>
       <c r="H4" s="12">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(E4,160)),0)</f>
-        <v/>
-      </c>
-      <c r="I4" s="12">
-        <f>G4-H4</f>
-        <v/>
-      </c>
-      <c r="J4" s="16">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E4),0))*Paramètres!$B$3</f>
-        <v/>
-      </c>
-      <c r="K4" s="12">
-        <f>D4-IFERROR(INDEX('Plan d''achat'!$K$2:$K$190,E4),0)</f>
+        <f>H3+E4</f>
+        <v/>
+      </c>
+      <c r="I4" s="10">
+        <f>B4-B3</f>
+        <v/>
+      </c>
+      <c r="J4" s="12">
+        <f>E4</f>
         <v/>
       </c>
     </row>
@@ -11859,44 +11841,40 @@
       <c r="A5" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="12">
-        <f>G4</f>
-        <v/>
-      </c>
-      <c r="C5" s="12">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E4),0))*Paramètres!$B$3</f>
+      <c r="B5" s="10">
+        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;H4))</f>
+        <v/>
+      </c>
+      <c r="C5" s="16">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,B5),0)</f>
         <v/>
       </c>
       <c r="D5" s="12">
-        <f>D4+C5</f>
-        <v/>
-      </c>
-      <c r="E5" s="10">
-        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;D5))</f>
-        <v/>
-      </c>
-      <c r="F5" s="10">
-        <f>E5-E4</f>
-        <v/>
-      </c>
-      <c r="G5" s="16">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E5),0)</f>
+        <f>C5*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="E5" s="16">
+        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,B5),0))*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="F5" s="12">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(B5,160)),0)</f>
+        <v/>
+      </c>
+      <c r="G5" s="12">
+        <f>C5-F5</f>
         <v/>
       </c>
       <c r="H5" s="12">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(E5,160)),0)</f>
-        <v/>
-      </c>
-      <c r="I5" s="12">
-        <f>G5-H5</f>
-        <v/>
-      </c>
-      <c r="J5" s="16">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E5),0))*Paramètres!$B$3</f>
-        <v/>
-      </c>
-      <c r="K5" s="12">
-        <f>D5-IFERROR(INDEX('Plan d''achat'!$K$2:$K$190,E5),0)</f>
+        <f>H4+E5</f>
+        <v/>
+      </c>
+      <c r="I5" s="10">
+        <f>B5-B4</f>
+        <v/>
+      </c>
+      <c r="J5" s="12">
+        <f>E5</f>
         <v/>
       </c>
     </row>
@@ -11904,44 +11882,40 @@
       <c r="A6" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="12">
-        <f>G5</f>
-        <v/>
-      </c>
-      <c r="C6" s="12">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E5),0))*Paramètres!$B$3</f>
+      <c r="B6" s="10">
+        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;H5))</f>
+        <v/>
+      </c>
+      <c r="C6" s="16">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,B6),0)</f>
         <v/>
       </c>
       <c r="D6" s="12">
-        <f>D5+C6</f>
-        <v/>
-      </c>
-      <c r="E6" s="10">
-        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;D6))</f>
-        <v/>
-      </c>
-      <c r="F6" s="10">
-        <f>E6-E5</f>
-        <v/>
-      </c>
-      <c r="G6" s="16">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E6),0)</f>
+        <f>C6*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="E6" s="16">
+        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,B6),0))*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="F6" s="12">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(B6,160)),0)</f>
+        <v/>
+      </c>
+      <c r="G6" s="12">
+        <f>C6-F6</f>
         <v/>
       </c>
       <c r="H6" s="12">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(E6,160)),0)</f>
-        <v/>
-      </c>
-      <c r="I6" s="12">
-        <f>G6-H6</f>
-        <v/>
-      </c>
-      <c r="J6" s="16">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E6),0))*Paramètres!$B$3</f>
-        <v/>
-      </c>
-      <c r="K6" s="12">
-        <f>D6-IFERROR(INDEX('Plan d''achat'!$K$2:$K$190,E6),0)</f>
+        <f>H5+E6</f>
+        <v/>
+      </c>
+      <c r="I6" s="10">
+        <f>B6-B5</f>
+        <v/>
+      </c>
+      <c r="J6" s="12">
+        <f>E6</f>
         <v/>
       </c>
     </row>
@@ -11949,44 +11923,40 @@
       <c r="A7" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="12">
-        <f>G6</f>
-        <v/>
-      </c>
-      <c r="C7" s="12">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E6),0))*Paramètres!$B$3</f>
+      <c r="B7" s="10">
+        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;H6))</f>
+        <v/>
+      </c>
+      <c r="C7" s="16">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,B7),0)</f>
         <v/>
       </c>
       <c r="D7" s="12">
-        <f>D6+C7</f>
-        <v/>
-      </c>
-      <c r="E7" s="10">
-        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;D7))</f>
-        <v/>
-      </c>
-      <c r="F7" s="10">
-        <f>E7-E6</f>
-        <v/>
-      </c>
-      <c r="G7" s="16">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E7),0)</f>
+        <f>C7*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="E7" s="16">
+        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,B7),0))*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="F7" s="12">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(B7,160)),0)</f>
+        <v/>
+      </c>
+      <c r="G7" s="12">
+        <f>C7-F7</f>
         <v/>
       </c>
       <c r="H7" s="12">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(E7,160)),0)</f>
-        <v/>
-      </c>
-      <c r="I7" s="12">
-        <f>G7-H7</f>
-        <v/>
-      </c>
-      <c r="J7" s="16">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E7),0))*Paramètres!$B$3</f>
-        <v/>
-      </c>
-      <c r="K7" s="12">
-        <f>D7-IFERROR(INDEX('Plan d''achat'!$K$2:$K$190,E7),0)</f>
+        <f>H6+E7</f>
+        <v/>
+      </c>
+      <c r="I7" s="10">
+        <f>B7-B6</f>
+        <v/>
+      </c>
+      <c r="J7" s="12">
+        <f>E7</f>
         <v/>
       </c>
     </row>
@@ -11994,44 +11964,40 @@
       <c r="A8" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="12">
-        <f>G7</f>
-        <v/>
-      </c>
-      <c r="C8" s="12">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E7),0))*Paramètres!$B$3</f>
+      <c r="B8" s="10">
+        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;H7))</f>
+        <v/>
+      </c>
+      <c r="C8" s="16">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,B8),0)</f>
         <v/>
       </c>
       <c r="D8" s="12">
-        <f>D7+C8</f>
-        <v/>
-      </c>
-      <c r="E8" s="10">
-        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;D8))</f>
-        <v/>
-      </c>
-      <c r="F8" s="10">
-        <f>E8-E7</f>
-        <v/>
-      </c>
-      <c r="G8" s="16">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E8),0)</f>
+        <f>C8*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="E8" s="16">
+        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,B8),0))*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="F8" s="12">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(B8,160)),0)</f>
+        <v/>
+      </c>
+      <c r="G8" s="12">
+        <f>C8-F8</f>
         <v/>
       </c>
       <c r="H8" s="12">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(E8,160)),0)</f>
-        <v/>
-      </c>
-      <c r="I8" s="12">
-        <f>G8-H8</f>
-        <v/>
-      </c>
-      <c r="J8" s="16">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E8),0))*Paramètres!$B$3</f>
-        <v/>
-      </c>
-      <c r="K8" s="12">
-        <f>D8-IFERROR(INDEX('Plan d''achat'!$K$2:$K$190,E8),0)</f>
+        <f>H7+E8</f>
+        <v/>
+      </c>
+      <c r="I8" s="10">
+        <f>B8-B7</f>
+        <v/>
+      </c>
+      <c r="J8" s="12">
+        <f>E8</f>
         <v/>
       </c>
     </row>
@@ -12039,44 +12005,40 @@
       <c r="A9" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="12">
-        <f>G8</f>
-        <v/>
-      </c>
-      <c r="C9" s="12">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E8),0))*Paramètres!$B$3</f>
+      <c r="B9" s="10">
+        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;H8))</f>
+        <v/>
+      </c>
+      <c r="C9" s="16">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,B9),0)</f>
         <v/>
       </c>
       <c r="D9" s="12">
-        <f>D8+C9</f>
-        <v/>
-      </c>
-      <c r="E9" s="10">
-        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;D9))</f>
-        <v/>
-      </c>
-      <c r="F9" s="10">
-        <f>E9-E8</f>
-        <v/>
-      </c>
-      <c r="G9" s="16">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E9),0)</f>
+        <f>C9*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="E9" s="16">
+        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,B9),0))*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="F9" s="12">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(B9,160)),0)</f>
+        <v/>
+      </c>
+      <c r="G9" s="12">
+        <f>C9-F9</f>
         <v/>
       </c>
       <c r="H9" s="12">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(E9,160)),0)</f>
-        <v/>
-      </c>
-      <c r="I9" s="12">
-        <f>G9-H9</f>
-        <v/>
-      </c>
-      <c r="J9" s="16">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E9),0))*Paramètres!$B$3</f>
-        <v/>
-      </c>
-      <c r="K9" s="12">
-        <f>D9-IFERROR(INDEX('Plan d''achat'!$K$2:$K$190,E9),0)</f>
+        <f>H8+E9</f>
+        <v/>
+      </c>
+      <c r="I9" s="10">
+        <f>B9-B8</f>
+        <v/>
+      </c>
+      <c r="J9" s="12">
+        <f>E9</f>
         <v/>
       </c>
     </row>
@@ -12084,44 +12046,40 @@
       <c r="A10" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="12">
-        <f>G9</f>
-        <v/>
-      </c>
-      <c r="C10" s="12">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E9),0))*Paramètres!$B$3</f>
+      <c r="B10" s="10">
+        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;H9))</f>
+        <v/>
+      </c>
+      <c r="C10" s="16">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,B10),0)</f>
         <v/>
       </c>
       <c r="D10" s="12">
-        <f>D9+C10</f>
-        <v/>
-      </c>
-      <c r="E10" s="10">
-        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;D10))</f>
-        <v/>
-      </c>
-      <c r="F10" s="10">
-        <f>E10-E9</f>
-        <v/>
-      </c>
-      <c r="G10" s="16">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E10),0)</f>
+        <f>C10*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="E10" s="16">
+        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,B10),0))*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="F10" s="12">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(B10,160)),0)</f>
+        <v/>
+      </c>
+      <c r="G10" s="12">
+        <f>C10-F10</f>
         <v/>
       </c>
       <c r="H10" s="12">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(E10,160)),0)</f>
-        <v/>
-      </c>
-      <c r="I10" s="12">
-        <f>G10-H10</f>
-        <v/>
-      </c>
-      <c r="J10" s="16">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E10),0))*Paramètres!$B$3</f>
-        <v/>
-      </c>
-      <c r="K10" s="12">
-        <f>D10-IFERROR(INDEX('Plan d''achat'!$K$2:$K$190,E10),0)</f>
+        <f>H9+E10</f>
+        <v/>
+      </c>
+      <c r="I10" s="10">
+        <f>B10-B9</f>
+        <v/>
+      </c>
+      <c r="J10" s="12">
+        <f>E10</f>
         <v/>
       </c>
     </row>
@@ -12129,44 +12087,40 @@
       <c r="A11" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="12">
-        <f>G10</f>
-        <v/>
-      </c>
-      <c r="C11" s="12">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E10),0))*Paramètres!$B$3</f>
+      <c r="B11" s="10">
+        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;H10))</f>
+        <v/>
+      </c>
+      <c r="C11" s="16">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,B11),0)</f>
         <v/>
       </c>
       <c r="D11" s="12">
-        <f>D10+C11</f>
-        <v/>
-      </c>
-      <c r="E11" s="10">
-        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;D11))</f>
-        <v/>
-      </c>
-      <c r="F11" s="10">
-        <f>E11-E10</f>
-        <v/>
-      </c>
-      <c r="G11" s="16">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E11),0)</f>
+        <f>C11*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="E11" s="16">
+        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,B11),0))*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="F11" s="12">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(B11,160)),0)</f>
+        <v/>
+      </c>
+      <c r="G11" s="12">
+        <f>C11-F11</f>
         <v/>
       </c>
       <c r="H11" s="12">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(E11,160)),0)</f>
-        <v/>
-      </c>
-      <c r="I11" s="12">
-        <f>G11-H11</f>
-        <v/>
-      </c>
-      <c r="J11" s="16">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E11),0))*Paramètres!$B$3</f>
-        <v/>
-      </c>
-      <c r="K11" s="12">
-        <f>D11-IFERROR(INDEX('Plan d''achat'!$K$2:$K$190,E11),0)</f>
+        <f>H10+E11</f>
+        <v/>
+      </c>
+      <c r="I11" s="10">
+        <f>B11-B10</f>
+        <v/>
+      </c>
+      <c r="J11" s="12">
+        <f>E11</f>
         <v/>
       </c>
     </row>
@@ -12174,44 +12128,40 @@
       <c r="A12" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="12">
-        <f>G11</f>
-        <v/>
-      </c>
-      <c r="C12" s="12">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E11),0))*Paramètres!$B$3</f>
+      <c r="B12" s="10">
+        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;H11))</f>
+        <v/>
+      </c>
+      <c r="C12" s="16">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,B12),0)</f>
         <v/>
       </c>
       <c r="D12" s="12">
-        <f>D11+C12</f>
-        <v/>
-      </c>
-      <c r="E12" s="10">
-        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;D12))</f>
-        <v/>
-      </c>
-      <c r="F12" s="10">
-        <f>E12-E11</f>
-        <v/>
-      </c>
-      <c r="G12" s="16">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E12),0)</f>
+        <f>C12*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="E12" s="16">
+        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,B12),0))*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="F12" s="12">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(B12,160)),0)</f>
+        <v/>
+      </c>
+      <c r="G12" s="12">
+        <f>C12-F12</f>
         <v/>
       </c>
       <c r="H12" s="12">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(E12,160)),0)</f>
-        <v/>
-      </c>
-      <c r="I12" s="12">
-        <f>G12-H12</f>
-        <v/>
-      </c>
-      <c r="J12" s="16">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E12),0))*Paramètres!$B$3</f>
-        <v/>
-      </c>
-      <c r="K12" s="12">
-        <f>D12-IFERROR(INDEX('Plan d''achat'!$K$2:$K$190,E12),0)</f>
+        <f>H11+E12</f>
+        <v/>
+      </c>
+      <c r="I12" s="10">
+        <f>B12-B11</f>
+        <v/>
+      </c>
+      <c r="J12" s="12">
+        <f>E12</f>
         <v/>
       </c>
     </row>
@@ -12219,44 +12169,40 @@
       <c r="A13" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="12">
-        <f>G12</f>
-        <v/>
-      </c>
-      <c r="C13" s="12">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E12),0))*Paramètres!$B$3</f>
+      <c r="B13" s="10">
+        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;H12))</f>
+        <v/>
+      </c>
+      <c r="C13" s="16">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,B13),0)</f>
         <v/>
       </c>
       <c r="D13" s="12">
-        <f>D12+C13</f>
-        <v/>
-      </c>
-      <c r="E13" s="10">
-        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;D13))</f>
-        <v/>
-      </c>
-      <c r="F13" s="10">
-        <f>E13-E12</f>
-        <v/>
-      </c>
-      <c r="G13" s="16">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E13),0)</f>
+        <f>C13*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="E13" s="16">
+        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,B13),0))*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="F13" s="12">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(B13,160)),0)</f>
+        <v/>
+      </c>
+      <c r="G13" s="12">
+        <f>C13-F13</f>
         <v/>
       </c>
       <c r="H13" s="12">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(E13,160)),0)</f>
-        <v/>
-      </c>
-      <c r="I13" s="12">
-        <f>G13-H13</f>
-        <v/>
-      </c>
-      <c r="J13" s="16">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E13),0))*Paramètres!$B$3</f>
-        <v/>
-      </c>
-      <c r="K13" s="12">
-        <f>D13-IFERROR(INDEX('Plan d''achat'!$K$2:$K$190,E13),0)</f>
+        <f>H12+E13</f>
+        <v/>
+      </c>
+      <c r="I13" s="10">
+        <f>B13-B12</f>
+        <v/>
+      </c>
+      <c r="J13" s="12">
+        <f>E13</f>
         <v/>
       </c>
     </row>
@@ -12264,44 +12210,40 @@
       <c r="A14" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="12">
-        <f>G13</f>
-        <v/>
-      </c>
-      <c r="C14" s="12">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E13),0))*Paramètres!$B$3</f>
+      <c r="B14" s="10">
+        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;H13))</f>
+        <v/>
+      </c>
+      <c r="C14" s="16">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,B14),0)</f>
         <v/>
       </c>
       <c r="D14" s="12">
-        <f>D13+C14</f>
-        <v/>
-      </c>
-      <c r="E14" s="10">
-        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;D14))</f>
-        <v/>
-      </c>
-      <c r="F14" s="10">
-        <f>E14-E13</f>
-        <v/>
-      </c>
-      <c r="G14" s="16">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E14),0)</f>
+        <f>C14*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="E14" s="16">
+        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,B14),0))*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="F14" s="12">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(B14,160)),0)</f>
+        <v/>
+      </c>
+      <c r="G14" s="12">
+        <f>C14-F14</f>
         <v/>
       </c>
       <c r="H14" s="12">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(E14,160)),0)</f>
-        <v/>
-      </c>
-      <c r="I14" s="12">
-        <f>G14-H14</f>
-        <v/>
-      </c>
-      <c r="J14" s="16">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E14),0))*Paramètres!$B$3</f>
-        <v/>
-      </c>
-      <c r="K14" s="12">
-        <f>D14-IFERROR(INDEX('Plan d''achat'!$K$2:$K$190,E14),0)</f>
+        <f>H13+E14</f>
+        <v/>
+      </c>
+      <c r="I14" s="10">
+        <f>B14-B13</f>
+        <v/>
+      </c>
+      <c r="J14" s="12">
+        <f>E14</f>
         <v/>
       </c>
     </row>
@@ -12309,44 +12251,40 @@
       <c r="A15" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="12">
-        <f>G14</f>
-        <v/>
-      </c>
-      <c r="C15" s="12">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E14),0))*Paramètres!$B$3</f>
+      <c r="B15" s="10">
+        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;H14))</f>
+        <v/>
+      </c>
+      <c r="C15" s="16">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,B15),0)</f>
         <v/>
       </c>
       <c r="D15" s="12">
-        <f>D14+C15</f>
-        <v/>
-      </c>
-      <c r="E15" s="10">
-        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;D15))</f>
-        <v/>
-      </c>
-      <c r="F15" s="10">
-        <f>E15-E14</f>
-        <v/>
-      </c>
-      <c r="G15" s="16">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E15),0)</f>
+        <f>C15*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="E15" s="16">
+        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,B15),0))*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="F15" s="12">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(B15,160)),0)</f>
+        <v/>
+      </c>
+      <c r="G15" s="12">
+        <f>C15-F15</f>
         <v/>
       </c>
       <c r="H15" s="12">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(E15,160)),0)</f>
-        <v/>
-      </c>
-      <c r="I15" s="12">
-        <f>G15-H15</f>
-        <v/>
-      </c>
-      <c r="J15" s="16">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E15),0))*Paramètres!$B$3</f>
-        <v/>
-      </c>
-      <c r="K15" s="12">
-        <f>D15-IFERROR(INDEX('Plan d''achat'!$K$2:$K$190,E15),0)</f>
+        <f>H14+E15</f>
+        <v/>
+      </c>
+      <c r="I15" s="10">
+        <f>B15-B14</f>
+        <v/>
+      </c>
+      <c r="J15" s="12">
+        <f>E15</f>
         <v/>
       </c>
     </row>
@@ -12354,44 +12292,40 @@
       <c r="A16" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="12">
-        <f>G15</f>
-        <v/>
-      </c>
-      <c r="C16" s="12">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E15),0))*Paramètres!$B$3</f>
+      <c r="B16" s="10">
+        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;H15))</f>
+        <v/>
+      </c>
+      <c r="C16" s="16">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,B16),0)</f>
         <v/>
       </c>
       <c r="D16" s="12">
-        <f>D15+C16</f>
-        <v/>
-      </c>
-      <c r="E16" s="10">
-        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;D16))</f>
-        <v/>
-      </c>
-      <c r="F16" s="10">
-        <f>E16-E15</f>
-        <v/>
-      </c>
-      <c r="G16" s="16">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E16),0)</f>
+        <f>C16*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="E16" s="16">
+        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,B16),0))*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="F16" s="12">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(B16,160)),0)</f>
+        <v/>
+      </c>
+      <c r="G16" s="12">
+        <f>C16-F16</f>
         <v/>
       </c>
       <c r="H16" s="12">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(E16,160)),0)</f>
-        <v/>
-      </c>
-      <c r="I16" s="12">
-        <f>G16-H16</f>
-        <v/>
-      </c>
-      <c r="J16" s="16">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E16),0))*Paramètres!$B$3</f>
-        <v/>
-      </c>
-      <c r="K16" s="12">
-        <f>D16-IFERROR(INDEX('Plan d''achat'!$K$2:$K$190,E16),0)</f>
+        <f>H15+E16</f>
+        <v/>
+      </c>
+      <c r="I16" s="10">
+        <f>B16-B15</f>
+        <v/>
+      </c>
+      <c r="J16" s="12">
+        <f>E16</f>
         <v/>
       </c>
     </row>
@@ -12399,44 +12333,40 @@
       <c r="A17" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="12">
-        <f>G16</f>
-        <v/>
-      </c>
-      <c r="C17" s="12">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E16),0))*Paramètres!$B$3</f>
+      <c r="B17" s="10">
+        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;H16))</f>
+        <v/>
+      </c>
+      <c r="C17" s="16">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,B17),0)</f>
         <v/>
       </c>
       <c r="D17" s="12">
-        <f>D16+C17</f>
-        <v/>
-      </c>
-      <c r="E17" s="10">
-        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;D17))</f>
-        <v/>
-      </c>
-      <c r="F17" s="10">
-        <f>E17-E16</f>
-        <v/>
-      </c>
-      <c r="G17" s="16">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E17),0)</f>
+        <f>C17*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="E17" s="16">
+        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,B17),0))*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="F17" s="12">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(B17,160)),0)</f>
+        <v/>
+      </c>
+      <c r="G17" s="12">
+        <f>C17-F17</f>
         <v/>
       </c>
       <c r="H17" s="12">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(E17,160)),0)</f>
-        <v/>
-      </c>
-      <c r="I17" s="12">
-        <f>G17-H17</f>
-        <v/>
-      </c>
-      <c r="J17" s="16">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E17),0))*Paramètres!$B$3</f>
-        <v/>
-      </c>
-      <c r="K17" s="12">
-        <f>D17-IFERROR(INDEX('Plan d''achat'!$K$2:$K$190,E17),0)</f>
+        <f>H16+E17</f>
+        <v/>
+      </c>
+      <c r="I17" s="10">
+        <f>B17-B16</f>
+        <v/>
+      </c>
+      <c r="J17" s="12">
+        <f>E17</f>
         <v/>
       </c>
     </row>
@@ -12444,44 +12374,40 @@
       <c r="A18" s="10" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="12">
-        <f>G17</f>
-        <v/>
-      </c>
-      <c r="C18" s="12">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E17),0))*Paramètres!$B$3</f>
+      <c r="B18" s="10">
+        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;H17))</f>
+        <v/>
+      </c>
+      <c r="C18" s="16">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,B18),0)</f>
         <v/>
       </c>
       <c r="D18" s="12">
-        <f>D17+C18</f>
-        <v/>
-      </c>
-      <c r="E18" s="10">
-        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;D18))</f>
-        <v/>
-      </c>
-      <c r="F18" s="10">
-        <f>E18-E17</f>
-        <v/>
-      </c>
-      <c r="G18" s="16">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E18),0)</f>
+        <f>C18*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="E18" s="16">
+        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,B18),0))*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="F18" s="12">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(B18,160)),0)</f>
+        <v/>
+      </c>
+      <c r="G18" s="12">
+        <f>C18-F18</f>
         <v/>
       </c>
       <c r="H18" s="12">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(E18,160)),0)</f>
-        <v/>
-      </c>
-      <c r="I18" s="12">
-        <f>G18-H18</f>
-        <v/>
-      </c>
-      <c r="J18" s="16">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E18),0))*Paramètres!$B$3</f>
-        <v/>
-      </c>
-      <c r="K18" s="12">
-        <f>D18-IFERROR(INDEX('Plan d''achat'!$K$2:$K$190,E18),0)</f>
+        <f>H17+E18</f>
+        <v/>
+      </c>
+      <c r="I18" s="10">
+        <f>B18-B17</f>
+        <v/>
+      </c>
+      <c r="J18" s="12">
+        <f>E18</f>
         <v/>
       </c>
     </row>
@@ -12489,44 +12415,40 @@
       <c r="A19" s="10" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="12">
-        <f>G18</f>
-        <v/>
-      </c>
-      <c r="C19" s="12">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E18),0))*Paramètres!$B$3</f>
+      <c r="B19" s="10">
+        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;H18))</f>
+        <v/>
+      </c>
+      <c r="C19" s="16">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,B19),0)</f>
         <v/>
       </c>
       <c r="D19" s="12">
-        <f>D18+C19</f>
-        <v/>
-      </c>
-      <c r="E19" s="10">
-        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;D19))</f>
-        <v/>
-      </c>
-      <c r="F19" s="10">
-        <f>E19-E18</f>
-        <v/>
-      </c>
-      <c r="G19" s="16">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E19),0)</f>
+        <f>C19*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="E19" s="16">
+        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,B19),0))*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="F19" s="12">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(B19,160)),0)</f>
+        <v/>
+      </c>
+      <c r="G19" s="12">
+        <f>C19-F19</f>
         <v/>
       </c>
       <c r="H19" s="12">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(E19,160)),0)</f>
-        <v/>
-      </c>
-      <c r="I19" s="12">
-        <f>G19-H19</f>
-        <v/>
-      </c>
-      <c r="J19" s="16">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E19),0))*Paramètres!$B$3</f>
-        <v/>
-      </c>
-      <c r="K19" s="12">
-        <f>D19-IFERROR(INDEX('Plan d''achat'!$K$2:$K$190,E19),0)</f>
+        <f>H18+E19</f>
+        <v/>
+      </c>
+      <c r="I19" s="10">
+        <f>B19-B18</f>
+        <v/>
+      </c>
+      <c r="J19" s="12">
+        <f>E19</f>
         <v/>
       </c>
     </row>
@@ -12534,44 +12456,40 @@
       <c r="A20" s="10" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="12">
-        <f>G19</f>
-        <v/>
-      </c>
-      <c r="C20" s="12">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E19),0))*Paramètres!$B$3</f>
+      <c r="B20" s="10">
+        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;H19))</f>
+        <v/>
+      </c>
+      <c r="C20" s="16">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,B20),0)</f>
         <v/>
       </c>
       <c r="D20" s="12">
-        <f>D19+C20</f>
-        <v/>
-      </c>
-      <c r="E20" s="10">
-        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;D20))</f>
-        <v/>
-      </c>
-      <c r="F20" s="10">
-        <f>E20-E19</f>
-        <v/>
-      </c>
-      <c r="G20" s="16">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E20),0)</f>
+        <f>C20*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="E20" s="16">
+        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,B20),0))*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="F20" s="12">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(B20,160)),0)</f>
+        <v/>
+      </c>
+      <c r="G20" s="12">
+        <f>C20-F20</f>
         <v/>
       </c>
       <c r="H20" s="12">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(E20,160)),0)</f>
-        <v/>
-      </c>
-      <c r="I20" s="12">
-        <f>G20-H20</f>
-        <v/>
-      </c>
-      <c r="J20" s="16">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E20),0))*Paramètres!$B$3</f>
-        <v/>
-      </c>
-      <c r="K20" s="12">
-        <f>D20-IFERROR(INDEX('Plan d''achat'!$K$2:$K$190,E20),0)</f>
+        <f>H19+E20</f>
+        <v/>
+      </c>
+      <c r="I20" s="10">
+        <f>B20-B19</f>
+        <v/>
+      </c>
+      <c r="J20" s="12">
+        <f>E20</f>
         <v/>
       </c>
     </row>
@@ -12579,44 +12497,40 @@
       <c r="A21" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="12">
-        <f>G20</f>
-        <v/>
-      </c>
-      <c r="C21" s="12">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E20),0))*Paramètres!$B$3</f>
+      <c r="B21" s="10">
+        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;H20))</f>
+        <v/>
+      </c>
+      <c r="C21" s="16">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,B21),0)</f>
         <v/>
       </c>
       <c r="D21" s="12">
-        <f>D20+C21</f>
-        <v/>
-      </c>
-      <c r="E21" s="10">
-        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;D21))</f>
-        <v/>
-      </c>
-      <c r="F21" s="10">
-        <f>E21-E20</f>
-        <v/>
-      </c>
-      <c r="G21" s="16">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E21),0)</f>
+        <f>C21*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="E21" s="16">
+        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,B21),0))*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="F21" s="12">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(B21,160)),0)</f>
+        <v/>
+      </c>
+      <c r="G21" s="12">
+        <f>C21-F21</f>
         <v/>
       </c>
       <c r="H21" s="12">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(E21,160)),0)</f>
-        <v/>
-      </c>
-      <c r="I21" s="12">
-        <f>G21-H21</f>
-        <v/>
-      </c>
-      <c r="J21" s="16">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E21),0))*Paramètres!$B$3</f>
-        <v/>
-      </c>
-      <c r="K21" s="12">
-        <f>D21-IFERROR(INDEX('Plan d''achat'!$K$2:$K$190,E21),0)</f>
+        <f>H20+E21</f>
+        <v/>
+      </c>
+      <c r="I21" s="10">
+        <f>B21-B20</f>
+        <v/>
+      </c>
+      <c r="J21" s="12">
+        <f>E21</f>
         <v/>
       </c>
     </row>
@@ -12624,44 +12538,40 @@
       <c r="A22" s="10" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="12">
-        <f>G21</f>
-        <v/>
-      </c>
-      <c r="C22" s="12">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E21),0))*Paramètres!$B$3</f>
+      <c r="B22" s="10">
+        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;H21))</f>
+        <v/>
+      </c>
+      <c r="C22" s="16">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,B22),0)</f>
         <v/>
       </c>
       <c r="D22" s="12">
-        <f>D21+C22</f>
-        <v/>
-      </c>
-      <c r="E22" s="10">
-        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;D22))</f>
-        <v/>
-      </c>
-      <c r="F22" s="10">
-        <f>E22-E21</f>
-        <v/>
-      </c>
-      <c r="G22" s="16">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E22),0)</f>
+        <f>C22*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="E22" s="16">
+        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,B22),0))*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="F22" s="12">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(B22,160)),0)</f>
+        <v/>
+      </c>
+      <c r="G22" s="12">
+        <f>C22-F22</f>
         <v/>
       </c>
       <c r="H22" s="12">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(E22,160)),0)</f>
-        <v/>
-      </c>
-      <c r="I22" s="12">
-        <f>G22-H22</f>
-        <v/>
-      </c>
-      <c r="J22" s="16">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E22),0))*Paramètres!$B$3</f>
-        <v/>
-      </c>
-      <c r="K22" s="12">
-        <f>D22-IFERROR(INDEX('Plan d''achat'!$K$2:$K$190,E22),0)</f>
+        <f>H21+E22</f>
+        <v/>
+      </c>
+      <c r="I22" s="10">
+        <f>B22-B21</f>
+        <v/>
+      </c>
+      <c r="J22" s="12">
+        <f>E22</f>
         <v/>
       </c>
     </row>
@@ -12669,44 +12579,40 @@
       <c r="A23" s="10" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="12">
-        <f>G22</f>
-        <v/>
-      </c>
-      <c r="C23" s="12">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E22),0))*Paramètres!$B$3</f>
+      <c r="B23" s="10">
+        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;H22))</f>
+        <v/>
+      </c>
+      <c r="C23" s="16">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,B23),0)</f>
         <v/>
       </c>
       <c r="D23" s="12">
-        <f>D22+C23</f>
-        <v/>
-      </c>
-      <c r="E23" s="10">
-        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;D23))</f>
-        <v/>
-      </c>
-      <c r="F23" s="10">
-        <f>E23-E22</f>
-        <v/>
-      </c>
-      <c r="G23" s="16">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E23),0)</f>
+        <f>C23*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="E23" s="16">
+        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,B23),0))*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="F23" s="12">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(B23,160)),0)</f>
+        <v/>
+      </c>
+      <c r="G23" s="12">
+        <f>C23-F23</f>
         <v/>
       </c>
       <c r="H23" s="12">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(E23,160)),0)</f>
-        <v/>
-      </c>
-      <c r="I23" s="12">
-        <f>G23-H23</f>
-        <v/>
-      </c>
-      <c r="J23" s="16">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E23),0))*Paramètres!$B$3</f>
-        <v/>
-      </c>
-      <c r="K23" s="12">
-        <f>D23-IFERROR(INDEX('Plan d''achat'!$K$2:$K$190,E23),0)</f>
+        <f>H22+E23</f>
+        <v/>
+      </c>
+      <c r="I23" s="10">
+        <f>B23-B22</f>
+        <v/>
+      </c>
+      <c r="J23" s="12">
+        <f>E23</f>
         <v/>
       </c>
     </row>
@@ -12714,44 +12620,40 @@
       <c r="A24" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="12">
-        <f>G23</f>
-        <v/>
-      </c>
-      <c r="C24" s="12">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E23),0))*Paramètres!$B$3</f>
+      <c r="B24" s="10">
+        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;H23))</f>
+        <v/>
+      </c>
+      <c r="C24" s="16">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,B24),0)</f>
         <v/>
       </c>
       <c r="D24" s="12">
-        <f>D23+C24</f>
-        <v/>
-      </c>
-      <c r="E24" s="10">
-        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;D24))</f>
-        <v/>
-      </c>
-      <c r="F24" s="10">
-        <f>E24-E23</f>
-        <v/>
-      </c>
-      <c r="G24" s="16">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E24),0)</f>
+        <f>C24*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="E24" s="16">
+        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,B24),0))*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="F24" s="12">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(B24,160)),0)</f>
+        <v/>
+      </c>
+      <c r="G24" s="12">
+        <f>C24-F24</f>
         <v/>
       </c>
       <c r="H24" s="12">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(E24,160)),0)</f>
-        <v/>
-      </c>
-      <c r="I24" s="12">
-        <f>G24-H24</f>
-        <v/>
-      </c>
-      <c r="J24" s="16">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E24),0))*Paramètres!$B$3</f>
-        <v/>
-      </c>
-      <c r="K24" s="12">
-        <f>D24-IFERROR(INDEX('Plan d''achat'!$K$2:$K$190,E24),0)</f>
+        <f>H23+E24</f>
+        <v/>
+      </c>
+      <c r="I24" s="10">
+        <f>B24-B23</f>
+        <v/>
+      </c>
+      <c r="J24" s="12">
+        <f>E24</f>
         <v/>
       </c>
     </row>
@@ -12759,44 +12661,40 @@
       <c r="A25" s="10" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="12">
-        <f>G24</f>
-        <v/>
-      </c>
-      <c r="C25" s="12">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E24),0))*Paramètres!$B$3</f>
+      <c r="B25" s="10">
+        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;H24))</f>
+        <v/>
+      </c>
+      <c r="C25" s="16">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,B25),0)</f>
         <v/>
       </c>
       <c r="D25" s="12">
-        <f>D24+C25</f>
-        <v/>
-      </c>
-      <c r="E25" s="10">
-        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;D25))</f>
-        <v/>
-      </c>
-      <c r="F25" s="10">
-        <f>E25-E24</f>
-        <v/>
-      </c>
-      <c r="G25" s="16">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E25),0)</f>
+        <f>C25*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="E25" s="16">
+        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,B25),0))*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="F25" s="12">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(B25,160)),0)</f>
+        <v/>
+      </c>
+      <c r="G25" s="12">
+        <f>C25-F25</f>
         <v/>
       </c>
       <c r="H25" s="12">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(E25,160)),0)</f>
-        <v/>
-      </c>
-      <c r="I25" s="12">
-        <f>G25-H25</f>
-        <v/>
-      </c>
-      <c r="J25" s="16">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E25),0))*Paramètres!$B$3</f>
-        <v/>
-      </c>
-      <c r="K25" s="12">
-        <f>D25-IFERROR(INDEX('Plan d''achat'!$K$2:$K$190,E25),0)</f>
+        <f>H24+E25</f>
+        <v/>
+      </c>
+      <c r="I25" s="10">
+        <f>B25-B24</f>
+        <v/>
+      </c>
+      <c r="J25" s="12">
+        <f>E25</f>
         <v/>
       </c>
     </row>
@@ -12804,44 +12702,40 @@
       <c r="A26" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="12">
-        <f>G25</f>
-        <v/>
-      </c>
-      <c r="C26" s="12">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E25),0))*Paramètres!$B$3</f>
+      <c r="B26" s="10">
+        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;H25))</f>
+        <v/>
+      </c>
+      <c r="C26" s="16">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,B26),0)</f>
         <v/>
       </c>
       <c r="D26" s="12">
-        <f>D25+C26</f>
-        <v/>
-      </c>
-      <c r="E26" s="10">
-        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;D26))</f>
-        <v/>
-      </c>
-      <c r="F26" s="10">
-        <f>E26-E25</f>
-        <v/>
-      </c>
-      <c r="G26" s="16">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E26),0)</f>
+        <f>C26*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="E26" s="16">
+        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,B26),0))*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="F26" s="12">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(B26,160)),0)</f>
+        <v/>
+      </c>
+      <c r="G26" s="12">
+        <f>C26-F26</f>
         <v/>
       </c>
       <c r="H26" s="12">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(E26,160)),0)</f>
-        <v/>
-      </c>
-      <c r="I26" s="12">
-        <f>G26-H26</f>
-        <v/>
-      </c>
-      <c r="J26" s="16">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E26),0))*Paramètres!$B$3</f>
-        <v/>
-      </c>
-      <c r="K26" s="12">
-        <f>D26-IFERROR(INDEX('Plan d''achat'!$K$2:$K$190,E26),0)</f>
+        <f>H25+E26</f>
+        <v/>
+      </c>
+      <c r="I26" s="10">
+        <f>B26-B25</f>
+        <v/>
+      </c>
+      <c r="J26" s="12">
+        <f>E26</f>
         <v/>
       </c>
     </row>
@@ -12849,44 +12743,40 @@
       <c r="A27" s="10" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="12">
-        <f>G26</f>
-        <v/>
-      </c>
-      <c r="C27" s="12">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E26),0))*Paramètres!$B$3</f>
+      <c r="B27" s="10">
+        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;H26))</f>
+        <v/>
+      </c>
+      <c r="C27" s="16">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,B27),0)</f>
         <v/>
       </c>
       <c r="D27" s="12">
-        <f>D26+C27</f>
-        <v/>
-      </c>
-      <c r="E27" s="10">
-        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;D27))</f>
-        <v/>
-      </c>
-      <c r="F27" s="10">
-        <f>E27-E26</f>
-        <v/>
-      </c>
-      <c r="G27" s="16">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E27),0)</f>
+        <f>C27*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="E27" s="16">
+        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,B27),0))*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="F27" s="12">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(B27,160)),0)</f>
+        <v/>
+      </c>
+      <c r="G27" s="12">
+        <f>C27-F27</f>
         <v/>
       </c>
       <c r="H27" s="12">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(E27,160)),0)</f>
-        <v/>
-      </c>
-      <c r="I27" s="12">
-        <f>G27-H27</f>
-        <v/>
-      </c>
-      <c r="J27" s="16">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E27),0))*Paramètres!$B$3</f>
-        <v/>
-      </c>
-      <c r="K27" s="12">
-        <f>D27-IFERROR(INDEX('Plan d''achat'!$K$2:$K$190,E27),0)</f>
+        <f>H26+E27</f>
+        <v/>
+      </c>
+      <c r="I27" s="10">
+        <f>B27-B26</f>
+        <v/>
+      </c>
+      <c r="J27" s="12">
+        <f>E27</f>
         <v/>
       </c>
     </row>
@@ -12894,44 +12784,40 @@
       <c r="A28" s="10" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="12">
-        <f>G27</f>
-        <v/>
-      </c>
-      <c r="C28" s="12">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E27),0))*Paramètres!$B$3</f>
+      <c r="B28" s="10">
+        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;H27))</f>
+        <v/>
+      </c>
+      <c r="C28" s="16">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,B28),0)</f>
         <v/>
       </c>
       <c r="D28" s="12">
-        <f>D27+C28</f>
-        <v/>
-      </c>
-      <c r="E28" s="10">
-        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;D28))</f>
-        <v/>
-      </c>
-      <c r="F28" s="10">
-        <f>E28-E27</f>
-        <v/>
-      </c>
-      <c r="G28" s="16">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E28),0)</f>
+        <f>C28*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="E28" s="16">
+        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,B28),0))*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="F28" s="12">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(B28,160)),0)</f>
+        <v/>
+      </c>
+      <c r="G28" s="12">
+        <f>C28-F28</f>
         <v/>
       </c>
       <c r="H28" s="12">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(E28,160)),0)</f>
-        <v/>
-      </c>
-      <c r="I28" s="12">
-        <f>G28-H28</f>
-        <v/>
-      </c>
-      <c r="J28" s="16">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E28),0))*Paramètres!$B$3</f>
-        <v/>
-      </c>
-      <c r="K28" s="12">
-        <f>D28-IFERROR(INDEX('Plan d''achat'!$K$2:$K$190,E28),0)</f>
+        <f>H27+E28</f>
+        <v/>
+      </c>
+      <c r="I28" s="10">
+        <f>B28-B27</f>
+        <v/>
+      </c>
+      <c r="J28" s="12">
+        <f>E28</f>
         <v/>
       </c>
     </row>
@@ -12939,44 +12825,40 @@
       <c r="A29" s="10" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="12">
-        <f>G28</f>
-        <v/>
-      </c>
-      <c r="C29" s="12">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E28),0))*Paramètres!$B$3</f>
+      <c r="B29" s="10">
+        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;H28))</f>
+        <v/>
+      </c>
+      <c r="C29" s="16">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,B29),0)</f>
         <v/>
       </c>
       <c r="D29" s="12">
-        <f>D28+C29</f>
-        <v/>
-      </c>
-      <c r="E29" s="10">
-        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;D29))</f>
-        <v/>
-      </c>
-      <c r="F29" s="10">
-        <f>E29-E28</f>
-        <v/>
-      </c>
-      <c r="G29" s="16">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E29),0)</f>
+        <f>C29*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="E29" s="16">
+        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,B29),0))*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="F29" s="12">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(B29,160)),0)</f>
+        <v/>
+      </c>
+      <c r="G29" s="12">
+        <f>C29-F29</f>
         <v/>
       </c>
       <c r="H29" s="12">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(E29,160)),0)</f>
-        <v/>
-      </c>
-      <c r="I29" s="12">
-        <f>G29-H29</f>
-        <v/>
-      </c>
-      <c r="J29" s="16">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E29),0))*Paramètres!$B$3</f>
-        <v/>
-      </c>
-      <c r="K29" s="12">
-        <f>D29-IFERROR(INDEX('Plan d''achat'!$K$2:$K$190,E29),0)</f>
+        <f>H28+E29</f>
+        <v/>
+      </c>
+      <c r="I29" s="10">
+        <f>B29-B28</f>
+        <v/>
+      </c>
+      <c r="J29" s="12">
+        <f>E29</f>
         <v/>
       </c>
     </row>
@@ -12984,44 +12866,40 @@
       <c r="A30" s="10" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="12">
-        <f>G29</f>
-        <v/>
-      </c>
-      <c r="C30" s="12">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E29),0))*Paramètres!$B$3</f>
+      <c r="B30" s="10">
+        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;H29))</f>
+        <v/>
+      </c>
+      <c r="C30" s="16">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,B30),0)</f>
         <v/>
       </c>
       <c r="D30" s="12">
-        <f>D29+C30</f>
-        <v/>
-      </c>
-      <c r="E30" s="10">
-        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;D30))</f>
-        <v/>
-      </c>
-      <c r="F30" s="10">
-        <f>E30-E29</f>
-        <v/>
-      </c>
-      <c r="G30" s="16">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E30),0)</f>
+        <f>C30*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="E30" s="16">
+        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,B30),0))*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="F30" s="12">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(B30,160)),0)</f>
+        <v/>
+      </c>
+      <c r="G30" s="12">
+        <f>C30-F30</f>
         <v/>
       </c>
       <c r="H30" s="12">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(E30,160)),0)</f>
-        <v/>
-      </c>
-      <c r="I30" s="12">
-        <f>G30-H30</f>
-        <v/>
-      </c>
-      <c r="J30" s="16">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E30),0))*Paramètres!$B$3</f>
-        <v/>
-      </c>
-      <c r="K30" s="12">
-        <f>D30-IFERROR(INDEX('Plan d''achat'!$K$2:$K$190,E30),0)</f>
+        <f>H29+E30</f>
+        <v/>
+      </c>
+      <c r="I30" s="10">
+        <f>B30-B29</f>
+        <v/>
+      </c>
+      <c r="J30" s="12">
+        <f>E30</f>
         <v/>
       </c>
     </row>
@@ -13029,44 +12907,40 @@
       <c r="A31" s="10" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="12">
-        <f>G30</f>
-        <v/>
-      </c>
-      <c r="C31" s="12">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E30),0))*Paramètres!$B$3</f>
+      <c r="B31" s="10">
+        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;H30))</f>
+        <v/>
+      </c>
+      <c r="C31" s="16">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,B31),0)</f>
         <v/>
       </c>
       <c r="D31" s="12">
-        <f>D30+C31</f>
-        <v/>
-      </c>
-      <c r="E31" s="10">
-        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;D31))</f>
-        <v/>
-      </c>
-      <c r="F31" s="10">
-        <f>E31-E30</f>
-        <v/>
-      </c>
-      <c r="G31" s="16">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E31),0)</f>
+        <f>C31*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="E31" s="16">
+        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,B31),0))*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="F31" s="12">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(B31,160)),0)</f>
+        <v/>
+      </c>
+      <c r="G31" s="12">
+        <f>C31-F31</f>
         <v/>
       </c>
       <c r="H31" s="12">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(E31,160)),0)</f>
-        <v/>
-      </c>
-      <c r="I31" s="12">
-        <f>G31-H31</f>
-        <v/>
-      </c>
-      <c r="J31" s="16">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E31),0))*Paramètres!$B$3</f>
-        <v/>
-      </c>
-      <c r="K31" s="12">
-        <f>D31-IFERROR(INDEX('Plan d''achat'!$K$2:$K$190,E31),0)</f>
+        <f>H30+E31</f>
+        <v/>
+      </c>
+      <c r="I31" s="10">
+        <f>B31-B30</f>
+        <v/>
+      </c>
+      <c r="J31" s="12">
+        <f>E31</f>
         <v/>
       </c>
     </row>
@@ -13074,44 +12948,40 @@
       <c r="A32" s="10" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="12">
-        <f>G31</f>
-        <v/>
-      </c>
-      <c r="C32" s="12">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E31),0))*Paramètres!$B$3</f>
+      <c r="B32" s="10">
+        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;H31))</f>
+        <v/>
+      </c>
+      <c r="C32" s="16">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,B32),0)</f>
         <v/>
       </c>
       <c r="D32" s="12">
-        <f>D31+C32</f>
-        <v/>
-      </c>
-      <c r="E32" s="10">
-        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;D32))</f>
-        <v/>
-      </c>
-      <c r="F32" s="10">
-        <f>E32-E31</f>
-        <v/>
-      </c>
-      <c r="G32" s="16">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E32),0)</f>
+        <f>C32*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="E32" s="16">
+        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,B32),0))*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="F32" s="12">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(B32,160)),0)</f>
+        <v/>
+      </c>
+      <c r="G32" s="12">
+        <f>C32-F32</f>
         <v/>
       </c>
       <c r="H32" s="12">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(E32,160)),0)</f>
-        <v/>
-      </c>
-      <c r="I32" s="12">
-        <f>G32-H32</f>
-        <v/>
-      </c>
-      <c r="J32" s="16">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E32),0))*Paramètres!$B$3</f>
-        <v/>
-      </c>
-      <c r="K32" s="12">
-        <f>D32-IFERROR(INDEX('Plan d''achat'!$K$2:$K$190,E32),0)</f>
+        <f>H31+E32</f>
+        <v/>
+      </c>
+      <c r="I32" s="10">
+        <f>B32-B31</f>
+        <v/>
+      </c>
+      <c r="J32" s="12">
+        <f>E32</f>
         <v/>
       </c>
     </row>
@@ -13119,44 +12989,40 @@
       <c r="A33" s="10" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="12">
-        <f>G32</f>
-        <v/>
-      </c>
-      <c r="C33" s="12">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E32),0))*Paramètres!$B$3</f>
+      <c r="B33" s="10">
+        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;H32))</f>
+        <v/>
+      </c>
+      <c r="C33" s="16">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,B33),0)</f>
         <v/>
       </c>
       <c r="D33" s="12">
-        <f>D32+C33</f>
-        <v/>
-      </c>
-      <c r="E33" s="10">
-        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;D33))</f>
-        <v/>
-      </c>
-      <c r="F33" s="10">
-        <f>E33-E32</f>
-        <v/>
-      </c>
-      <c r="G33" s="16">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E33),0)</f>
+        <f>C33*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="E33" s="16">
+        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,B33),0))*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="F33" s="12">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(B33,160)),0)</f>
+        <v/>
+      </c>
+      <c r="G33" s="12">
+        <f>C33-F33</f>
         <v/>
       </c>
       <c r="H33" s="12">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(E33,160)),0)</f>
-        <v/>
-      </c>
-      <c r="I33" s="12">
-        <f>G33-H33</f>
-        <v/>
-      </c>
-      <c r="J33" s="16">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E33),0))*Paramètres!$B$3</f>
-        <v/>
-      </c>
-      <c r="K33" s="12">
-        <f>D33-IFERROR(INDEX('Plan d''achat'!$K$2:$K$190,E33),0)</f>
+        <f>H32+E33</f>
+        <v/>
+      </c>
+      <c r="I33" s="10">
+        <f>B33-B32</f>
+        <v/>
+      </c>
+      <c r="J33" s="12">
+        <f>E33</f>
         <v/>
       </c>
     </row>
@@ -13164,44 +13030,40 @@
       <c r="A34" s="10" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="12">
-        <f>G33</f>
-        <v/>
-      </c>
-      <c r="C34" s="12">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E33),0))*Paramètres!$B$3</f>
+      <c r="B34" s="10">
+        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;H33))</f>
+        <v/>
+      </c>
+      <c r="C34" s="16">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,B34),0)</f>
         <v/>
       </c>
       <c r="D34" s="12">
-        <f>D33+C34</f>
-        <v/>
-      </c>
-      <c r="E34" s="10">
-        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;D34))</f>
-        <v/>
-      </c>
-      <c r="F34" s="10">
-        <f>E34-E33</f>
-        <v/>
-      </c>
-      <c r="G34" s="16">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E34),0)</f>
+        <f>C34*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="E34" s="16">
+        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,B34),0))*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="F34" s="12">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(B34,160)),0)</f>
+        <v/>
+      </c>
+      <c r="G34" s="12">
+        <f>C34-F34</f>
         <v/>
       </c>
       <c r="H34" s="12">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(E34,160)),0)</f>
-        <v/>
-      </c>
-      <c r="I34" s="12">
-        <f>G34-H34</f>
-        <v/>
-      </c>
-      <c r="J34" s="16">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E34),0))*Paramètres!$B$3</f>
-        <v/>
-      </c>
-      <c r="K34" s="12">
-        <f>D34-IFERROR(INDEX('Plan d''achat'!$K$2:$K$190,E34),0)</f>
+        <f>H33+E34</f>
+        <v/>
+      </c>
+      <c r="I34" s="10">
+        <f>B34-B33</f>
+        <v/>
+      </c>
+      <c r="J34" s="12">
+        <f>E34</f>
         <v/>
       </c>
     </row>
@@ -13209,44 +13071,40 @@
       <c r="A35" s="10" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="12">
-        <f>G34</f>
-        <v/>
-      </c>
-      <c r="C35" s="12">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E34),0))*Paramètres!$B$3</f>
+      <c r="B35" s="10">
+        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;H34))</f>
+        <v/>
+      </c>
+      <c r="C35" s="16">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,B35),0)</f>
         <v/>
       </c>
       <c r="D35" s="12">
-        <f>D34+C35</f>
-        <v/>
-      </c>
-      <c r="E35" s="10">
-        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;D35))</f>
-        <v/>
-      </c>
-      <c r="F35" s="10">
-        <f>E35-E34</f>
-        <v/>
-      </c>
-      <c r="G35" s="16">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E35),0)</f>
+        <f>C35*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="E35" s="16">
+        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,B35),0))*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="F35" s="12">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(B35,160)),0)</f>
+        <v/>
+      </c>
+      <c r="G35" s="12">
+        <f>C35-F35</f>
         <v/>
       </c>
       <c r="H35" s="12">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(E35,160)),0)</f>
-        <v/>
-      </c>
-      <c r="I35" s="12">
-        <f>G35-H35</f>
-        <v/>
-      </c>
-      <c r="J35" s="16">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E35),0))*Paramètres!$B$3</f>
-        <v/>
-      </c>
-      <c r="K35" s="12">
-        <f>D35-IFERROR(INDEX('Plan d''achat'!$K$2:$K$190,E35),0)</f>
+        <f>H34+E35</f>
+        <v/>
+      </c>
+      <c r="I35" s="10">
+        <f>B35-B34</f>
+        <v/>
+      </c>
+      <c r="J35" s="12">
+        <f>E35</f>
         <v/>
       </c>
     </row>
@@ -13254,44 +13112,40 @@
       <c r="A36" s="10" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="12">
-        <f>G35</f>
-        <v/>
-      </c>
-      <c r="C36" s="12">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E35),0))*Paramètres!$B$3</f>
+      <c r="B36" s="10">
+        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;H35))</f>
+        <v/>
+      </c>
+      <c r="C36" s="16">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,B36),0)</f>
         <v/>
       </c>
       <c r="D36" s="12">
-        <f>D35+C36</f>
-        <v/>
-      </c>
-      <c r="E36" s="10">
-        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;D36))</f>
-        <v/>
-      </c>
-      <c r="F36" s="10">
-        <f>E36-E35</f>
-        <v/>
-      </c>
-      <c r="G36" s="16">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E36),0)</f>
+        <f>C36*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="E36" s="16">
+        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,B36),0))*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="F36" s="12">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(B36,160)),0)</f>
+        <v/>
+      </c>
+      <c r="G36" s="12">
+        <f>C36-F36</f>
         <v/>
       </c>
       <c r="H36" s="12">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(E36,160)),0)</f>
-        <v/>
-      </c>
-      <c r="I36" s="12">
-        <f>G36-H36</f>
-        <v/>
-      </c>
-      <c r="J36" s="16">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E36),0))*Paramètres!$B$3</f>
-        <v/>
-      </c>
-      <c r="K36" s="12">
-        <f>D36-IFERROR(INDEX('Plan d''achat'!$K$2:$K$190,E36),0)</f>
+        <f>H35+E36</f>
+        <v/>
+      </c>
+      <c r="I36" s="10">
+        <f>B36-B35</f>
+        <v/>
+      </c>
+      <c r="J36" s="12">
+        <f>E36</f>
         <v/>
       </c>
     </row>
@@ -13299,44 +13153,40 @@
       <c r="A37" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="12">
-        <f>G36</f>
-        <v/>
-      </c>
-      <c r="C37" s="12">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E36),0))*Paramètres!$B$3</f>
+      <c r="B37" s="10">
+        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;H36))</f>
+        <v/>
+      </c>
+      <c r="C37" s="16">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,B37),0)</f>
         <v/>
       </c>
       <c r="D37" s="12">
-        <f>D36+C37</f>
-        <v/>
-      </c>
-      <c r="E37" s="10">
-        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;D37))</f>
-        <v/>
-      </c>
-      <c r="F37" s="10">
-        <f>E37-E36</f>
-        <v/>
-      </c>
-      <c r="G37" s="16">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E37),0)</f>
+        <f>C37*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="E37" s="16">
+        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,B37),0))*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="F37" s="12">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(B37,160)),0)</f>
+        <v/>
+      </c>
+      <c r="G37" s="12">
+        <f>C37-F37</f>
         <v/>
       </c>
       <c r="H37" s="12">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(E37,160)),0)</f>
-        <v/>
-      </c>
-      <c r="I37" s="12">
-        <f>G37-H37</f>
-        <v/>
-      </c>
-      <c r="J37" s="16">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E37),0))*Paramètres!$B$3</f>
-        <v/>
-      </c>
-      <c r="K37" s="12">
-        <f>D37-IFERROR(INDEX('Plan d''achat'!$K$2:$K$190,E37),0)</f>
+        <f>H36+E37</f>
+        <v/>
+      </c>
+      <c r="I37" s="10">
+        <f>B37-B36</f>
+        <v/>
+      </c>
+      <c r="J37" s="12">
+        <f>E37</f>
         <v/>
       </c>
     </row>
@@ -13344,44 +13194,40 @@
       <c r="A38" s="10" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="12">
-        <f>G37</f>
-        <v/>
-      </c>
-      <c r="C38" s="12">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E37),0))*Paramètres!$B$3</f>
+      <c r="B38" s="10">
+        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;H37))</f>
+        <v/>
+      </c>
+      <c r="C38" s="16">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,B38),0)</f>
         <v/>
       </c>
       <c r="D38" s="12">
-        <f>D37+C38</f>
-        <v/>
-      </c>
-      <c r="E38" s="10">
-        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;D38))</f>
-        <v/>
-      </c>
-      <c r="F38" s="10">
-        <f>E38-E37</f>
-        <v/>
-      </c>
-      <c r="G38" s="16">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E38),0)</f>
+        <f>C38*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="E38" s="16">
+        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,B38),0))*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="F38" s="12">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(B38,160)),0)</f>
+        <v/>
+      </c>
+      <c r="G38" s="12">
+        <f>C38-F38</f>
         <v/>
       </c>
       <c r="H38" s="12">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(E38,160)),0)</f>
-        <v/>
-      </c>
-      <c r="I38" s="12">
-        <f>G38-H38</f>
-        <v/>
-      </c>
-      <c r="J38" s="16">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E38),0))*Paramètres!$B$3</f>
-        <v/>
-      </c>
-      <c r="K38" s="12">
-        <f>D38-IFERROR(INDEX('Plan d''achat'!$K$2:$K$190,E38),0)</f>
+        <f>H37+E38</f>
+        <v/>
+      </c>
+      <c r="I38" s="10">
+        <f>B38-B37</f>
+        <v/>
+      </c>
+      <c r="J38" s="12">
+        <f>E38</f>
         <v/>
       </c>
     </row>
@@ -13389,44 +13235,40 @@
       <c r="A39" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="12">
-        <f>G38</f>
-        <v/>
-      </c>
-      <c r="C39" s="12">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E38),0))*Paramètres!$B$3</f>
+      <c r="B39" s="10">
+        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;H38))</f>
+        <v/>
+      </c>
+      <c r="C39" s="16">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,B39),0)</f>
         <v/>
       </c>
       <c r="D39" s="12">
-        <f>D38+C39</f>
-        <v/>
-      </c>
-      <c r="E39" s="10">
-        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;D39))</f>
-        <v/>
-      </c>
-      <c r="F39" s="10">
-        <f>E39-E38</f>
-        <v/>
-      </c>
-      <c r="G39" s="16">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E39),0)</f>
+        <f>C39*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="E39" s="16">
+        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,B39),0))*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="F39" s="12">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(B39,160)),0)</f>
+        <v/>
+      </c>
+      <c r="G39" s="12">
+        <f>C39-F39</f>
         <v/>
       </c>
       <c r="H39" s="12">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(E39,160)),0)</f>
-        <v/>
-      </c>
-      <c r="I39" s="12">
-        <f>G39-H39</f>
-        <v/>
-      </c>
-      <c r="J39" s="16">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E39),0))*Paramètres!$B$3</f>
-        <v/>
-      </c>
-      <c r="K39" s="12">
-        <f>D39-IFERROR(INDEX('Plan d''achat'!$K$2:$K$190,E39),0)</f>
+        <f>H38+E39</f>
+        <v/>
+      </c>
+      <c r="I39" s="10">
+        <f>B39-B38</f>
+        <v/>
+      </c>
+      <c r="J39" s="12">
+        <f>E39</f>
         <v/>
       </c>
     </row>
@@ -13434,44 +13276,40 @@
       <c r="A40" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="12">
-        <f>G39</f>
-        <v/>
-      </c>
-      <c r="C40" s="12">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E39),0))*Paramètres!$B$3</f>
+      <c r="B40" s="10">
+        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;H39))</f>
+        <v/>
+      </c>
+      <c r="C40" s="16">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,B40),0)</f>
         <v/>
       </c>
       <c r="D40" s="12">
-        <f>D39+C40</f>
-        <v/>
-      </c>
-      <c r="E40" s="10">
-        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;D40))</f>
-        <v/>
-      </c>
-      <c r="F40" s="10">
-        <f>E40-E39</f>
-        <v/>
-      </c>
-      <c r="G40" s="16">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E40),0)</f>
+        <f>C40*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="E40" s="16">
+        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,B40),0))*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="F40" s="12">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(B40,160)),0)</f>
+        <v/>
+      </c>
+      <c r="G40" s="12">
+        <f>C40-F40</f>
         <v/>
       </c>
       <c r="H40" s="12">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(E40,160)),0)</f>
-        <v/>
-      </c>
-      <c r="I40" s="12">
-        <f>G40-H40</f>
-        <v/>
-      </c>
-      <c r="J40" s="16">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E40),0))*Paramètres!$B$3</f>
-        <v/>
-      </c>
-      <c r="K40" s="12">
-        <f>D40-IFERROR(INDEX('Plan d''achat'!$K$2:$K$190,E40),0)</f>
+        <f>H39+E40</f>
+        <v/>
+      </c>
+      <c r="I40" s="10">
+        <f>B40-B39</f>
+        <v/>
+      </c>
+      <c r="J40" s="12">
+        <f>E40</f>
         <v/>
       </c>
     </row>
@@ -13479,44 +13317,40 @@
       <c r="A41" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="12">
-        <f>G40</f>
-        <v/>
-      </c>
-      <c r="C41" s="12">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E40),0))*Paramètres!$B$3</f>
+      <c r="B41" s="10">
+        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;H40))</f>
+        <v/>
+      </c>
+      <c r="C41" s="16">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,B41),0)</f>
         <v/>
       </c>
       <c r="D41" s="12">
-        <f>D40+C41</f>
-        <v/>
-      </c>
-      <c r="E41" s="10">
-        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;D41))</f>
-        <v/>
-      </c>
-      <c r="F41" s="10">
-        <f>E41-E40</f>
-        <v/>
-      </c>
-      <c r="G41" s="16">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E41),0)</f>
+        <f>C41*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="E41" s="16">
+        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,B41),0))*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="F41" s="12">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(B41,160)),0)</f>
+        <v/>
+      </c>
+      <c r="G41" s="12">
+        <f>C41-F41</f>
         <v/>
       </c>
       <c r="H41" s="12">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(E41,160)),0)</f>
-        <v/>
-      </c>
-      <c r="I41" s="12">
-        <f>G41-H41</f>
-        <v/>
-      </c>
-      <c r="J41" s="16">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E41),0))*Paramètres!$B$3</f>
-        <v/>
-      </c>
-      <c r="K41" s="12">
-        <f>D41-IFERROR(INDEX('Plan d''achat'!$K$2:$K$190,E41),0)</f>
+        <f>H40+E41</f>
+        <v/>
+      </c>
+      <c r="I41" s="10">
+        <f>B41-B40</f>
+        <v/>
+      </c>
+      <c r="J41" s="12">
+        <f>E41</f>
         <v/>
       </c>
     </row>
@@ -13524,44 +13358,40 @@
       <c r="A42" s="10" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="12">
-        <f>G41</f>
-        <v/>
-      </c>
-      <c r="C42" s="12">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E41),0))*Paramètres!$B$3</f>
+      <c r="B42" s="10">
+        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;H41))</f>
+        <v/>
+      </c>
+      <c r="C42" s="16">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,B42),0)</f>
         <v/>
       </c>
       <c r="D42" s="12">
-        <f>D41+C42</f>
-        <v/>
-      </c>
-      <c r="E42" s="10">
-        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;D42))</f>
-        <v/>
-      </c>
-      <c r="F42" s="10">
-        <f>E42-E41</f>
-        <v/>
-      </c>
-      <c r="G42" s="16">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E42),0)</f>
+        <f>C42*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="E42" s="16">
+        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,B42),0))*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="F42" s="12">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(B42,160)),0)</f>
+        <v/>
+      </c>
+      <c r="G42" s="12">
+        <f>C42-F42</f>
         <v/>
       </c>
       <c r="H42" s="12">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(E42,160)),0)</f>
-        <v/>
-      </c>
-      <c r="I42" s="12">
-        <f>G42-H42</f>
-        <v/>
-      </c>
-      <c r="J42" s="16">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E42),0))*Paramètres!$B$3</f>
-        <v/>
-      </c>
-      <c r="K42" s="12">
-        <f>D42-IFERROR(INDEX('Plan d''achat'!$K$2:$K$190,E42),0)</f>
+        <f>H41+E42</f>
+        <v/>
+      </c>
+      <c r="I42" s="10">
+        <f>B42-B41</f>
+        <v/>
+      </c>
+      <c r="J42" s="12">
+        <f>E42</f>
         <v/>
       </c>
     </row>
@@ -13569,44 +13399,40 @@
       <c r="A43" s="10" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="12">
-        <f>G42</f>
-        <v/>
-      </c>
-      <c r="C43" s="12">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E42),0))*Paramètres!$B$3</f>
+      <c r="B43" s="10">
+        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;H42))</f>
+        <v/>
+      </c>
+      <c r="C43" s="16">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,B43),0)</f>
         <v/>
       </c>
       <c r="D43" s="12">
-        <f>D42+C43</f>
-        <v/>
-      </c>
-      <c r="E43" s="10">
-        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;D43))</f>
-        <v/>
-      </c>
-      <c r="F43" s="10">
-        <f>E43-E42</f>
-        <v/>
-      </c>
-      <c r="G43" s="16">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E43),0)</f>
+        <f>C43*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="E43" s="16">
+        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,B43),0))*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="F43" s="12">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(B43,160)),0)</f>
+        <v/>
+      </c>
+      <c r="G43" s="12">
+        <f>C43-F43</f>
         <v/>
       </c>
       <c r="H43" s="12">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(E43,160)),0)</f>
-        <v/>
-      </c>
-      <c r="I43" s="12">
-        <f>G43-H43</f>
-        <v/>
-      </c>
-      <c r="J43" s="16">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E43),0))*Paramètres!$B$3</f>
-        <v/>
-      </c>
-      <c r="K43" s="12">
-        <f>D43-IFERROR(INDEX('Plan d''achat'!$K$2:$K$190,E43),0)</f>
+        <f>H42+E43</f>
+        <v/>
+      </c>
+      <c r="I43" s="10">
+        <f>B43-B42</f>
+        <v/>
+      </c>
+      <c r="J43" s="12">
+        <f>E43</f>
         <v/>
       </c>
     </row>
@@ -13614,44 +13440,40 @@
       <c r="A44" s="10" t="n">
         <v>43</v>
       </c>
-      <c r="B44" s="12">
-        <f>G43</f>
-        <v/>
-      </c>
-      <c r="C44" s="12">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E43),0))*Paramètres!$B$3</f>
+      <c r="B44" s="10">
+        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;H43))</f>
+        <v/>
+      </c>
+      <c r="C44" s="16">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,B44),0)</f>
         <v/>
       </c>
       <c r="D44" s="12">
-        <f>D43+C44</f>
-        <v/>
-      </c>
-      <c r="E44" s="10">
-        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;D44))</f>
-        <v/>
-      </c>
-      <c r="F44" s="10">
-        <f>E44-E43</f>
-        <v/>
-      </c>
-      <c r="G44" s="16">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E44),0)</f>
+        <f>C44*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="E44" s="16">
+        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,B44),0))*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="F44" s="12">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(B44,160)),0)</f>
+        <v/>
+      </c>
+      <c r="G44" s="12">
+        <f>C44-F44</f>
         <v/>
       </c>
       <c r="H44" s="12">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(E44,160)),0)</f>
-        <v/>
-      </c>
-      <c r="I44" s="12">
-        <f>G44-H44</f>
-        <v/>
-      </c>
-      <c r="J44" s="16">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E44),0))*Paramètres!$B$3</f>
-        <v/>
-      </c>
-      <c r="K44" s="12">
-        <f>D44-IFERROR(INDEX('Plan d''achat'!$K$2:$K$190,E44),0)</f>
+        <f>H43+E44</f>
+        <v/>
+      </c>
+      <c r="I44" s="10">
+        <f>B44-B43</f>
+        <v/>
+      </c>
+      <c r="J44" s="12">
+        <f>E44</f>
         <v/>
       </c>
     </row>
@@ -13659,44 +13481,40 @@
       <c r="A45" s="10" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="12">
-        <f>G44</f>
-        <v/>
-      </c>
-      <c r="C45" s="12">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E44),0))*Paramètres!$B$3</f>
+      <c r="B45" s="10">
+        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;H44))</f>
+        <v/>
+      </c>
+      <c r="C45" s="16">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,B45),0)</f>
         <v/>
       </c>
       <c r="D45" s="12">
-        <f>D44+C45</f>
-        <v/>
-      </c>
-      <c r="E45" s="10">
-        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;D45))</f>
-        <v/>
-      </c>
-      <c r="F45" s="10">
-        <f>E45-E44</f>
-        <v/>
-      </c>
-      <c r="G45" s="16">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E45),0)</f>
+        <f>C45*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="E45" s="16">
+        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,B45),0))*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="F45" s="12">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(B45,160)),0)</f>
+        <v/>
+      </c>
+      <c r="G45" s="12">
+        <f>C45-F45</f>
         <v/>
       </c>
       <c r="H45" s="12">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(E45,160)),0)</f>
-        <v/>
-      </c>
-      <c r="I45" s="12">
-        <f>G45-H45</f>
-        <v/>
-      </c>
-      <c r="J45" s="16">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E45),0))*Paramètres!$B$3</f>
-        <v/>
-      </c>
-      <c r="K45" s="12">
-        <f>D45-IFERROR(INDEX('Plan d''achat'!$K$2:$K$190,E45),0)</f>
+        <f>H44+E45</f>
+        <v/>
+      </c>
+      <c r="I45" s="10">
+        <f>B45-B44</f>
+        <v/>
+      </c>
+      <c r="J45" s="12">
+        <f>E45</f>
         <v/>
       </c>
     </row>
@@ -13704,44 +13522,40 @@
       <c r="A46" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="12">
-        <f>G45</f>
-        <v/>
-      </c>
-      <c r="C46" s="12">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E45),0))*Paramètres!$B$3</f>
+      <c r="B46" s="10">
+        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;H45))</f>
+        <v/>
+      </c>
+      <c r="C46" s="16">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,B46),0)</f>
         <v/>
       </c>
       <c r="D46" s="12">
-        <f>D45+C46</f>
-        <v/>
-      </c>
-      <c r="E46" s="10">
-        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;D46))</f>
-        <v/>
-      </c>
-      <c r="F46" s="10">
-        <f>E46-E45</f>
-        <v/>
-      </c>
-      <c r="G46" s="16">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E46),0)</f>
+        <f>C46*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="E46" s="16">
+        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,B46),0))*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="F46" s="12">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(B46,160)),0)</f>
+        <v/>
+      </c>
+      <c r="G46" s="12">
+        <f>C46-F46</f>
         <v/>
       </c>
       <c r="H46" s="12">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(E46,160)),0)</f>
-        <v/>
-      </c>
-      <c r="I46" s="12">
-        <f>G46-H46</f>
-        <v/>
-      </c>
-      <c r="J46" s="16">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E46),0))*Paramètres!$B$3</f>
-        <v/>
-      </c>
-      <c r="K46" s="12">
-        <f>D46-IFERROR(INDEX('Plan d''achat'!$K$2:$K$190,E46),0)</f>
+        <f>H45+E46</f>
+        <v/>
+      </c>
+      <c r="I46" s="10">
+        <f>B46-B45</f>
+        <v/>
+      </c>
+      <c r="J46" s="12">
+        <f>E46</f>
         <v/>
       </c>
     </row>
@@ -13749,44 +13563,40 @@
       <c r="A47" s="10" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="12">
-        <f>G46</f>
-        <v/>
-      </c>
-      <c r="C47" s="12">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E46),0))*Paramètres!$B$3</f>
+      <c r="B47" s="10">
+        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;H46))</f>
+        <v/>
+      </c>
+      <c r="C47" s="16">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,B47),0)</f>
         <v/>
       </c>
       <c r="D47" s="12">
-        <f>D46+C47</f>
-        <v/>
-      </c>
-      <c r="E47" s="10">
-        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;D47))</f>
-        <v/>
-      </c>
-      <c r="F47" s="10">
-        <f>E47-E46</f>
-        <v/>
-      </c>
-      <c r="G47" s="16">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E47),0)</f>
+        <f>C47*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="E47" s="16">
+        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,B47),0))*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="F47" s="12">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(B47,160)),0)</f>
+        <v/>
+      </c>
+      <c r="G47" s="12">
+        <f>C47-F47</f>
         <v/>
       </c>
       <c r="H47" s="12">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(E47,160)),0)</f>
-        <v/>
-      </c>
-      <c r="I47" s="12">
-        <f>G47-H47</f>
-        <v/>
-      </c>
-      <c r="J47" s="16">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E47),0))*Paramètres!$B$3</f>
-        <v/>
-      </c>
-      <c r="K47" s="12">
-        <f>D47-IFERROR(INDEX('Plan d''achat'!$K$2:$K$190,E47),0)</f>
+        <f>H46+E47</f>
+        <v/>
+      </c>
+      <c r="I47" s="10">
+        <f>B47-B46</f>
+        <v/>
+      </c>
+      <c r="J47" s="12">
+        <f>E47</f>
         <v/>
       </c>
     </row>
@@ -13794,44 +13604,40 @@
       <c r="A48" s="10" t="n">
         <v>47</v>
       </c>
-      <c r="B48" s="12">
-        <f>G47</f>
-        <v/>
-      </c>
-      <c r="C48" s="12">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E47),0))*Paramètres!$B$3</f>
+      <c r="B48" s="10">
+        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;H47))</f>
+        <v/>
+      </c>
+      <c r="C48" s="16">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,B48),0)</f>
         <v/>
       </c>
       <c r="D48" s="12">
-        <f>D47+C48</f>
-        <v/>
-      </c>
-      <c r="E48" s="10">
-        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;D48))</f>
-        <v/>
-      </c>
-      <c r="F48" s="10">
-        <f>E48-E47</f>
-        <v/>
-      </c>
-      <c r="G48" s="16">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E48),0)</f>
+        <f>C48*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="E48" s="16">
+        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,B48),0))*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="F48" s="12">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(B48,160)),0)</f>
+        <v/>
+      </c>
+      <c r="G48" s="12">
+        <f>C48-F48</f>
         <v/>
       </c>
       <c r="H48" s="12">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(E48,160)),0)</f>
-        <v/>
-      </c>
-      <c r="I48" s="12">
-        <f>G48-H48</f>
-        <v/>
-      </c>
-      <c r="J48" s="16">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E48),0))*Paramètres!$B$3</f>
-        <v/>
-      </c>
-      <c r="K48" s="12">
-        <f>D48-IFERROR(INDEX('Plan d''achat'!$K$2:$K$190,E48),0)</f>
+        <f>H47+E48</f>
+        <v/>
+      </c>
+      <c r="I48" s="10">
+        <f>B48-B47</f>
+        <v/>
+      </c>
+      <c r="J48" s="12">
+        <f>E48</f>
         <v/>
       </c>
     </row>
@@ -13839,44 +13645,40 @@
       <c r="A49" s="10" t="n">
         <v>48</v>
       </c>
-      <c r="B49" s="12">
-        <f>G48</f>
-        <v/>
-      </c>
-      <c r="C49" s="12">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E48),0))*Paramètres!$B$3</f>
+      <c r="B49" s="10">
+        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;H48))</f>
+        <v/>
+      </c>
+      <c r="C49" s="16">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,B49),0)</f>
         <v/>
       </c>
       <c r="D49" s="12">
-        <f>D48+C49</f>
-        <v/>
-      </c>
-      <c r="E49" s="10">
-        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;D49))</f>
-        <v/>
-      </c>
-      <c r="F49" s="10">
-        <f>E49-E48</f>
-        <v/>
-      </c>
-      <c r="G49" s="16">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E49),0)</f>
+        <f>C49*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="E49" s="16">
+        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,B49),0))*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="F49" s="12">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(B49,160)),0)</f>
+        <v/>
+      </c>
+      <c r="G49" s="12">
+        <f>C49-F49</f>
         <v/>
       </c>
       <c r="H49" s="12">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(E49,160)),0)</f>
-        <v/>
-      </c>
-      <c r="I49" s="12">
-        <f>G49-H49</f>
-        <v/>
-      </c>
-      <c r="J49" s="16">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E49),0))*Paramètres!$B$3</f>
-        <v/>
-      </c>
-      <c r="K49" s="12">
-        <f>D49-IFERROR(INDEX('Plan d''achat'!$K$2:$K$190,E49),0)</f>
+        <f>H48+E49</f>
+        <v/>
+      </c>
+      <c r="I49" s="10">
+        <f>B49-B48</f>
+        <v/>
+      </c>
+      <c r="J49" s="12">
+        <f>E49</f>
         <v/>
       </c>
     </row>
@@ -13884,44 +13686,40 @@
       <c r="A50" s="10" t="n">
         <v>49</v>
       </c>
-      <c r="B50" s="12">
-        <f>G49</f>
-        <v/>
-      </c>
-      <c r="C50" s="12">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E49),0))*Paramètres!$B$3</f>
+      <c r="B50" s="10">
+        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;H49))</f>
+        <v/>
+      </c>
+      <c r="C50" s="16">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,B50),0)</f>
         <v/>
       </c>
       <c r="D50" s="12">
-        <f>D49+C50</f>
-        <v/>
-      </c>
-      <c r="E50" s="10">
-        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;D50))</f>
-        <v/>
-      </c>
-      <c r="F50" s="10">
-        <f>E50-E49</f>
-        <v/>
-      </c>
-      <c r="G50" s="16">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E50),0)</f>
+        <f>C50*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="E50" s="16">
+        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,B50),0))*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="F50" s="12">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(B50,160)),0)</f>
+        <v/>
+      </c>
+      <c r="G50" s="12">
+        <f>C50-F50</f>
         <v/>
       </c>
       <c r="H50" s="12">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(E50,160)),0)</f>
-        <v/>
-      </c>
-      <c r="I50" s="12">
-        <f>G50-H50</f>
-        <v/>
-      </c>
-      <c r="J50" s="16">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E50),0))*Paramètres!$B$3</f>
-        <v/>
-      </c>
-      <c r="K50" s="12">
-        <f>D50-IFERROR(INDEX('Plan d''achat'!$K$2:$K$190,E50),0)</f>
+        <f>H49+E50</f>
+        <v/>
+      </c>
+      <c r="I50" s="10">
+        <f>B50-B49</f>
+        <v/>
+      </c>
+      <c r="J50" s="12">
+        <f>E50</f>
         <v/>
       </c>
     </row>
@@ -13929,44 +13727,40 @@
       <c r="A51" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="B51" s="12">
-        <f>G50</f>
-        <v/>
-      </c>
-      <c r="C51" s="12">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E50),0))*Paramètres!$B$3</f>
+      <c r="B51" s="10">
+        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;H50))</f>
+        <v/>
+      </c>
+      <c r="C51" s="16">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,B51),0)</f>
         <v/>
       </c>
       <c r="D51" s="12">
-        <f>D50+C51</f>
-        <v/>
-      </c>
-      <c r="E51" s="10">
-        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;D51))</f>
-        <v/>
-      </c>
-      <c r="F51" s="10">
-        <f>E51-E50</f>
-        <v/>
-      </c>
-      <c r="G51" s="16">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E51),0)</f>
+        <f>C51*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="E51" s="16">
+        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,B51),0))*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="F51" s="12">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(B51,160)),0)</f>
+        <v/>
+      </c>
+      <c r="G51" s="12">
+        <f>C51-F51</f>
         <v/>
       </c>
       <c r="H51" s="12">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(E51,160)),0)</f>
-        <v/>
-      </c>
-      <c r="I51" s="12">
-        <f>G51-H51</f>
-        <v/>
-      </c>
-      <c r="J51" s="16">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E51),0))*Paramètres!$B$3</f>
-        <v/>
-      </c>
-      <c r="K51" s="12">
-        <f>D51-IFERROR(INDEX('Plan d''achat'!$K$2:$K$190,E51),0)</f>
+        <f>H50+E51</f>
+        <v/>
+      </c>
+      <c r="I51" s="10">
+        <f>B51-B50</f>
+        <v/>
+      </c>
+      <c r="J51" s="12">
+        <f>E51</f>
         <v/>
       </c>
     </row>
@@ -13974,44 +13768,40 @@
       <c r="A52" s="10" t="n">
         <v>51</v>
       </c>
-      <c r="B52" s="12">
-        <f>G51</f>
-        <v/>
-      </c>
-      <c r="C52" s="12">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E51),0))*Paramètres!$B$3</f>
+      <c r="B52" s="10">
+        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;H51))</f>
+        <v/>
+      </c>
+      <c r="C52" s="16">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,B52),0)</f>
         <v/>
       </c>
       <c r="D52" s="12">
-        <f>D51+C52</f>
-        <v/>
-      </c>
-      <c r="E52" s="10">
-        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;D52))</f>
-        <v/>
-      </c>
-      <c r="F52" s="10">
-        <f>E52-E51</f>
-        <v/>
-      </c>
-      <c r="G52" s="16">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E52),0)</f>
+        <f>C52*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="E52" s="16">
+        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,B52),0))*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="F52" s="12">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(B52,160)),0)</f>
+        <v/>
+      </c>
+      <c r="G52" s="12">
+        <f>C52-F52</f>
         <v/>
       </c>
       <c r="H52" s="12">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(E52,160)),0)</f>
-        <v/>
-      </c>
-      <c r="I52" s="12">
-        <f>G52-H52</f>
-        <v/>
-      </c>
-      <c r="J52" s="16">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E52),0))*Paramètres!$B$3</f>
-        <v/>
-      </c>
-      <c r="K52" s="12">
-        <f>D52-IFERROR(INDEX('Plan d''achat'!$K$2:$K$190,E52),0)</f>
+        <f>H51+E52</f>
+        <v/>
+      </c>
+      <c r="I52" s="10">
+        <f>B52-B51</f>
+        <v/>
+      </c>
+      <c r="J52" s="12">
+        <f>E52</f>
         <v/>
       </c>
     </row>
@@ -14019,44 +13809,40 @@
       <c r="A53" s="10" t="n">
         <v>52</v>
       </c>
-      <c r="B53" s="12">
-        <f>G52</f>
-        <v/>
-      </c>
-      <c r="C53" s="12">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E52),0))*Paramètres!$B$3</f>
+      <c r="B53" s="10">
+        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;H52))</f>
+        <v/>
+      </c>
+      <c r="C53" s="16">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,B53),0)</f>
         <v/>
       </c>
       <c r="D53" s="12">
-        <f>D52+C53</f>
-        <v/>
-      </c>
-      <c r="E53" s="10">
-        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;D53))</f>
-        <v/>
-      </c>
-      <c r="F53" s="10">
-        <f>E53-E52</f>
-        <v/>
-      </c>
-      <c r="G53" s="16">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E53),0)</f>
+        <f>C53*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="E53" s="16">
+        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,B53),0))*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="F53" s="12">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(B53,160)),0)</f>
+        <v/>
+      </c>
+      <c r="G53" s="12">
+        <f>C53-F53</f>
         <v/>
       </c>
       <c r="H53" s="12">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(E53,160)),0)</f>
-        <v/>
-      </c>
-      <c r="I53" s="12">
-        <f>G53-H53</f>
-        <v/>
-      </c>
-      <c r="J53" s="16">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E53),0))*Paramètres!$B$3</f>
-        <v/>
-      </c>
-      <c r="K53" s="12">
-        <f>D53-IFERROR(INDEX('Plan d''achat'!$K$2:$K$190,E53),0)</f>
+        <f>H52+E53</f>
+        <v/>
+      </c>
+      <c r="I53" s="10">
+        <f>B53-B52</f>
+        <v/>
+      </c>
+      <c r="J53" s="12">
+        <f>E53</f>
         <v/>
       </c>
     </row>
@@ -14064,44 +13850,40 @@
       <c r="A54" s="10" t="n">
         <v>53</v>
       </c>
-      <c r="B54" s="12">
-        <f>G53</f>
-        <v/>
-      </c>
-      <c r="C54" s="12">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E53),0))*Paramètres!$B$3</f>
+      <c r="B54" s="10">
+        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;H53))</f>
+        <v/>
+      </c>
+      <c r="C54" s="16">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,B54),0)</f>
         <v/>
       </c>
       <c r="D54" s="12">
-        <f>D53+C54</f>
-        <v/>
-      </c>
-      <c r="E54" s="10">
-        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;D54))</f>
-        <v/>
-      </c>
-      <c r="F54" s="10">
-        <f>E54-E53</f>
-        <v/>
-      </c>
-      <c r="G54" s="16">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E54),0)</f>
+        <f>C54*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="E54" s="16">
+        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,B54),0))*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="F54" s="12">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(B54,160)),0)</f>
+        <v/>
+      </c>
+      <c r="G54" s="12">
+        <f>C54-F54</f>
         <v/>
       </c>
       <c r="H54" s="12">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(E54,160)),0)</f>
-        <v/>
-      </c>
-      <c r="I54" s="12">
-        <f>G54-H54</f>
-        <v/>
-      </c>
-      <c r="J54" s="16">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E54),0))*Paramètres!$B$3</f>
-        <v/>
-      </c>
-      <c r="K54" s="12">
-        <f>D54-IFERROR(INDEX('Plan d''achat'!$K$2:$K$190,E54),0)</f>
+        <f>H53+E54</f>
+        <v/>
+      </c>
+      <c r="I54" s="10">
+        <f>B54-B53</f>
+        <v/>
+      </c>
+      <c r="J54" s="12">
+        <f>E54</f>
         <v/>
       </c>
     </row>
@@ -14109,44 +13891,40 @@
       <c r="A55" s="10" t="n">
         <v>54</v>
       </c>
-      <c r="B55" s="12">
-        <f>G54</f>
-        <v/>
-      </c>
-      <c r="C55" s="12">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E54),0))*Paramètres!$B$3</f>
+      <c r="B55" s="10">
+        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;H54))</f>
+        <v/>
+      </c>
+      <c r="C55" s="16">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,B55),0)</f>
         <v/>
       </c>
       <c r="D55" s="12">
-        <f>D54+C55</f>
-        <v/>
-      </c>
-      <c r="E55" s="10">
-        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;D55))</f>
-        <v/>
-      </c>
-      <c r="F55" s="10">
-        <f>E55-E54</f>
-        <v/>
-      </c>
-      <c r="G55" s="16">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E55),0)</f>
+        <f>C55*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="E55" s="16">
+        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,B55),0))*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="F55" s="12">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(B55,160)),0)</f>
+        <v/>
+      </c>
+      <c r="G55" s="12">
+        <f>C55-F55</f>
         <v/>
       </c>
       <c r="H55" s="12">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(E55,160)),0)</f>
-        <v/>
-      </c>
-      <c r="I55" s="12">
-        <f>G55-H55</f>
-        <v/>
-      </c>
-      <c r="J55" s="16">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E55),0))*Paramètres!$B$3</f>
-        <v/>
-      </c>
-      <c r="K55" s="12">
-        <f>D55-IFERROR(INDEX('Plan d''achat'!$K$2:$K$190,E55),0)</f>
+        <f>H54+E55</f>
+        <v/>
+      </c>
+      <c r="I55" s="10">
+        <f>B55-B54</f>
+        <v/>
+      </c>
+      <c r="J55" s="12">
+        <f>E55</f>
         <v/>
       </c>
     </row>
@@ -14154,44 +13932,40 @@
       <c r="A56" s="10" t="n">
         <v>55</v>
       </c>
-      <c r="B56" s="12">
-        <f>G55</f>
-        <v/>
-      </c>
-      <c r="C56" s="12">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E55),0))*Paramètres!$B$3</f>
+      <c r="B56" s="10">
+        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;H55))</f>
+        <v/>
+      </c>
+      <c r="C56" s="16">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,B56),0)</f>
         <v/>
       </c>
       <c r="D56" s="12">
-        <f>D55+C56</f>
-        <v/>
-      </c>
-      <c r="E56" s="10">
-        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;D56))</f>
-        <v/>
-      </c>
-      <c r="F56" s="10">
-        <f>E56-E55</f>
-        <v/>
-      </c>
-      <c r="G56" s="16">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E56),0)</f>
+        <f>C56*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="E56" s="16">
+        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,B56),0))*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="F56" s="12">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(B56,160)),0)</f>
+        <v/>
+      </c>
+      <c r="G56" s="12">
+        <f>C56-F56</f>
         <v/>
       </c>
       <c r="H56" s="12">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(E56,160)),0)</f>
-        <v/>
-      </c>
-      <c r="I56" s="12">
-        <f>G56-H56</f>
-        <v/>
-      </c>
-      <c r="J56" s="16">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E56),0))*Paramètres!$B$3</f>
-        <v/>
-      </c>
-      <c r="K56" s="12">
-        <f>D56-IFERROR(INDEX('Plan d''achat'!$K$2:$K$190,E56),0)</f>
+        <f>H55+E56</f>
+        <v/>
+      </c>
+      <c r="I56" s="10">
+        <f>B56-B55</f>
+        <v/>
+      </c>
+      <c r="J56" s="12">
+        <f>E56</f>
         <v/>
       </c>
     </row>
@@ -14199,44 +13973,40 @@
       <c r="A57" s="10" t="n">
         <v>56</v>
       </c>
-      <c r="B57" s="12">
-        <f>G56</f>
-        <v/>
-      </c>
-      <c r="C57" s="12">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E56),0))*Paramètres!$B$3</f>
+      <c r="B57" s="10">
+        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;H56))</f>
+        <v/>
+      </c>
+      <c r="C57" s="16">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,B57),0)</f>
         <v/>
       </c>
       <c r="D57" s="12">
-        <f>D56+C57</f>
-        <v/>
-      </c>
-      <c r="E57" s="10">
-        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;D57))</f>
-        <v/>
-      </c>
-      <c r="F57" s="10">
-        <f>E57-E56</f>
-        <v/>
-      </c>
-      <c r="G57" s="16">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E57),0)</f>
+        <f>C57*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="E57" s="16">
+        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,B57),0))*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="F57" s="12">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(B57,160)),0)</f>
+        <v/>
+      </c>
+      <c r="G57" s="12">
+        <f>C57-F57</f>
         <v/>
       </c>
       <c r="H57" s="12">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(E57,160)),0)</f>
-        <v/>
-      </c>
-      <c r="I57" s="12">
-        <f>G57-H57</f>
-        <v/>
-      </c>
-      <c r="J57" s="16">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E57),0))*Paramètres!$B$3</f>
-        <v/>
-      </c>
-      <c r="K57" s="12">
-        <f>D57-IFERROR(INDEX('Plan d''achat'!$K$2:$K$190,E57),0)</f>
+        <f>H56+E57</f>
+        <v/>
+      </c>
+      <c r="I57" s="10">
+        <f>B57-B56</f>
+        <v/>
+      </c>
+      <c r="J57" s="12">
+        <f>E57</f>
         <v/>
       </c>
     </row>
@@ -14244,44 +14014,40 @@
       <c r="A58" s="10" t="n">
         <v>57</v>
       </c>
-      <c r="B58" s="12">
-        <f>G57</f>
-        <v/>
-      </c>
-      <c r="C58" s="12">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E57),0))*Paramètres!$B$3</f>
+      <c r="B58" s="10">
+        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;H57))</f>
+        <v/>
+      </c>
+      <c r="C58" s="16">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,B58),0)</f>
         <v/>
       </c>
       <c r="D58" s="12">
-        <f>D57+C58</f>
-        <v/>
-      </c>
-      <c r="E58" s="10">
-        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;D58))</f>
-        <v/>
-      </c>
-      <c r="F58" s="10">
-        <f>E58-E57</f>
-        <v/>
-      </c>
-      <c r="G58" s="16">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E58),0)</f>
+        <f>C58*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="E58" s="16">
+        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,B58),0))*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="F58" s="12">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(B58,160)),0)</f>
+        <v/>
+      </c>
+      <c r="G58" s="12">
+        <f>C58-F58</f>
         <v/>
       </c>
       <c r="H58" s="12">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(E58,160)),0)</f>
-        <v/>
-      </c>
-      <c r="I58" s="12">
-        <f>G58-H58</f>
-        <v/>
-      </c>
-      <c r="J58" s="16">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E58),0))*Paramètres!$B$3</f>
-        <v/>
-      </c>
-      <c r="K58" s="12">
-        <f>D58-IFERROR(INDEX('Plan d''achat'!$K$2:$K$190,E58),0)</f>
+        <f>H57+E58</f>
+        <v/>
+      </c>
+      <c r="I58" s="10">
+        <f>B58-B57</f>
+        <v/>
+      </c>
+      <c r="J58" s="12">
+        <f>E58</f>
         <v/>
       </c>
     </row>
@@ -14289,44 +14055,40 @@
       <c r="A59" s="10" t="n">
         <v>58</v>
       </c>
-      <c r="B59" s="12">
-        <f>G58</f>
-        <v/>
-      </c>
-      <c r="C59" s="12">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E58),0))*Paramètres!$B$3</f>
+      <c r="B59" s="10">
+        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;H58))</f>
+        <v/>
+      </c>
+      <c r="C59" s="16">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,B59),0)</f>
         <v/>
       </c>
       <c r="D59" s="12">
-        <f>D58+C59</f>
-        <v/>
-      </c>
-      <c r="E59" s="10">
-        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;D59))</f>
-        <v/>
-      </c>
-      <c r="F59" s="10">
-        <f>E59-E58</f>
-        <v/>
-      </c>
-      <c r="G59" s="16">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E59),0)</f>
+        <f>C59*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="E59" s="16">
+        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,B59),0))*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="F59" s="12">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(B59,160)),0)</f>
+        <v/>
+      </c>
+      <c r="G59" s="12">
+        <f>C59-F59</f>
         <v/>
       </c>
       <c r="H59" s="12">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(E59,160)),0)</f>
-        <v/>
-      </c>
-      <c r="I59" s="12">
-        <f>G59-H59</f>
-        <v/>
-      </c>
-      <c r="J59" s="16">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E59),0))*Paramètres!$B$3</f>
-        <v/>
-      </c>
-      <c r="K59" s="12">
-        <f>D59-IFERROR(INDEX('Plan d''achat'!$K$2:$K$190,E59),0)</f>
+        <f>H58+E59</f>
+        <v/>
+      </c>
+      <c r="I59" s="10">
+        <f>B59-B58</f>
+        <v/>
+      </c>
+      <c r="J59" s="12">
+        <f>E59</f>
         <v/>
       </c>
     </row>
@@ -14334,44 +14096,40 @@
       <c r="A60" s="10" t="n">
         <v>59</v>
       </c>
-      <c r="B60" s="12">
-        <f>G59</f>
-        <v/>
-      </c>
-      <c r="C60" s="12">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E59),0))*Paramètres!$B$3</f>
+      <c r="B60" s="10">
+        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;H59))</f>
+        <v/>
+      </c>
+      <c r="C60" s="16">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,B60),0)</f>
         <v/>
       </c>
       <c r="D60" s="12">
-        <f>D59+C60</f>
-        <v/>
-      </c>
-      <c r="E60" s="10">
-        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;D60))</f>
-        <v/>
-      </c>
-      <c r="F60" s="10">
-        <f>E60-E59</f>
-        <v/>
-      </c>
-      <c r="G60" s="16">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E60),0)</f>
+        <f>C60*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="E60" s="16">
+        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,B60),0))*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="F60" s="12">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(B60,160)),0)</f>
+        <v/>
+      </c>
+      <c r="G60" s="12">
+        <f>C60-F60</f>
         <v/>
       </c>
       <c r="H60" s="12">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(E60,160)),0)</f>
-        <v/>
-      </c>
-      <c r="I60" s="12">
-        <f>G60-H60</f>
-        <v/>
-      </c>
-      <c r="J60" s="16">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E60),0))*Paramètres!$B$3</f>
-        <v/>
-      </c>
-      <c r="K60" s="12">
-        <f>D60-IFERROR(INDEX('Plan d''achat'!$K$2:$K$190,E60),0)</f>
+        <f>H59+E60</f>
+        <v/>
+      </c>
+      <c r="I60" s="10">
+        <f>B60-B59</f>
+        <v/>
+      </c>
+      <c r="J60" s="12">
+        <f>E60</f>
         <v/>
       </c>
     </row>
@@ -14379,44 +14137,40 @@
       <c r="A61" s="10" t="n">
         <v>60</v>
       </c>
-      <c r="B61" s="12">
-        <f>G60</f>
-        <v/>
-      </c>
-      <c r="C61" s="12">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E60),0))*Paramètres!$B$3</f>
+      <c r="B61" s="10">
+        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;H60))</f>
+        <v/>
+      </c>
+      <c r="C61" s="16">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,B61),0)</f>
         <v/>
       </c>
       <c r="D61" s="12">
-        <f>D60+C61</f>
-        <v/>
-      </c>
-      <c r="E61" s="10">
-        <f>MIN(189,COUNTIF('Plan d''achat'!$K$2:$K$190,"&lt;="&amp;D61))</f>
-        <v/>
-      </c>
-      <c r="F61" s="10">
-        <f>E61-E60</f>
-        <v/>
-      </c>
-      <c r="G61" s="16">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,E61),0)</f>
+        <f>C61*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="E61" s="16">
+        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,B61),0))*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="F61" s="12">
+        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(B61,160)),0)</f>
+        <v/>
+      </c>
+      <c r="G61" s="12">
+        <f>C61-F61</f>
         <v/>
       </c>
       <c r="H61" s="12">
-        <f>Paramètres!$B$5+IFERROR(INDEX('Plan d''achat'!$I$2:$I$190,MIN(E61,160)),0)</f>
-        <v/>
-      </c>
-      <c r="I61" s="12">
-        <f>G61-H61</f>
-        <v/>
-      </c>
-      <c r="J61" s="16">
-        <f>(Paramètres!$B$5*(1-Paramètres!$B$4)+IFERROR(INDEX('Plan d''achat'!$J$2:$J$190,E61),0))*Paramètres!$B$3</f>
-        <v/>
-      </c>
-      <c r="K61" s="12">
-        <f>D61-IFERROR(INDEX('Plan d''achat'!$K$2:$K$190,E61),0)</f>
+        <f>H60+E61</f>
+        <v/>
+      </c>
+      <c r="I61" s="10">
+        <f>B61-B60</f>
+        <v/>
+      </c>
+      <c r="J61" s="12">
+        <f>E61</f>
         <v/>
       </c>
     </row>
